--- a/nested-array-prototypes/BigSpill 2.0 - Proto.xlsx
+++ b/nested-array-prototypes/BigSpill 2.0 - Proto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PatrickHogan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3733CF7-00D9-4D4F-8DBE-68B391A9CCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F438D02C-363E-4E5F-96F0-465FDF4114EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="893" xr2:uid="{2BAC9648-7901-4C2D-8363-8B16D8920BAA}"/>
   </bookViews>
@@ -53,7 +53,7 @@
     <definedName name="GameTIme">PTQWise!$F$8:$F$10</definedName>
     <definedName name="Grid">Navigate2D!$B$14:$G$20</definedName>
     <definedName name="GridLookupλ">_xlfn.LAMBDA(_xlpm.lookup_values,_xlpm.match_array,_xlpm.return_array,_xlop.if_not_found,_xlop.match_mode,_xlop.search_mode, _xlfn.LET(_xlpm.height₁, ROWS(_xlpm.match_array), _xlpm.width₁, COLUMNS(_xlpm.match_array), _xlpm.height₂, ROWS(_xlpm.return_array), _xlpm.width₂, COLUMNS(_xlpm.return_array), _xlpm.ShapeMisMatch?, OR(_xlpm.height₁ &lt;&gt; _xlpm.height₂, _xlpm.width₁ &lt;&gt; _xlpm.width₂), _xlpm.NotPresent?, NOT(_xlfn.HASALL(_xlpm.match_array, _xlpm.lookup_values)), IF(_xlpm.NotPresent?, #N/A, IF(_xlpm.ShapeMisMatch?, #VALUE!, _xlfn.LET(_xlpm.if_not_found, IF(_xlfn.ISOMITTED(_xlpm.if_not_found), NA(), _xlpm.if_not_found), _xlpm.match_mode, IF(_xlfn.ISOMITTED(_xlpm.match_mode), 0, _xlpm.match_mode), _xlpm.search_mode, IF(_xlfn.ISOMITTED(_xlpm.search_mode), 1, _xlpm.search_mode), _xlpm.R, _xlfn.XMATCH(_xlpm.lookup_values, _xlfn.TOCOL(_xlpm.match_array), _xlpm.match_mode, _xlpm.search_mode), _xlpm.i, QUOTIENT(_xlpm.R - 1, _xlpm.width₁) + 1, _xlpm.j, MOD(_xlpm.R - 1, _xlpm.width₁) + 1, _xlpm.final, _xlfn.IFNA(INDEX(_xlpm.return_array, _xlpm.i, _xlpm.j), _xlpm.if_not_found), _xlpm.final)))))</definedName>
-    <definedName name="HSplitλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.split_interval,_xlop.pad_with, _xlfn.LET(_xlpm.height, ROWS(_xlpm.array), _xlpm.width, COLUMNS(_xlpm.array), _xlpm.split_interval, INDEX(_xlpm.split_interval, 1, 1), _xlpm.IsScalar?, AND(_xlpm.height = 1, _xlpm.width = 1), _xlpm.IsNx1?, _xlpm.width = 1, _xlpm.InvalidSplit?, OR(ISTEXT(_xlpm.split_interval), _xlpm.split_interval &lt;= 0), IF(OR(_xlpm.IsScalar?, _xlpm.IsNx1?), _xlfn._ARRAY(_xlfn._ARRAYROW(_xlpm.array)), IF(_xlpm.InvalidSplit?, #VALUE!, _xlfn.LET(_xlpm.pad_with, IF(_xlfn.ISOMITTED(_xlpm.pad_with), NA(), INDEX(_xlpm.pad_with, 1, 1)), _xlpm.PadCols, MOD(-_xlpm.width, _xlpm.split_interval), _xlpm.new_array, _xlfn.EXPAND(_xlpm.array, , _xlpm.width + _xlpm.PadCols, _xlpm.pad_with), _xlpm.anchors, _xlfn.SEQUENCE((_xlpm.PadCols + _xlpm.width) / _xlpm.split_interval, , 1, _xlpm.split_interval), _xlpm.step, _xlfn.SEQUENCE(_xlpm.split_interval, , 0), _xlpm.Partλ, _xlfn.LAMBDA(_xlpm.idx, _xlfn.LET(_xlpm.r, _xlpm.idx + _xlpm.step, _xlpm.part, _xlfn.CHOOSECOLS(_xlpm.new_array, _xlpm.r), _xlpm.part)), _xlpm.lists, _xlfn.MAP(_xlpm.anchors, _xlpm.Partλ), _xlpm.lists)))))</definedName>
+    <definedName name="HSplitλ">_xlfn.LAMBDA(_xlpm.array,_xlpm.split_interval,_xlop.pad_with, _xlfn.LET(_xlpm.height, ROWS(_xlpm.array), _xlpm.width, COLUMNS(_xlpm.array), _xlpm.split_interval, INDEX(_xlpm.split_interval, 1, 1), _xlpm.IsScalar?, AND(_xlpm.height = 1, _xlpm.width = 1), _xlpm.IsNx1?, _xlpm.width = 1, _xlpm.InvalidSplit?, OR(ISTEXT(_xlpm.split_interval), _xlpm.split_interval &lt;= 0), IF(OR(_xlpm.IsScalar?, _xlpm.IsNx1?), _xlfn._ARRAY(_xlfn._ARRAYROW(_xlpm.array)), IF(_xlpm.InvalidSplit?, #VALUE!, _xlfn.LET(_xlpm.pad_with, IF(_xlfn.ISOMITTED(_xlpm.pad_with), NA(), INDEX(_xlpm.pad_with, 1, 1)), _xlpm.PadCols, MOD(-_xlpm.width, _xlpm.split_interval), _xlpm.new_array, _xlfn.EXPAND(_xlpm.array, , _xlpm.width + _xlpm.PadCols, _xlpm.pad_with), _xlpm.anchors, _xlfn.SEQUENCE(, (_xlpm.PadCols + _xlpm.width) / _xlpm.split_interval, 1, _xlpm.split_interval), _xlpm.step, _xlfn.SEQUENCE(_xlpm.split_interval, , 0), _xlpm.Partλ, _xlfn.LAMBDA(_xlpm.idx, _xlfn.LET(_xlpm.r, _xlpm.idx + _xlpm.step, _xlpm.part, _xlfn.CHOOSECOLS(_xlpm.new_array, _xlpm.r), _xlpm.part)), _xlpm.lists, _xlfn.MAP(_xlpm.anchors, _xlpm.Partλ), _xlpm.lists)))))</definedName>
     <definedName name="Icons">GridLookup!$G$12:$H$13</definedName>
     <definedName name="Kernel_1">Convolve!$I$5:$K$7</definedName>
     <definedName name="Kernel_2">Convolve!$I$9:$J$10</definedName>
@@ -2295,7 +2295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2435,13 +2435,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="18" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2454,31 +2448,25 @@
     <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2491,40 +2479,37 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3626,16 +3611,6 @@
     <v>100</v>
     <v>47</v>
   </a>
-  <a r="2" c="4">
-    <v t="s">Cara</v>
-    <v t="s">HR</v>
-    <v>77</v>
-    <v t="s">East</v>
-    <v t="s">Dan</v>
-    <v t="s">IT</v>
-    <v>85</v>
-    <v t="s">South</v>
-  </a>
   <a r="4" c="5">
     <v>38</v>
     <v>86</v>
@@ -3657,6 +3632,16 @@
     <v>93</v>
     <v>15</v>
     <v>100</v>
+  </a>
+  <a r="2" c="4">
+    <v t="s">Cara</v>
+    <v t="s">HR</v>
+    <v>77</v>
+    <v t="s">East</v>
+    <v t="s">Dan</v>
+    <v t="s">IT</v>
+    <v>85</v>
+    <v t="s">South</v>
   </a>
   <a r="2" c="4">
     <v t="s">Jack</v>
@@ -4316,7 +4301,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="295" row="9">
+  <wetp:taskpane dockstate="right" visibility="0" width="863" row="9">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -4351,7 +4336,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="C1:D37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.6640625" customWidth="1"/>
@@ -4648,10 +4633,10 @@
         <v>2</v>
       </c>
       <c r="F12" s="54"/>
-      <c r="G12" s="97" t="s">
+      <c r="G12" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="98" t="s">
+      <c r="H12" s="86" t="s">
         <v>24</v>
       </c>
       <c r="I12" s="54"/>
@@ -4703,10 +4688,10 @@
         <v>4</v>
       </c>
       <c r="F13" s="3"/>
-      <c r="G13" s="99" t="s">
+      <c r="G13" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="100" t="s">
+      <c r="H13" s="88" t="s">
         <v>26</v>
       </c>
       <c r="M13" s="66">
@@ -5130,109 +5115,36 @@
       <c r="V2" s="8"/>
       <c r="W2" s="8"/>
       <c r="X2" s="8"/>
-      <c r="Y2" s="86"/>
+      <c r="Y2" s="79"/>
     </row>
     <row r="3" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B3" s="9"/>
-      <c r="C3" s="85" t="s">
+      <c r="C3" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="85"/>
-      <c r="N3" s="85"/>
-      <c r="O3" s="85"/>
-      <c r="P3" s="85"/>
-      <c r="Q3" s="85"/>
-      <c r="R3" s="85"/>
-      <c r="S3" s="85"/>
-      <c r="T3" s="85"/>
-      <c r="U3" s="85"/>
-      <c r="V3" s="85"/>
-      <c r="W3" s="85"/>
-      <c r="X3" s="85"/>
-      <c r="Y3" s="87"/>
+      <c r="Y3" s="80"/>
     </row>
     <row r="4" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B4" s="9"/>
-      <c r="C4" s="85" t="s">
+      <c r="C4" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="85"/>
-      <c r="P4" s="85"/>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="85"/>
-      <c r="U4" s="85"/>
-      <c r="V4" s="85"/>
-      <c r="W4" s="85"/>
-      <c r="X4" s="85"/>
-      <c r="Y4" s="87"/>
+      <c r="Y4" s="80"/>
     </row>
     <row r="5" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="85"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="85"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="85"/>
-      <c r="K5" s="85"/>
-      <c r="L5" s="85"/>
-      <c r="M5" s="85"/>
-      <c r="N5" s="85" t="s">
+      <c r="N5" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="85"/>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="85"/>
-      <c r="R5" s="85"/>
-      <c r="S5" s="85"/>
-      <c r="T5" s="85"/>
-      <c r="U5" s="85"/>
-      <c r="V5" s="85"/>
-      <c r="W5" s="85"/>
-      <c r="X5" s="85"/>
-      <c r="Y5" s="87"/>
+      <c r="Y5" s="80"/>
     </row>
     <row r="6" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B6" s="9"/>
-      <c r="C6" s="85" t="s">
+      <c r="C6" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="85"/>
-      <c r="K6" s="85"/>
-      <c r="L6" s="85"/>
-      <c r="M6" s="85"/>
       <c r="N6" s="19">
         <v>1</v>
       </c>
@@ -5242,31 +5154,13 @@
       <c r="P6" s="19">
         <v>3</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85"/>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
-      <c r="V6" s="85"/>
-      <c r="W6" s="85"/>
-      <c r="X6" s="85"/>
-      <c r="Y6" s="87"/>
+      <c r="Y6" s="80"/>
     </row>
     <row r="7" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B7" s="9"/>
-      <c r="C7" s="88" t="s">
+      <c r="C7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="85"/>
-      <c r="K7" s="85"/>
-      <c r="L7" s="85"/>
-      <c r="M7" s="85"/>
       <c r="N7" s="19">
         <v>4</v>
       </c>
@@ -5276,31 +5170,13 @@
       <c r="P7" s="19">
         <v>6</v>
       </c>
-      <c r="Q7" s="85"/>
-      <c r="R7" s="85"/>
-      <c r="S7" s="85"/>
-      <c r="T7" s="85"/>
-      <c r="U7" s="85"/>
-      <c r="V7" s="85"/>
-      <c r="W7" s="85"/>
-      <c r="X7" s="85"/>
-      <c r="Y7" s="87"/>
+      <c r="Y7" s="80"/>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B8" s="9"/>
-      <c r="C8" s="85" t="s">
+      <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="85"/>
-      <c r="K8" s="85"/>
-      <c r="L8" s="85"/>
-      <c r="M8" s="85"/>
       <c r="N8" s="19">
         <v>7</v>
       </c>
@@ -5310,99 +5186,28 @@
       <c r="P8" s="19">
         <v>9</v>
       </c>
-      <c r="Q8" s="85"/>
-      <c r="R8" s="85"/>
-      <c r="S8" s="85"/>
-      <c r="T8" s="85"/>
-      <c r="U8" s="85"/>
-      <c r="V8" s="85"/>
-      <c r="W8" s="85"/>
-      <c r="X8" s="85"/>
-      <c r="Y8" s="87"/>
+      <c r="Y8" s="80"/>
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B9" s="9"/>
-      <c r="C9" s="85" t="s">
+      <c r="C9" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
-      <c r="J9" s="85"/>
-      <c r="K9" s="85"/>
-      <c r="L9" s="85"/>
-      <c r="M9" s="85"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="85"/>
-      <c r="P9" s="85"/>
-      <c r="Q9" s="85"/>
-      <c r="R9" s="85"/>
-      <c r="S9" s="85"/>
-      <c r="T9" s="85"/>
-      <c r="U9" s="85"/>
-      <c r="V9" s="85"/>
-      <c r="W9" s="85"/>
-      <c r="X9" s="85"/>
-      <c r="Y9" s="87"/>
+      <c r="Y9" s="80"/>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B10" s="9"/>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="85"/>
-      <c r="K10" s="85"/>
-      <c r="L10" s="85"/>
-      <c r="M10" s="85"/>
-      <c r="N10" s="88" t="s">
+      <c r="N10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O10" s="85"/>
-      <c r="P10" s="85"/>
-      <c r="Q10" s="85"/>
-      <c r="R10" s="85"/>
-      <c r="S10" s="85"/>
-      <c r="T10" s="85"/>
-      <c r="U10" s="85"/>
-      <c r="V10" s="85"/>
-      <c r="W10" s="85"/>
-      <c r="X10" s="85"/>
-      <c r="Y10" s="87"/>
+      <c r="Y10" s="80"/>
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B11" s="9"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="85"/>
-      <c r="K11" s="85"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="85"/>
-      <c r="N11" s="85"/>
-      <c r="O11" s="85"/>
-      <c r="P11" s="85"/>
-      <c r="Q11" s="85"/>
-      <c r="R11" s="85"/>
-      <c r="S11" s="85"/>
-      <c r="T11" s="85"/>
-      <c r="U11" s="85"/>
-      <c r="V11" s="85"/>
-      <c r="W11" s="85"/>
-      <c r="X11" s="85"/>
-      <c r="Y11" s="87"/>
+      <c r="Y11" s="80"/>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B12" s="10"/>
@@ -5428,7 +5233,7 @@
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
-      <c r="Y12" s="89"/>
+      <c r="Y12" s="81"/>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B13" s="15" t="s">
@@ -5438,11 +5243,6 @@
       <c r="J13" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="R13" s="85"/>
-      <c r="S13" s="85"/>
-      <c r="T13" s="85"/>
-      <c r="U13" s="85"/>
-      <c r="V13" s="85"/>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B14" s="2">
@@ -5464,7 +5264,7 @@
         <v>702</v>
       </c>
       <c r="H14" s="26"/>
-      <c r="I14" s="92"/>
+      <c r="I14" s="82"/>
       <c r="J14" s="23" t="s">
         <v>53</v>
       </c>
@@ -5499,12 +5299,12 @@
         <v>53</v>
       </c>
       <c r="U14" s="8"/>
-      <c r="V14" s="93" t="s">
+      <c r="V14" s="83" t="s">
         <v>59</v>
       </c>
       <c r="W14" s="8"/>
       <c r="X14" s="8"/>
-      <c r="Y14" s="86"/>
+      <c r="Y14" s="79"/>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B15" s="2">
@@ -5525,7 +5325,7 @@
       <c r="G15" s="22">
         <v>992</v>
       </c>
-      <c r="H15" s="91"/>
+      <c r="H15" s="3"/>
       <c r="I15" s="17"/>
       <c r="J15" s="23" t="s">
         <v>53</v>
@@ -5560,13 +5360,10 @@
       <c r="T15" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="U15" s="85"/>
-      <c r="V15" s="94" t="s">
+      <c r="V15" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="W15" s="85"/>
-      <c r="X15" s="85"/>
-      <c r="Y15" s="87"/>
+      <c r="Y15" s="80"/>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B16" s="2">
@@ -5587,7 +5384,7 @@
       <c r="G16" s="2">
         <v>300</v>
       </c>
-      <c r="H16" s="91"/>
+      <c r="H16" s="3"/>
       <c r="I16" s="17"/>
       <c r="J16" s="5" t="s">
         <v>7</v>
@@ -5622,13 +5419,10 @@
       <c r="T16" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="U16" s="85"/>
-      <c r="V16" s="94" t="s">
+      <c r="V16" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="W16" s="85"/>
-      <c r="X16" s="85"/>
-      <c r="Y16" s="87"/>
+      <c r="Y16" s="80"/>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B17" s="2">
@@ -5649,7 +5443,7 @@
       <c r="G17" s="2">
         <v>86</v>
       </c>
-      <c r="H17" s="91"/>
+      <c r="H17" s="3"/>
       <c r="I17" s="17"/>
       <c r="J17" s="5" t="s">
         <v>7</v>
@@ -5684,11 +5478,7 @@
       <c r="T17" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="U17" s="85"/>
-      <c r="V17" s="85"/>
-      <c r="W17" s="85"/>
-      <c r="X17" s="85"/>
-      <c r="Y17" s="87"/>
+      <c r="Y17" s="80"/>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B18" s="2">
@@ -5709,7 +5499,7 @@
       <c r="G18" s="2">
         <v>536</v>
       </c>
-      <c r="H18" s="91"/>
+      <c r="H18" s="3"/>
       <c r="I18" s="17"/>
       <c r="J18" s="5" t="s">
         <v>53</v>
@@ -5744,11 +5534,7 @@
       <c r="T18" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="U18" s="85"/>
-      <c r="V18" s="85"/>
-      <c r="W18" s="85"/>
-      <c r="X18" s="85"/>
-      <c r="Y18" s="87"/>
+      <c r="Y18" s="80"/>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B19" s="2">
@@ -5769,7 +5555,7 @@
       <c r="G19" s="2">
         <v>314</v>
       </c>
-      <c r="H19" s="91"/>
+      <c r="H19" s="3"/>
       <c r="I19" s="17"/>
       <c r="J19" s="5" t="s">
         <v>54</v>
@@ -5804,11 +5590,7 @@
       <c r="T19" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="U19" s="85"/>
-      <c r="V19" s="85"/>
-      <c r="W19" s="85"/>
-      <c r="X19" s="85"/>
-      <c r="Y19" s="87"/>
+      <c r="Y19" s="80"/>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B20" s="2">
@@ -5829,7 +5611,7 @@
       <c r="G20" s="2">
         <v>3</v>
       </c>
-      <c r="H20" s="91"/>
+      <c r="H20" s="3"/>
       <c r="I20" s="17"/>
       <c r="J20" s="5" t="s">
         <v>54</v>
@@ -5864,20 +5646,14 @@
       <c r="T20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="U20" s="85"/>
-      <c r="V20" s="85"/>
-      <c r="W20" s="85"/>
-      <c r="X20" s="85"/>
-      <c r="Y20" s="87"/>
+      <c r="Y20" s="80"/>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B21" s="7"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="91"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
       <c r="I21" s="17"/>
       <c r="J21" s="5" t="s">
         <v>7</v>
@@ -5912,20 +5688,14 @@
       <c r="T21" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="U21" s="85"/>
-      <c r="V21" s="85"/>
-      <c r="W21" s="85"/>
-      <c r="X21" s="85"/>
-      <c r="Y21" s="87"/>
+      <c r="Y21" s="80"/>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B22" s="9"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="91"/>
-      <c r="H22" s="91"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
       <c r="I22" s="17"/>
       <c r="J22" s="5" t="s">
         <v>7</v>
@@ -5960,11 +5730,7 @@
       <c r="T22" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="U22" s="85"/>
-      <c r="V22" s="85"/>
-      <c r="W22" s="85"/>
-      <c r="X22" s="85"/>
-      <c r="Y22" s="87"/>
+      <c r="Y22" s="80"/>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B23" s="10"/>
@@ -5990,7 +5756,7 @@
       <c r="V23" s="11"/>
       <c r="W23" s="11"/>
       <c r="X23" s="11"/>
-      <c r="Y23" s="89"/>
+      <c r="Y23" s="81"/>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B24" s="7"/>
@@ -6024,7 +5790,7 @@
       <c r="V24" s="8"/>
       <c r="W24" s="8"/>
       <c r="X24" s="8"/>
-      <c r="Y24" s="86"/>
+      <c r="Y24" s="79"/>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B25" s="9"/>
@@ -6034,10 +5800,6 @@
       <c r="D25" s="31">
         <v>20</v>
       </c>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
       <c r="I25" s="9"/>
       <c r="J25" s="33" t="s">
         <v>55</v>
@@ -6045,28 +5807,21 @@
       <c r="K25" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="85"/>
       <c r="P25" s="24" t="s">
         <v>53</v>
       </c>
       <c r="Q25" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="R25" s="91"/>
-      <c r="S25" s="91"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
       <c r="T25" s="29" t="s">
         <v>72</v>
       </c>
       <c r="U25" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="V25" s="85"/>
-      <c r="W25" s="85"/>
-      <c r="X25" s="85"/>
-      <c r="Y25" s="87"/>
+      <c r="Y25" s="80"/>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B26" s="9"/>
@@ -6076,10 +5831,6 @@
       <c r="D26" s="31">
         <v>40</v>
       </c>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
       <c r="I26" s="9"/>
       <c r="J26" s="33" t="s">
         <v>55</v>
@@ -6087,28 +5838,21 @@
       <c r="K26" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="L26" s="85"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="85"/>
-      <c r="O26" s="85"/>
       <c r="P26" s="24" t="s">
         <v>55</v>
       </c>
       <c r="Q26" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="R26" s="91"/>
-      <c r="S26" s="91"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
       <c r="T26" s="29" t="s">
         <v>72</v>
       </c>
       <c r="U26" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="V26" s="85"/>
-      <c r="W26" s="85"/>
-      <c r="X26" s="85"/>
-      <c r="Y26" s="87"/>
+      <c r="Y26" s="80"/>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B27" s="10"/>
@@ -6134,7 +5878,7 @@
       <c r="V27" s="11"/>
       <c r="W27" s="11"/>
       <c r="X27" s="11"/>
-      <c r="Y27" s="89"/>
+      <c r="Y27" s="81"/>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B28" s="7"/>
@@ -6166,39 +5910,22 @@
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
       <c r="X28" s="8"/>
-      <c r="Y28" s="86"/>
+      <c r="Y28" s="79"/>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B29" s="9"/>
-      <c r="C29" s="95" t="s">
+      <c r="C29" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="91"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
+      <c r="D29" s="3"/>
       <c r="I29" s="9"/>
-      <c r="J29" s="96" t="s">
+      <c r="J29" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="85"/>
-      <c r="O29" s="85"/>
-      <c r="P29" s="96" t="s">
+      <c r="P29" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="Q29" s="85"/>
-      <c r="R29" s="85"/>
-      <c r="S29" s="85"/>
-      <c r="T29" s="85"/>
-      <c r="U29" s="85"/>
-      <c r="V29" s="85"/>
-      <c r="W29" s="85"/>
-      <c r="X29" s="85"/>
-      <c r="Y29" s="87"/>
+      <c r="Y29" s="80"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B30" s="9"/>
@@ -6209,10 +5936,6 @@
       <c r="D30" s="21">
         <v>963</v>
       </c>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
       <c r="I30" s="9"/>
       <c r="J30" s="23" t="str" cm="1">
         <f t="array" ref="J30:K31">Navigate2Dλ(KernelB,TerrainMask,1)</f>
@@ -6221,23 +5944,12 @@
       <c r="K30" s="23" t="str">
         <v>R</v>
       </c>
-      <c r="L30" s="91"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="85"/>
-      <c r="O30" s="85"/>
-      <c r="P30" s="91" t="str" cm="1">
+      <c r="L30" s="3"/>
+      <c r="P30" s="3" t="str" cm="1">
         <f t="array" ref="P30">Navigate2Dλ(KernelC,TerrainMask,2)</f>
         <v>Kernel: R2C10</v>
       </c>
-      <c r="Q30" s="85"/>
-      <c r="R30" s="85"/>
-      <c r="S30" s="85"/>
-      <c r="T30" s="85"/>
-      <c r="U30" s="85"/>
-      <c r="V30" s="85"/>
-      <c r="W30" s="85"/>
-      <c r="X30" s="85"/>
-      <c r="Y30" s="87"/>
+      <c r="Y30" s="80"/>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B31" s="9"/>
@@ -6247,10 +5959,6 @@
       <c r="D31" s="21">
         <v>642</v>
       </c>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
       <c r="I31" s="9"/>
       <c r="J31" s="23" t="str">
         <v>R</v>
@@ -6258,102 +5966,50 @@
       <c r="K31" s="23" t="str">
         <v>S</v>
       </c>
-      <c r="L31" s="91"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="85"/>
-      <c r="O31" s="85"/>
-      <c r="P31" s="85"/>
-      <c r="Q31" s="85"/>
-      <c r="R31" s="85"/>
-      <c r="S31" s="85"/>
-      <c r="T31" s="85"/>
-      <c r="U31" s="85"/>
-      <c r="V31" s="85"/>
-      <c r="W31" s="85"/>
-      <c r="X31" s="85"/>
-      <c r="Y31" s="87"/>
+      <c r="L31" s="3"/>
+      <c r="Y31" s="80"/>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B32" s="9"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="85"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
       <c r="I32" s="9"/>
-      <c r="J32" s="91"/>
-      <c r="K32" s="91"/>
-      <c r="L32" s="91"/>
-      <c r="M32" s="85"/>
-      <c r="N32" s="85"/>
-      <c r="O32" s="85"/>
-      <c r="P32" s="90" t="s">
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="P32" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="Q32" s="85"/>
-      <c r="R32" s="85"/>
-      <c r="S32" s="85"/>
-      <c r="T32" s="85"/>
-      <c r="U32" s="90" t="s">
+      <c r="U32" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="V32" s="85"/>
-      <c r="W32" s="85"/>
-      <c r="X32" s="85"/>
-      <c r="Y32" s="87"/>
+      <c r="Y32" s="80"/>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B33" s="9"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="85"/>
-      <c r="E33" s="85"/>
-      <c r="F33" s="85"/>
-      <c r="G33" s="85"/>
-      <c r="H33" s="85"/>
       <c r="I33" s="9"/>
-      <c r="J33" s="90" t="s">
+      <c r="J33" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="K33" s="91"/>
-      <c r="L33" s="91"/>
-      <c r="M33" s="85"/>
-      <c r="N33" s="85"/>
-      <c r="O33" s="85"/>
-      <c r="P33" s="96" t="s">
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="P33" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Q33" s="85"/>
-      <c r="R33" s="85"/>
-      <c r="S33" s="85"/>
-      <c r="T33" s="85"/>
-      <c r="U33" s="96" t="s">
+      <c r="U33" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="V33" s="85"/>
-      <c r="W33" s="85"/>
-      <c r="X33" s="85"/>
-      <c r="Y33" s="87"/>
+      <c r="Y33" s="80"/>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B34" s="9"/>
-      <c r="C34" s="90" t="s">
+      <c r="C34" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="85"/>
-      <c r="F34" s="85"/>
-      <c r="G34" s="85"/>
-      <c r="H34" s="85"/>
       <c r="I34" s="9"/>
-      <c r="J34" s="96" t="s">
+      <c r="J34" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K34" s="91"/>
-      <c r="L34" s="91"/>
-      <c r="M34" s="85"/>
-      <c r="N34" s="85"/>
-      <c r="O34" s="85"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
       <c r="P34" s="25" t="str" cm="1">
         <f t="array" ref="P34:Q35">Navigate2Dλ(KernelC,TerrainMask,4)</f>
         <v>R</v>
@@ -6361,9 +6017,6 @@
       <c r="Q34" s="25" t="str">
         <v>V</v>
       </c>
-      <c r="R34" s="85"/>
-      <c r="S34" s="85"/>
-      <c r="T34" s="85"/>
       <c r="U34" s="27" t="str" cm="1">
         <f t="array" ref="U34:V37">Navigate2Dλ(KernelC,TerrainMask,,4,2)</f>
         <v>R</v>
@@ -6371,20 +6024,13 @@
       <c r="V34" s="27" t="str">
         <v>K</v>
       </c>
-      <c r="W34" s="85"/>
-      <c r="X34" s="85"/>
-      <c r="Y34" s="87"/>
+      <c r="Y34" s="80"/>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B35" s="9"/>
-      <c r="C35" s="96" t="s">
+      <c r="C35" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="85"/>
-      <c r="E35" s="85"/>
-      <c r="F35" s="85"/>
-      <c r="G35" s="85"/>
-      <c r="H35" s="85"/>
       <c r="I35" s="9"/>
       <c r="J35" s="14" t="str" cm="1">
         <f t="array" ref="J35:L37">Navigate2Dλ(KernelB,TerrainMask,9,3,3)</f>
@@ -6396,27 +6042,19 @@
       <c r="L35" s="14" t="str">
         <v>R</v>
       </c>
-      <c r="M35" s="85"/>
-      <c r="N35" s="85"/>
-      <c r="O35" s="85"/>
       <c r="P35" s="25" t="str">
         <v>S</v>
       </c>
       <c r="Q35" s="25" t="str">
         <v>S</v>
       </c>
-      <c r="R35" s="85"/>
-      <c r="S35" s="85"/>
-      <c r="T35" s="85"/>
       <c r="U35" s="27" t="str">
         <v>R</v>
       </c>
       <c r="V35" s="27" t="str">
         <v>R</v>
       </c>
-      <c r="W35" s="85"/>
-      <c r="X35" s="85"/>
-      <c r="Y35" s="87"/>
+      <c r="Y35" s="80"/>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B36" s="9"/>
@@ -6427,10 +6065,6 @@
       <c r="D36" s="22">
         <v>702</v>
       </c>
-      <c r="E36" s="85"/>
-      <c r="F36" s="85"/>
-      <c r="G36" s="85"/>
-      <c r="H36" s="85"/>
       <c r="I36" s="9"/>
       <c r="J36" s="14" t="str">
         <v>K</v>
@@ -6441,23 +6075,13 @@
       <c r="L36" s="14" t="str">
         <v>K</v>
       </c>
-      <c r="M36" s="85"/>
-      <c r="N36" s="85"/>
-      <c r="O36" s="85"/>
-      <c r="P36" s="85"/>
-      <c r="Q36" s="85"/>
-      <c r="R36" s="85"/>
-      <c r="S36" s="85"/>
-      <c r="T36" s="85"/>
       <c r="U36" s="27" t="str">
         <v>K</v>
       </c>
       <c r="V36" s="27" t="str">
         <v>V</v>
       </c>
-      <c r="W36" s="85"/>
-      <c r="X36" s="85"/>
-      <c r="Y36" s="87"/>
+      <c r="Y36" s="80"/>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B37" s="9"/>
@@ -6467,10 +6091,6 @@
       <c r="D37" s="22">
         <v>992</v>
       </c>
-      <c r="E37" s="85"/>
-      <c r="F37" s="85"/>
-      <c r="G37" s="85"/>
-      <c r="H37" s="85"/>
       <c r="I37" s="9"/>
       <c r="J37" s="14" t="str">
         <v>R</v>
@@ -6481,160 +6101,46 @@
       <c r="L37" s="14" t="str">
         <v>K</v>
       </c>
-      <c r="M37" s="85"/>
-      <c r="N37" s="85"/>
-      <c r="O37" s="85"/>
-      <c r="P37" s="85"/>
-      <c r="Q37" s="85"/>
-      <c r="R37" s="85"/>
-      <c r="S37" s="85"/>
-      <c r="T37" s="85"/>
       <c r="U37" s="27" t="str">
         <v>V</v>
       </c>
       <c r="V37" s="27" t="str">
         <v>R</v>
       </c>
-      <c r="W37" s="85"/>
-      <c r="X37" s="85"/>
-      <c r="Y37" s="87"/>
+      <c r="Y37" s="80"/>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B38" s="9"/>
-      <c r="C38" s="85"/>
-      <c r="D38" s="85"/>
-      <c r="E38" s="85"/>
-      <c r="F38" s="85"/>
-      <c r="G38" s="85"/>
-      <c r="H38" s="85"/>
       <c r="I38" s="9"/>
-      <c r="J38" s="85"/>
-      <c r="K38" s="85"/>
-      <c r="L38" s="85"/>
-      <c r="M38" s="85"/>
-      <c r="N38" s="85"/>
-      <c r="O38" s="85"/>
-      <c r="P38" s="90" t="s">
+      <c r="P38" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="Q38" s="85"/>
-      <c r="R38" s="85"/>
-      <c r="S38" s="85"/>
-      <c r="T38" s="85"/>
-      <c r="U38" s="85"/>
-      <c r="V38" s="85"/>
-      <c r="W38" s="85"/>
-      <c r="X38" s="85"/>
-      <c r="Y38" s="87"/>
+      <c r="Y38" s="80"/>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B39" s="9"/>
-      <c r="C39" s="85"/>
-      <c r="D39" s="85"/>
-      <c r="E39" s="85"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="85"/>
-      <c r="H39" s="85"/>
       <c r="I39" s="9"/>
-      <c r="J39" s="85"/>
-      <c r="K39" s="85"/>
-      <c r="L39" s="85"/>
-      <c r="M39" s="85"/>
-      <c r="N39" s="85"/>
-      <c r="O39" s="85"/>
-      <c r="P39" s="96" t="s">
+      <c r="P39" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="Q39" s="85"/>
-      <c r="R39" s="85"/>
-      <c r="S39" s="85"/>
-      <c r="T39" s="85"/>
-      <c r="U39" s="85"/>
-      <c r="V39" s="85"/>
-      <c r="W39" s="85"/>
-      <c r="X39" s="85"/>
-      <c r="Y39" s="87"/>
+      <c r="Y39" s="80"/>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B40" s="9"/>
-      <c r="C40" s="85"/>
-      <c r="D40" s="85"/>
-      <c r="E40" s="85"/>
-      <c r="F40" s="85"/>
-      <c r="G40" s="85"/>
-      <c r="H40" s="85"/>
       <c r="I40" s="9"/>
-      <c r="J40" s="85"/>
-      <c r="K40" s="85"/>
-      <c r="L40" s="85"/>
-      <c r="M40" s="85"/>
-      <c r="N40" s="85"/>
-      <c r="O40" s="85"/>
-      <c r="P40" s="91" t="e" cm="1">
+      <c r="P40" s="3" t="e" cm="1">
         <f t="array" ref="P40">Navigate2Dλ(KernelD,TerrainMask,6)</f>
         <v>#N/A</v>
       </c>
-      <c r="Q40" s="85"/>
-      <c r="R40" s="85"/>
-      <c r="S40" s="85"/>
-      <c r="T40" s="85"/>
-      <c r="U40" s="85"/>
-      <c r="V40" s="85"/>
-      <c r="W40" s="85"/>
-      <c r="X40" s="85"/>
-      <c r="Y40" s="87"/>
+      <c r="Y40" s="80"/>
     </row>
     <row r="41" spans="2:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B41" s="9"/>
-      <c r="C41" s="85"/>
-      <c r="D41" s="85"/>
-      <c r="E41" s="85"/>
-      <c r="F41" s="85"/>
-      <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
-      <c r="I41" s="85"/>
-      <c r="J41" s="85"/>
-      <c r="K41" s="85"/>
-      <c r="L41" s="85"/>
-      <c r="M41" s="85"/>
-      <c r="N41" s="85"/>
-      <c r="O41" s="85"/>
-      <c r="P41" s="85"/>
-      <c r="Q41" s="85"/>
-      <c r="R41" s="85"/>
-      <c r="S41" s="85"/>
-      <c r="T41" s="85"/>
-      <c r="U41" s="85"/>
-      <c r="V41" s="85"/>
-      <c r="W41" s="85"/>
-      <c r="X41" s="85"/>
-      <c r="Y41" s="87"/>
+      <c r="Y41" s="80"/>
     </row>
     <row r="42" spans="2:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B42" s="9"/>
-      <c r="C42" s="85"/>
-      <c r="D42" s="85"/>
-      <c r="E42" s="85"/>
-      <c r="F42" s="85"/>
-      <c r="G42" s="85"/>
-      <c r="H42" s="85"/>
-      <c r="I42" s="85"/>
-      <c r="J42" s="85"/>
-      <c r="K42" s="85"/>
-      <c r="L42" s="85"/>
-      <c r="M42" s="85"/>
-      <c r="N42" s="85"/>
-      <c r="O42" s="85"/>
-      <c r="P42" s="85"/>
-      <c r="Q42" s="85"/>
-      <c r="R42" s="85"/>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
-      <c r="V42" s="85"/>
-      <c r="W42" s="85"/>
-      <c r="X42" s="85"/>
-      <c r="Y42" s="87"/>
+      <c r="Y42" s="80"/>
     </row>
     <row r="43" spans="2:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B43" s="10"/>
@@ -6660,7 +6166,7 @@
       <c r="V43" s="11"/>
       <c r="W43" s="11"/>
       <c r="X43" s="11"/>
-      <c r="Y43" s="89"/>
+      <c r="Y43" s="81"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7623,17 +7129,19 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="e" cm="1" vm="72">
-        <f t="array" ref="H18:H19">HSplitλ(WeeklyData,5)</f>
+        <f t="array" ref="H18:I18">HSplitλ(WeeklyData,5)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="I18" s="3"/>
+      <c r="I18" s="3" t="e" vm="73">
+        <v>#VALUE!</v>
+      </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B19" s="3" t="e" vm="73">
+      <c r="B19" s="3" t="e" vm="74">
         <v>#VALUE!</v>
       </c>
       <c r="C19" s="3"/>
@@ -7641,9 +7149,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3" t="e" vm="74">
-        <v>#VALUE!</v>
-      </c>
+      <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -7679,7 +7185,10 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="e" cm="1" vm="76">
-        <f t="array" ref="B25:B26">HSplitλ(RegionalData,2)</f>
+        <f t="array" ref="B25:C25">HSplitλ(RegionalData,2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C25" t="e" vm="77">
         <v>#VALUE!</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -7687,9 +7196,7 @@
       </c>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B26" s="3" t="e" vm="77">
-        <v>#VALUE!</v>
-      </c>
+      <c r="B26" s="3"/>
       <c r="H26" s="3" t="e" cm="1" vm="78">
         <f t="array" ref="H26:H29">VSplitλ(WeeklyData,1)</f>
         <v>#VALUE!</v>
@@ -15834,119 +15341,119 @@
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="71" t="s">
         <v>217</v>
       </c>
-      <c r="D7" s="73" t="s">
+      <c r="D7" s="71" t="s">
         <v>133</v>
       </c>
-      <c r="F7" s="73" t="s">
+      <c r="F7" s="71" t="s">
         <v>232</v>
       </c>
-      <c r="H7" s="73" t="s">
+      <c r="H7" s="71" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B8" s="73" t="s">
+      <c r="B8" s="71" t="s">
         <v>218</v>
       </c>
-      <c r="D8" s="73" t="s">
+      <c r="D8" s="71" t="s">
         <v>225</v>
       </c>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="71" t="s">
         <v>235</v>
       </c>
-      <c r="H8" s="73" t="s">
+      <c r="H8" s="71" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B9" s="73" t="s">
+      <c r="B9" s="71" t="s">
         <v>219</v>
       </c>
-      <c r="D9" s="73" t="s">
+      <c r="D9" s="71" t="s">
         <v>226</v>
       </c>
-      <c r="F9" s="73" t="s">
+      <c r="F9" s="71" t="s">
         <v>228</v>
       </c>
-      <c r="H9" s="73" t="s">
+      <c r="H9" s="71" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B10" s="73" t="s">
+      <c r="B10" s="71" t="s">
         <v>220</v>
       </c>
-      <c r="D10" s="73" t="s">
+      <c r="D10" s="71" t="s">
         <v>227</v>
       </c>
-      <c r="F10" s="73" t="s">
+      <c r="F10" s="71" t="s">
         <v>229</v>
       </c>
-      <c r="H10" s="73" t="s">
+      <c r="H10" s="71" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="71" t="s">
         <v>221</v>
       </c>
-      <c r="D11" s="73" t="s">
+      <c r="D11" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="F11" s="73" t="s">
+      <c r="F11" s="71" t="s">
         <v>230</v>
       </c>
-      <c r="H11" s="73" t="s">
+      <c r="H11" s="71" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B12" s="73" t="s">
+      <c r="B12" s="71" t="s">
         <v>222</v>
       </c>
-      <c r="D12" s="73" t="s">
+      <c r="D12" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="F12" s="73" t="s">
+      <c r="F12" s="71" t="s">
         <v>231</v>
       </c>
-      <c r="H12" s="73" t="s">
+      <c r="H12" s="71" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B13" s="73" t="s">
+      <c r="B13" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="F13" s="73" t="s">
+      <c r="F13" s="71" t="s">
         <v>237</v>
       </c>
-      <c r="H13" s="73" t="s">
+      <c r="H13" s="71" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="73" t="s">
+      <c r="B14" s="71" t="s">
         <v>223</v>
       </c>
-      <c r="D14" s="73" t="s">
+      <c r="D14" s="71" t="s">
         <v>227</v>
       </c>
-      <c r="F14" s="73" t="s">
+      <c r="F14" s="71" t="s">
         <v>239</v>
       </c>
-      <c r="H14" s="73" t="s">
+      <c r="H14" s="71" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="73" t="s">
+      <c r="B15" s="71" t="s">
         <v>224</v>
       </c>
     </row>
@@ -16051,1509 +15558,1505 @@
   <dimension ref="B2:L87"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.08203125" style="71" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" style="71" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" style="71"/>
-    <col min="4" max="4" width="10.25" style="71" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" style="71" customWidth="1"/>
-    <col min="6" max="6" width="11.75" style="71" customWidth="1"/>
-    <col min="7" max="7" width="12.75" style="71" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="71" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="71"/>
-    <col min="10" max="10" width="7.83203125" style="71" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.6640625" style="71"/>
-    <col min="12" max="12" width="12.5" style="71" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.6640625" style="71"/>
+    <col min="1" max="1" width="5.08203125" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" customWidth="1"/>
+    <col min="4" max="4" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" customWidth="1"/>
+    <col min="6" max="6" width="11.75" customWidth="1"/>
+    <col min="7" max="7" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="38" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="38" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="38" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="D7" s="74" t="s">
+      <c r="D7" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="F7" s="74" t="s">
+      <c r="F7" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="H7" s="74" t="s">
+      <c r="H7" s="20" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B8" s="77" t="s">
+      <c r="B8" s="71" t="s">
         <v>251</v>
       </c>
-      <c r="D8" s="77" t="s">
+      <c r="D8" s="71" t="s">
         <v>252</v>
       </c>
-      <c r="F8" s="78" t="s">
+      <c r="F8" s="72" t="s">
         <v>262</v>
       </c>
-      <c r="H8" s="77" t="s">
+      <c r="H8" s="71" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="71" t="s">
         <v>253</v>
       </c>
-      <c r="D9" s="77" t="s">
+      <c r="D9" s="71" t="s">
         <v>254</v>
       </c>
-      <c r="F9" s="79" t="s">
+      <c r="F9" s="73" t="s">
         <v>258</v>
       </c>
-      <c r="H9" s="77" t="s">
+      <c r="H9" s="71" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="71" t="s">
         <v>255</v>
       </c>
-      <c r="D10" s="77" t="s">
+      <c r="D10" s="71" t="s">
         <v>256</v>
       </c>
-      <c r="F10" s="78" t="s">
+      <c r="F10" s="72" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="71" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B15" s="75" t="s">
+      <c r="B15" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="E15" s="75" t="s">
+      <c r="E15" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="I15" s="75" t="s">
+      <c r="I15" s="4" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B16" s="76" t="str" cm="1">
+      <c r="B16" s="3" t="str" cm="1">
         <f t="array" ref="B16:C27">Pairwiseλ(PoolA,PoolB)</f>
         <v>Bluebirds</v>
       </c>
-      <c r="C16" s="76" t="str">
+      <c r="C16" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="E16" s="76" t="str" cm="1">
+      <c r="E16" s="3" t="str" cm="1">
         <f t="array" ref="E16:G51">Triplewiseλ(PoolA,PoolB,GameTIme)</f>
         <v>Bluebirds</v>
       </c>
-      <c r="F16" s="76" t="str">
+      <c r="F16" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="G16" s="76" t="str">
+      <c r="G16" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="I16" s="76" t="str" cm="1">
+      <c r="I16" s="3" t="str" cm="1">
         <f t="array" ref="I16:L87">Quadwiseλ(PoolA,PoolB,GameTIme,Location)</f>
         <v>Bluebirds</v>
       </c>
-      <c r="J16" s="76" t="str">
+      <c r="J16" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K16" s="76" t="str">
+      <c r="K16" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L16" s="76" t="str">
+      <c r="L16" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B17" s="76" t="str">
+      <c r="B17" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="C17" s="76" t="str">
+      <c r="C17" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="E17" s="76" t="str">
+      <c r="E17" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="F17" s="76" t="str">
+      <c r="F17" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="G17" s="76" t="str">
+      <c r="G17" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="I17" s="76" t="str">
+      <c r="I17" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J17" s="76" t="str">
+      <c r="J17" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K17" s="76" t="str">
+      <c r="K17" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L17" s="76" t="str">
+      <c r="L17" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B18" s="76" t="str">
+      <c r="B18" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="C18" s="76" t="str">
+      <c r="C18" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="E18" s="76" t="str">
+      <c r="E18" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="F18" s="76" t="str">
+      <c r="F18" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="G18" s="76" t="str">
+      <c r="G18" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="I18" s="76" t="str">
+      <c r="I18" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J18" s="76" t="str">
+      <c r="J18" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K18" s="76" t="str">
+      <c r="K18" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L18" s="76" t="str">
+      <c r="L18" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B19" s="76" t="str">
+      <c r="B19" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="C19" s="76" t="str">
+      <c r="C19" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="E19" s="76" t="str">
+      <c r="E19" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="F19" s="76" t="str">
+      <c r="F19" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="G19" s="76" t="str">
+      <c r="G19" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="I19" s="76" t="str">
+      <c r="I19" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J19" s="76" t="str">
+      <c r="J19" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K19" s="76" t="str">
+      <c r="K19" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L19" s="76" t="str">
+      <c r="L19" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B20" s="76" t="str">
+      <c r="B20" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="C20" s="76" t="str">
+      <c r="C20" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="E20" s="76" t="str">
+      <c r="E20" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="F20" s="76" t="str">
+      <c r="F20" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="G20" s="76" t="str">
+      <c r="G20" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="I20" s="76" t="str">
+      <c r="I20" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J20" s="76" t="str">
+      <c r="J20" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K20" s="76" t="str">
+      <c r="K20" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L20" s="76" t="str">
+      <c r="L20" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B21" s="76" t="str">
+      <c r="B21" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="C21" s="76" t="str">
+      <c r="C21" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="E21" s="76" t="str">
+      <c r="E21" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="F21" s="76" t="str">
+      <c r="F21" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="G21" s="76" t="str">
+      <c r="G21" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="I21" s="76" t="str">
+      <c r="I21" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J21" s="76" t="str">
+      <c r="J21" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K21" s="76" t="str">
+      <c r="K21" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L21" s="76" t="str">
+      <c r="L21" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B22" s="76" t="str">
+      <c r="B22" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="C22" s="76" t="str">
+      <c r="C22" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="E22" s="76" t="str">
+      <c r="E22" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="F22" s="76" t="str">
+      <c r="F22" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="G22" s="76" t="str">
+      <c r="G22" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="I22" s="76" t="str">
+      <c r="I22" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J22" s="76" t="str">
+      <c r="J22" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K22" s="76" t="str">
+      <c r="K22" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L22" s="76" t="str">
+      <c r="L22" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B23" s="76" t="str">
+      <c r="B23" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="C23" s="76" t="str">
+      <c r="C23" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="E23" s="76" t="str">
+      <c r="E23" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="F23" s="76" t="str">
+      <c r="F23" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="G23" s="76" t="str">
+      <c r="G23" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="I23" s="76" t="str">
+      <c r="I23" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J23" s="76" t="str">
+      <c r="J23" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K23" s="76" t="str">
+      <c r="K23" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L23" s="76" t="str">
+      <c r="L23" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B24" s="76" t="str">
+      <c r="B24" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="C24" s="76" t="str">
+      <c r="C24" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="E24" s="76" t="str">
+      <c r="E24" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="F24" s="76" t="str">
+      <c r="F24" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="G24" s="76" t="str">
+      <c r="G24" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="I24" s="76" t="str">
+      <c r="I24" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J24" s="76" t="str">
+      <c r="J24" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K24" s="76" t="str">
+      <c r="K24" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L24" s="76" t="str">
+      <c r="L24" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B25" s="76" t="str">
+      <c r="B25" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="C25" s="76" t="str">
+      <c r="C25" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="E25" s="76" t="str">
+      <c r="E25" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="F25" s="76" t="str">
+      <c r="F25" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="G25" s="76" t="str">
+      <c r="G25" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="I25" s="76" t="str">
+      <c r="I25" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J25" s="76" t="str">
+      <c r="J25" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K25" s="76" t="str">
+      <c r="K25" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L25" s="76" t="str">
+      <c r="L25" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B26" s="76" t="str">
+      <c r="B26" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="C26" s="76" t="str">
+      <c r="C26" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="E26" s="76" t="str">
+      <c r="E26" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="F26" s="76" t="str">
+      <c r="F26" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="G26" s="76" t="str">
+      <c r="G26" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="I26" s="76" t="str">
+      <c r="I26" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J26" s="76" t="str">
+      <c r="J26" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K26" s="76" t="str">
+      <c r="K26" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L26" s="76" t="str">
+      <c r="L26" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B27" s="76" t="str">
+      <c r="B27" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="C27" s="76" t="str">
+      <c r="C27" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="E27" s="76" t="str">
+      <c r="E27" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="F27" s="76" t="str">
+      <c r="F27" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="G27" s="76" t="str">
+      <c r="G27" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="I27" s="76" t="str">
+      <c r="I27" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J27" s="76" t="str">
+      <c r="J27" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K27" s="76" t="str">
+      <c r="K27" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L27" s="76" t="str">
+      <c r="L27" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="E28" s="76" t="str">
+      <c r="E28" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="F28" s="76" t="str">
+      <c r="F28" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="G28" s="76" t="str">
+      <c r="G28" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="I28" s="76" t="str">
+      <c r="I28" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J28" s="76" t="str">
+      <c r="J28" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K28" s="76" t="str">
+      <c r="K28" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L28" s="76" t="str">
+      <c r="L28" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="E29" s="76" t="str">
+      <c r="E29" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="F29" s="76" t="str">
+      <c r="F29" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="G29" s="76" t="str">
+      <c r="G29" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="I29" s="76" t="str">
+      <c r="I29" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J29" s="76" t="str">
+      <c r="J29" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K29" s="76" t="str">
+      <c r="K29" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L29" s="76" t="str">
+      <c r="L29" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="E30" s="76" t="str">
+      <c r="E30" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="F30" s="76" t="str">
+      <c r="F30" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="G30" s="76" t="str">
+      <c r="G30" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="I30" s="76" t="str">
+      <c r="I30" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J30" s="76" t="str">
+      <c r="J30" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K30" s="76" t="str">
+      <c r="K30" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L30" s="76" t="str">
+      <c r="L30" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="E31" s="76" t="str">
+      <c r="E31" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="F31" s="76" t="str">
+      <c r="F31" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="G31" s="76" t="str">
+      <c r="G31" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="I31" s="76" t="str">
+      <c r="I31" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J31" s="76" t="str">
+      <c r="J31" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K31" s="76" t="str">
+      <c r="K31" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L31" s="76" t="str">
+      <c r="L31" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="E32" s="76" t="str">
+      <c r="E32" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="F32" s="76" t="str">
+      <c r="F32" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="G32" s="76" t="str">
+      <c r="G32" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="I32" s="76" t="str">
+      <c r="I32" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J32" s="76" t="str">
+      <c r="J32" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K32" s="76" t="str">
+      <c r="K32" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L32" s="76" t="str">
+      <c r="L32" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="33" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E33" s="76" t="str">
+      <c r="E33" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="F33" s="76" t="str">
+      <c r="F33" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="G33" s="76" t="str">
+      <c r="G33" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="I33" s="76" t="str">
+      <c r="I33" s="3" t="str">
         <v>Bluebirds</v>
       </c>
-      <c r="J33" s="76" t="str">
+      <c r="J33" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K33" s="76" t="str">
+      <c r="K33" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L33" s="76" t="str">
+      <c r="L33" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="34" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E34" s="76" t="str">
+      <c r="E34" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="F34" s="76" t="str">
+      <c r="F34" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="G34" s="76" t="str">
+      <c r="G34" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="I34" s="76" t="str">
+      <c r="I34" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J34" s="76" t="str">
+      <c r="J34" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K34" s="76" t="str">
+      <c r="K34" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L34" s="76" t="str">
+      <c r="L34" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="35" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E35" s="76" t="str">
+      <c r="E35" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="F35" s="76" t="str">
+      <c r="F35" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="G35" s="76" t="str">
+      <c r="G35" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="I35" s="76" t="str">
+      <c r="I35" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J35" s="76" t="str">
+      <c r="J35" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K35" s="76" t="str">
+      <c r="K35" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L35" s="76" t="str">
+      <c r="L35" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="36" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E36" s="76" t="str">
+      <c r="E36" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="F36" s="76" t="str">
+      <c r="F36" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="G36" s="76" t="str">
+      <c r="G36" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="I36" s="76" t="str">
+      <c r="I36" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J36" s="76" t="str">
+      <c r="J36" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K36" s="76" t="str">
+      <c r="K36" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L36" s="76" t="str">
+      <c r="L36" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="37" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E37" s="76" t="str">
+      <c r="E37" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="F37" s="76" t="str">
+      <c r="F37" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="G37" s="76" t="str">
+      <c r="G37" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="I37" s="76" t="str">
+      <c r="I37" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J37" s="76" t="str">
+      <c r="J37" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K37" s="76" t="str">
+      <c r="K37" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L37" s="76" t="str">
+      <c r="L37" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="38" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E38" s="76" t="str">
+      <c r="E38" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="F38" s="76" t="str">
+      <c r="F38" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="G38" s="76" t="str">
+      <c r="G38" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="I38" s="76" t="str">
+      <c r="I38" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J38" s="76" t="str">
+      <c r="J38" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K38" s="76" t="str">
+      <c r="K38" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L38" s="76" t="str">
+      <c r="L38" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="39" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E39" s="76" t="str">
+      <c r="E39" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="F39" s="76" t="str">
+      <c r="F39" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="G39" s="76" t="str">
+      <c r="G39" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="I39" s="76" t="str">
+      <c r="I39" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J39" s="76" t="str">
+      <c r="J39" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K39" s="76" t="str">
+      <c r="K39" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L39" s="76" t="str">
+      <c r="L39" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="40" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E40" s="76" t="str">
+      <c r="E40" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="F40" s="76" t="str">
+      <c r="F40" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="G40" s="76" t="str">
+      <c r="G40" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="I40" s="76" t="str">
+      <c r="I40" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J40" s="76" t="str">
+      <c r="J40" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K40" s="76" t="str">
+      <c r="K40" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L40" s="76" t="str">
+      <c r="L40" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="41" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E41" s="76" t="str">
+      <c r="E41" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="F41" s="76" t="str">
+      <c r="F41" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="G41" s="76" t="str">
+      <c r="G41" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="I41" s="76" t="str">
+      <c r="I41" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J41" s="76" t="str">
+      <c r="J41" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K41" s="76" t="str">
+      <c r="K41" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L41" s="76" t="str">
+      <c r="L41" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="42" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E42" s="76" t="str">
+      <c r="E42" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="F42" s="76" t="str">
+      <c r="F42" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="G42" s="76" t="str">
+      <c r="G42" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="I42" s="76" t="str">
+      <c r="I42" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J42" s="76" t="str">
+      <c r="J42" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K42" s="76" t="str">
+      <c r="K42" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L42" s="76" t="str">
+      <c r="L42" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="43" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E43" s="76" t="str">
+      <c r="E43" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="F43" s="76" t="str">
+      <c r="F43" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="G43" s="76" t="str">
+      <c r="G43" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="I43" s="76" t="str">
+      <c r="I43" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J43" s="76" t="str">
+      <c r="J43" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K43" s="76" t="str">
+      <c r="K43" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L43" s="76" t="str">
+      <c r="L43" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="44" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E44" s="76" t="str">
+      <c r="E44" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="F44" s="76" t="str">
+      <c r="F44" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="G44" s="76" t="str">
+      <c r="G44" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="I44" s="76" t="str">
+      <c r="I44" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J44" s="76" t="str">
+      <c r="J44" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K44" s="76" t="str">
+      <c r="K44" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L44" s="76" t="str">
+      <c r="L44" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="45" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E45" s="76" t="str">
+      <c r="E45" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="F45" s="76" t="str">
+      <c r="F45" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="G45" s="76" t="str">
+      <c r="G45" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="I45" s="76" t="str">
+      <c r="I45" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J45" s="76" t="str">
+      <c r="J45" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K45" s="76" t="str">
+      <c r="K45" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L45" s="76" t="str">
+      <c r="L45" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="46" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E46" s="76" t="str">
+      <c r="E46" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="F46" s="76" t="str">
+      <c r="F46" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="G46" s="76" t="str">
+      <c r="G46" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="I46" s="76" t="str">
+      <c r="I46" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J46" s="76" t="str">
+      <c r="J46" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K46" s="76" t="str">
+      <c r="K46" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L46" s="76" t="str">
+      <c r="L46" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="47" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E47" s="76" t="str">
+      <c r="E47" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="F47" s="76" t="str">
+      <c r="F47" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="G47" s="76" t="str">
+      <c r="G47" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="I47" s="76" t="str">
+      <c r="I47" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J47" s="76" t="str">
+      <c r="J47" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K47" s="76" t="str">
+      <c r="K47" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L47" s="76" t="str">
+      <c r="L47" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="48" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E48" s="76" t="str">
+      <c r="E48" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="F48" s="76" t="str">
+      <c r="F48" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="G48" s="76" t="str">
+      <c r="G48" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="I48" s="76" t="str">
+      <c r="I48" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J48" s="76" t="str">
+      <c r="J48" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K48" s="76" t="str">
+      <c r="K48" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L48" s="76" t="str">
+      <c r="L48" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="49" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E49" s="76" t="str">
+      <c r="E49" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="F49" s="76" t="str">
+      <c r="F49" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="G49" s="76" t="str">
+      <c r="G49" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="I49" s="76" t="str">
+      <c r="I49" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J49" s="76" t="str">
+      <c r="J49" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K49" s="76" t="str">
+      <c r="K49" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L49" s="76" t="str">
+      <c r="L49" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="50" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E50" s="76" t="str">
+      <c r="E50" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="F50" s="76" t="str">
+      <c r="F50" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="G50" s="76" t="str">
+      <c r="G50" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="I50" s="76" t="str">
+      <c r="I50" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J50" s="76" t="str">
+      <c r="J50" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K50" s="76" t="str">
+      <c r="K50" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L50" s="76" t="str">
+      <c r="L50" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="51" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="E51" s="76" t="str">
+      <c r="E51" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="F51" s="76" t="str">
+      <c r="F51" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="G51" s="76" t="str">
+      <c r="G51" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="I51" s="76" t="str">
+      <c r="I51" s="3" t="str">
         <v>Zephyrs</v>
       </c>
-      <c r="J51" s="76" t="str">
+      <c r="J51" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K51" s="76" t="str">
+      <c r="K51" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L51" s="76" t="str">
+      <c r="L51" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="52" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I52" s="76" t="str">
+      <c r="I52" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J52" s="76" t="str">
+      <c r="J52" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K52" s="76" t="str">
+      <c r="K52" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L52" s="76" t="str">
+      <c r="L52" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="53" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I53" s="76" t="str">
+      <c r="I53" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J53" s="76" t="str">
+      <c r="J53" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K53" s="76" t="str">
+      <c r="K53" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L53" s="76" t="str">
+      <c r="L53" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="54" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I54" s="76" t="str">
+      <c r="I54" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J54" s="76" t="str">
+      <c r="J54" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K54" s="76" t="str">
+      <c r="K54" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L54" s="76" t="str">
+      <c r="L54" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="55" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I55" s="76" t="str">
+      <c r="I55" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J55" s="76" t="str">
+      <c r="J55" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K55" s="76" t="str">
+      <c r="K55" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L55" s="76" t="str">
+      <c r="L55" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="56" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I56" s="76" t="str">
+      <c r="I56" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J56" s="76" t="str">
+      <c r="J56" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K56" s="76" t="str">
+      <c r="K56" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L56" s="76" t="str">
+      <c r="L56" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="57" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I57" s="76" t="str">
+      <c r="I57" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J57" s="76" t="str">
+      <c r="J57" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K57" s="76" t="str">
+      <c r="K57" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L57" s="76" t="str">
+      <c r="L57" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="58" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I58" s="76" t="str">
+      <c r="I58" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J58" s="76" t="str">
+      <c r="J58" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K58" s="76" t="str">
+      <c r="K58" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L58" s="76" t="str">
+      <c r="L58" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="59" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I59" s="76" t="str">
+      <c r="I59" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J59" s="76" t="str">
+      <c r="J59" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K59" s="76" t="str">
+      <c r="K59" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L59" s="76" t="str">
+      <c r="L59" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="60" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I60" s="76" t="str">
+      <c r="I60" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J60" s="76" t="str">
+      <c r="J60" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K60" s="76" t="str">
+      <c r="K60" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L60" s="76" t="str">
+      <c r="L60" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="61" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I61" s="76" t="str">
+      <c r="I61" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J61" s="76" t="str">
+      <c r="J61" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K61" s="76" t="str">
+      <c r="K61" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L61" s="76" t="str">
+      <c r="L61" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="62" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I62" s="76" t="str">
+      <c r="I62" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J62" s="76" t="str">
+      <c r="J62" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K62" s="76" t="str">
+      <c r="K62" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L62" s="76" t="str">
+      <c r="L62" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="63" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I63" s="76" t="str">
+      <c r="I63" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J63" s="76" t="str">
+      <c r="J63" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K63" s="76" t="str">
+      <c r="K63" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L63" s="76" t="str">
+      <c r="L63" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="64" spans="5:12" x14ac:dyDescent="0.45">
-      <c r="I64" s="76" t="str">
+      <c r="I64" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J64" s="76" t="str">
+      <c r="J64" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K64" s="76" t="str">
+      <c r="K64" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L64" s="76" t="str">
+      <c r="L64" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="65" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I65" s="76" t="str">
+      <c r="I65" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J65" s="76" t="str">
+      <c r="J65" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K65" s="76" t="str">
+      <c r="K65" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L65" s="76" t="str">
+      <c r="L65" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="66" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I66" s="76" t="str">
+      <c r="I66" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J66" s="76" t="str">
+      <c r="J66" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K66" s="76" t="str">
+      <c r="K66" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L66" s="76" t="str">
+      <c r="L66" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="67" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I67" s="76" t="str">
+      <c r="I67" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J67" s="76" t="str">
+      <c r="J67" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K67" s="76" t="str">
+      <c r="K67" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L67" s="76" t="str">
+      <c r="L67" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="68" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I68" s="76" t="str">
+      <c r="I68" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J68" s="76" t="str">
+      <c r="J68" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K68" s="76" t="str">
+      <c r="K68" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L68" s="76" t="str">
+      <c r="L68" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="69" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I69" s="76" t="str">
+      <c r="I69" s="3" t="str">
         <v>Mammoths</v>
       </c>
-      <c r="J69" s="76" t="str">
+      <c r="J69" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K69" s="76" t="str">
+      <c r="K69" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L69" s="76" t="str">
+      <c r="L69" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="70" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I70" s="76" t="str">
+      <c r="I70" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J70" s="76" t="str">
+      <c r="J70" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K70" s="76" t="str">
+      <c r="K70" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L70" s="76" t="str">
+      <c r="L70" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="71" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I71" s="76" t="str">
+      <c r="I71" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J71" s="76" t="str">
+      <c r="J71" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K71" s="76" t="str">
+      <c r="K71" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L71" s="76" t="str">
+      <c r="L71" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="72" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I72" s="76" t="str">
+      <c r="I72" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J72" s="76" t="str">
+      <c r="J72" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K72" s="76" t="str">
+      <c r="K72" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L72" s="76" t="str">
+      <c r="L72" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="73" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I73" s="76" t="str">
+      <c r="I73" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J73" s="76" t="str">
+      <c r="J73" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K73" s="76" t="str">
+      <c r="K73" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L73" s="76" t="str">
+      <c r="L73" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="74" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I74" s="76" t="str">
+      <c r="I74" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J74" s="76" t="str">
+      <c r="J74" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K74" s="76" t="str">
+      <c r="K74" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L74" s="76" t="str">
+      <c r="L74" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="75" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I75" s="76" t="str">
+      <c r="I75" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J75" s="76" t="str">
+      <c r="J75" s="3" t="str">
         <v>Stars</v>
       </c>
-      <c r="K75" s="76" t="str">
+      <c r="K75" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L75" s="76" t="str">
+      <c r="L75" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="76" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I76" s="76" t="str">
+      <c r="I76" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J76" s="76" t="str">
+      <c r="J76" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K76" s="76" t="str">
+      <c r="K76" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L76" s="76" t="str">
+      <c r="L76" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="77" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I77" s="76" t="str">
+      <c r="I77" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J77" s="76" t="str">
+      <c r="J77" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K77" s="76" t="str">
+      <c r="K77" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L77" s="76" t="str">
+      <c r="L77" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="78" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I78" s="76" t="str">
+      <c r="I78" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J78" s="76" t="str">
+      <c r="J78" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K78" s="76" t="str">
+      <c r="K78" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L78" s="76" t="str">
+      <c r="L78" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="79" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I79" s="76" t="str">
+      <c r="I79" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J79" s="76" t="str">
+      <c r="J79" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K79" s="76" t="str">
+      <c r="K79" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L79" s="76" t="str">
+      <c r="L79" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="80" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I80" s="76" t="str">
+      <c r="I80" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J80" s="76" t="str">
+      <c r="J80" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K80" s="76" t="str">
+      <c r="K80" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L80" s="76" t="str">
+      <c r="L80" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="81" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I81" s="76" t="str">
+      <c r="I81" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J81" s="76" t="str">
+      <c r="J81" s="3" t="str">
         <v>Buzz</v>
       </c>
-      <c r="K81" s="76" t="str">
+      <c r="K81" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L81" s="76" t="str">
+      <c r="L81" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="82" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I82" s="76" t="str">
+      <c r="I82" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J82" s="76" t="str">
+      <c r="J82" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K82" s="76" t="str">
+      <c r="K82" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L82" s="76" t="str">
+      <c r="L82" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="83" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I83" s="76" t="str">
+      <c r="I83" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J83" s="76" t="str">
+      <c r="J83" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K83" s="76" t="str">
+      <c r="K83" s="3" t="str">
         <v>Morning</v>
       </c>
-      <c r="L83" s="76" t="str">
+      <c r="L83" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="84" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I84" s="76" t="str">
+      <c r="I84" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J84" s="76" t="str">
+      <c r="J84" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K84" s="76" t="str">
+      <c r="K84" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L84" s="76" t="str">
+      <c r="L84" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="85" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I85" s="76" t="str">
+      <c r="I85" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J85" s="76" t="str">
+      <c r="J85" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K85" s="76" t="str">
+      <c r="K85" s="3" t="str">
         <v>Noon</v>
       </c>
-      <c r="L85" s="76" t="str">
+      <c r="L85" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
     <row r="86" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I86" s="76" t="str">
+      <c r="I86" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J86" s="76" t="str">
+      <c r="J86" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K86" s="76" t="str">
+      <c r="K86" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L86" s="76" t="str">
+      <c r="L86" s="3" t="str">
         <v>Gymnasium</v>
       </c>
     </row>
     <row r="87" spans="9:12" x14ac:dyDescent="0.45">
-      <c r="I87" s="76" t="str">
+      <c r="I87" s="3" t="str">
         <v>Wildcats</v>
       </c>
-      <c r="J87" s="76" t="str">
+      <c r="J87" s="3" t="str">
         <v>Griffons</v>
       </c>
-      <c r="K87" s="76" t="str">
+      <c r="K87" s="3" t="str">
         <v>Night</v>
       </c>
-      <c r="L87" s="76" t="str">
+      <c r="L87" s="3" t="str">
         <v>Outdoor court</v>
       </c>
     </row>
@@ -17592,109 +17095,109 @@
       </c>
     </row>
     <row r="5" spans="2:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="109">
+      <c r="B5" s="96">
         <v>72</v>
       </c>
-      <c r="C5" s="110">
+      <c r="C5" s="97">
         <v>100</v>
       </c>
-      <c r="D5" s="105">
+      <c r="D5" s="92">
         <v>65</v>
       </c>
-      <c r="E5" s="102">
-        <v>7</v>
-      </c>
-      <c r="F5" s="101">
+      <c r="E5" s="89">
+        <v>7</v>
+      </c>
+      <c r="F5" s="74">
         <v>58</v>
       </c>
-      <c r="G5" s="101">
-        <v>9</v>
-      </c>
-      <c r="I5" s="81">
-        <v>1</v>
-      </c>
-      <c r="J5" s="81">
-        <v>2</v>
-      </c>
-      <c r="K5" s="81">
+      <c r="G5" s="74">
+        <v>9</v>
+      </c>
+      <c r="I5" s="75">
+        <v>1</v>
+      </c>
+      <c r="J5" s="75">
+        <v>2</v>
+      </c>
+      <c r="K5" s="75">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="111">
+      <c r="B6" s="98">
         <v>75</v>
       </c>
-      <c r="C6" s="112">
+      <c r="C6" s="99">
         <v>58</v>
       </c>
-      <c r="D6" s="106">
+      <c r="D6" s="93">
         <v>57</v>
       </c>
-      <c r="E6" s="102">
+      <c r="E6" s="89">
         <v>31</v>
       </c>
-      <c r="F6" s="101">
+      <c r="F6" s="74">
         <v>89</v>
       </c>
-      <c r="G6" s="101">
+      <c r="G6" s="74">
         <v>14</v>
       </c>
-      <c r="I6" s="81">
-        <v>2</v>
-      </c>
-      <c r="J6" s="81">
-        <v>4</v>
-      </c>
-      <c r="K6" s="81">
+      <c r="I6" s="75">
+        <v>2</v>
+      </c>
+      <c r="J6" s="75">
+        <v>4</v>
+      </c>
+      <c r="K6" s="75">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="2:13" ht="30" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="107">
+      <c r="B7" s="94">
         <v>54</v>
       </c>
-      <c r="C7" s="108">
+      <c r="C7" s="95">
         <v>71</v>
       </c>
-      <c r="D7" s="104">
+      <c r="D7" s="91">
         <v>58</v>
       </c>
-      <c r="E7" s="102">
+      <c r="E7" s="89">
         <v>96</v>
       </c>
-      <c r="F7" s="101">
+      <c r="F7" s="74">
         <v>40</v>
       </c>
-      <c r="G7" s="101">
-        <v>3</v>
-      </c>
-      <c r="I7" s="81">
-        <v>1</v>
-      </c>
-      <c r="J7" s="81">
-        <v>2</v>
-      </c>
-      <c r="K7" s="81">
+      <c r="G7" s="74">
+        <v>3</v>
+      </c>
+      <c r="I7" s="75">
+        <v>1</v>
+      </c>
+      <c r="J7" s="75">
+        <v>2</v>
+      </c>
+      <c r="K7" s="75">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:13" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="103">
+      <c r="B8" s="90">
         <v>65</v>
       </c>
-      <c r="C8" s="103">
+      <c r="C8" s="90">
         <v>74</v>
       </c>
-      <c r="D8" s="103">
+      <c r="D8" s="90">
         <v>21</v>
       </c>
-      <c r="E8" s="101">
+      <c r="E8" s="74">
         <v>83</v>
       </c>
-      <c r="F8" s="101">
+      <c r="F8" s="74">
         <v>100</v>
       </c>
-      <c r="G8" s="101">
+      <c r="G8" s="74">
         <v>43</v>
       </c>
       <c r="I8" s="20" t="s">
@@ -17702,62 +17205,62 @@
       </c>
     </row>
     <row r="9" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="101">
+      <c r="B9" s="74">
         <v>57</v>
       </c>
-      <c r="C9" s="101">
+      <c r="C9" s="74">
         <v>35</v>
       </c>
-      <c r="D9" s="101">
+      <c r="D9" s="74">
         <v>58</v>
       </c>
-      <c r="E9" s="101">
+      <c r="E9" s="74">
         <v>70</v>
       </c>
-      <c r="F9" s="101">
-        <v>9</v>
-      </c>
-      <c r="G9" s="101">
+      <c r="F9" s="74">
+        <v>9</v>
+      </c>
+      <c r="G9" s="74">
         <v>79</v>
       </c>
-      <c r="I9" s="83">
-        <v>1</v>
-      </c>
-      <c r="J9" s="83">
+      <c r="I9" s="77">
+        <v>1</v>
+      </c>
+      <c r="J9" s="77">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="101">
+      <c r="B10" s="74">
         <v>67</v>
       </c>
-      <c r="C10" s="101">
+      <c r="C10" s="74">
         <v>63</v>
       </c>
-      <c r="D10" s="101">
+      <c r="D10" s="74">
         <v>84</v>
       </c>
-      <c r="E10" s="101">
+      <c r="E10" s="74">
         <v>55</v>
       </c>
-      <c r="F10" s="101">
+      <c r="F10" s="74">
         <v>60</v>
       </c>
-      <c r="G10" s="101">
+      <c r="G10" s="74">
         <v>14</v>
       </c>
-      <c r="I10" s="83">
-        <v>1</v>
-      </c>
-      <c r="J10" s="83">
-        <v>1</v>
-      </c>
-      <c r="K10" s="82"/>
+      <c r="I10" s="77">
+        <v>1</v>
+      </c>
+      <c r="J10" s="77">
+        <v>1</v>
+      </c>
+      <c r="K10" s="76"/>
     </row>
     <row r="11" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="I11" s="82"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="76"/>
+      <c r="K11" s="76"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B13" s="20" t="s">
@@ -17776,137 +17279,137 @@
       </c>
     </row>
     <row r="15" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="B15" s="80" cm="1">
+      <c r="B15" s="74" cm="1">
         <f t="array" ref="B15:E18">Convolveλ(ConvolutionMatrix,Kernel_1)</f>
         <v>1087</v>
       </c>
-      <c r="C15" s="80">
+      <c r="C15" s="74">
         <v>926</v>
       </c>
-      <c r="D15" s="80">
+      <c r="D15" s="74">
         <v>843</v>
       </c>
-      <c r="E15" s="80">
+      <c r="E15" s="74">
         <v>757</v>
       </c>
-      <c r="I15" s="84" cm="1">
+      <c r="I15" s="78" cm="1">
         <f t="array" ref="I15:M19">Convolveλ(ConvolutionMatrix,Kernel_2,_xleta.AVERAGE)</f>
         <v>76.25</v>
       </c>
-      <c r="J15" s="84">
+      <c r="J15" s="78">
         <v>70</v>
       </c>
-      <c r="K15" s="84">
+      <c r="K15" s="78">
         <v>40</v>
       </c>
-      <c r="L15" s="84">
+      <c r="L15" s="78">
         <v>46.25</v>
       </c>
-      <c r="M15" s="84">
+      <c r="M15" s="78">
         <v>42.5</v>
       </c>
     </row>
     <row r="16" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="B16" s="80">
+      <c r="B16" s="74">
         <v>990</v>
       </c>
-      <c r="C16" s="80">
+      <c r="C16" s="74">
         <v>968</v>
       </c>
-      <c r="D16" s="80">
+      <c r="D16" s="74">
         <v>1075</v>
       </c>
-      <c r="E16" s="80">
+      <c r="E16" s="74">
         <v>907</v>
       </c>
-      <c r="I16" s="84">
+      <c r="I16" s="78">
         <v>64.5</v>
       </c>
-      <c r="J16" s="84">
+      <c r="J16" s="78">
         <v>61</v>
       </c>
-      <c r="K16" s="84">
+      <c r="K16" s="78">
         <v>60.5</v>
       </c>
-      <c r="L16" s="84">
+      <c r="L16" s="78">
         <v>64</v>
       </c>
-      <c r="M16" s="84">
+      <c r="M16" s="78">
         <v>36.5</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="80">
+      <c r="B17" s="74">
         <v>907</v>
       </c>
-      <c r="C17" s="80">
+      <c r="C17" s="74">
         <v>902</v>
       </c>
-      <c r="D17" s="80">
+      <c r="D17" s="74">
         <v>1071</v>
       </c>
-      <c r="E17" s="80">
+      <c r="E17" s="74">
         <v>998</v>
       </c>
-      <c r="I17" s="84">
+      <c r="I17" s="78">
         <v>66</v>
       </c>
-      <c r="J17" s="84">
+      <c r="J17" s="78">
         <v>56</v>
       </c>
-      <c r="K17" s="84">
+      <c r="K17" s="78">
         <v>64.5</v>
       </c>
-      <c r="L17" s="84">
+      <c r="L17" s="78">
         <v>79.75</v>
       </c>
-      <c r="M17" s="84">
+      <c r="M17" s="78">
         <v>46.5</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="B18" s="80">
+      <c r="B18" s="74">
         <v>881</v>
       </c>
-      <c r="C18" s="80">
+      <c r="C18" s="74">
         <v>927</v>
       </c>
-      <c r="D18" s="80">
+      <c r="D18" s="74">
         <v>955</v>
       </c>
-      <c r="E18" s="80">
+      <c r="E18" s="74">
         <v>849</v>
       </c>
-      <c r="I18" s="84">
+      <c r="I18" s="78">
         <v>57.75</v>
       </c>
-      <c r="J18" s="84">
+      <c r="J18" s="78">
         <v>47</v>
       </c>
-      <c r="K18" s="84">
+      <c r="K18" s="78">
         <v>58</v>
       </c>
-      <c r="L18" s="84">
+      <c r="L18" s="78">
         <v>65.5</v>
       </c>
-      <c r="M18" s="84">
+      <c r="M18" s="78">
         <v>57.75</v>
       </c>
     </row>
     <row r="19" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="I19" s="84">
+      <c r="I19" s="78">
         <v>55.5</v>
       </c>
-      <c r="J19" s="84">
+      <c r="J19" s="78">
         <v>60</v>
       </c>
-      <c r="K19" s="84">
+      <c r="K19" s="78">
         <v>66.75</v>
       </c>
-      <c r="L19" s="84">
+      <c r="L19" s="78">
         <v>48.5</v>
       </c>
-      <c r="M19" s="84">
+      <c r="M19" s="78">
         <v>40.5</v>
       </c>
     </row>
@@ -17921,88 +17424,88 @@
       </c>
     </row>
     <row r="23" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="I23" s="84" cm="1">
+      <c r="I23" s="78" cm="1">
         <f t="array" ref="I23:M27">Convolveλ(ConvolutionMatrix,Kernel_2,_xleta.MAX)</f>
         <v>100</v>
       </c>
-      <c r="J23" s="84">
+      <c r="J23" s="78">
         <v>100</v>
       </c>
-      <c r="K23" s="84">
+      <c r="K23" s="78">
         <v>65</v>
       </c>
-      <c r="L23" s="84">
+      <c r="L23" s="78">
         <v>89</v>
       </c>
-      <c r="M23" s="84">
+      <c r="M23" s="78">
         <v>89</v>
       </c>
     </row>
     <row r="24" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="I24" s="84">
+      <c r="I24" s="78">
         <v>75</v>
       </c>
-      <c r="J24" s="84">
+      <c r="J24" s="78">
         <v>71</v>
       </c>
-      <c r="K24" s="84">
+      <c r="K24" s="78">
         <v>96</v>
       </c>
-      <c r="L24" s="84">
+      <c r="L24" s="78">
         <v>96</v>
       </c>
-      <c r="M24" s="84">
+      <c r="M24" s="78">
         <v>89</v>
       </c>
     </row>
     <row r="25" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="I25" s="84">
+      <c r="I25" s="78">
         <v>74</v>
       </c>
-      <c r="J25" s="84">
+      <c r="J25" s="78">
         <v>74</v>
       </c>
-      <c r="K25" s="84">
+      <c r="K25" s="78">
         <v>96</v>
       </c>
-      <c r="L25" s="84">
+      <c r="L25" s="78">
         <v>100</v>
       </c>
-      <c r="M25" s="84">
+      <c r="M25" s="78">
         <v>100</v>
       </c>
     </row>
     <row r="26" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="I26" s="84">
+      <c r="I26" s="78">
         <v>74</v>
       </c>
-      <c r="J26" s="84">
+      <c r="J26" s="78">
         <v>74</v>
       </c>
-      <c r="K26" s="84">
+      <c r="K26" s="78">
         <v>83</v>
       </c>
-      <c r="L26" s="84">
+      <c r="L26" s="78">
         <v>100</v>
       </c>
-      <c r="M26" s="84">
+      <c r="M26" s="78">
         <v>100</v>
       </c>
     </row>
     <row r="27" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="I27" s="84">
+      <c r="I27" s="78">
         <v>67</v>
       </c>
-      <c r="J27" s="84">
+      <c r="J27" s="78">
         <v>84</v>
       </c>
-      <c r="K27" s="84">
+      <c r="K27" s="78">
         <v>84</v>
       </c>
-      <c r="L27" s="84">
+      <c r="L27" s="78">
         <v>70</v>
       </c>
-      <c r="M27" s="84">
+      <c r="M27" s="78">
         <v>79</v>
       </c>
     </row>
@@ -18389,20 +17892,20 @@
         <v>120</v>
       </c>
       <c r="K15" s="36"/>
-      <c r="M15" s="113" t="e" cm="1" vm="10">
+      <c r="M15" s="100" t="e" cm="1" vm="10">
         <f t="array" ref="M15:Q19">Blocksλ(_xlfn.ANCHORARRAY(B3),2,2)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N15" s="113" t="e" vm="11">
+      <c r="N15" s="100" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
-      <c r="O15" s="113" t="e" vm="12">
+      <c r="O15" s="100" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
-      <c r="P15" s="113" t="e" vm="13">
+      <c r="P15" s="100" t="e" vm="13">
         <v>#VALUE!</v>
       </c>
-      <c r="Q15" s="113" t="e" vm="14">
+      <c r="Q15" s="100" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -18417,19 +17920,19 @@
       <c r="I16" s="36"/>
       <c r="J16" s="36"/>
       <c r="K16" s="36"/>
-      <c r="M16" s="113" t="e" vm="15">
+      <c r="M16" s="100" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
-      <c r="N16" s="113" t="e" vm="16">
+      <c r="N16" s="100" t="e" vm="16">
         <v>#VALUE!</v>
       </c>
-      <c r="O16" s="113" t="e" vm="17">
+      <c r="O16" s="100" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
-      <c r="P16" s="113" t="e" vm="18">
+      <c r="P16" s="100" t="e" vm="18">
         <v>#VALUE!</v>
       </c>
-      <c r="Q16" s="113" t="e" vm="19">
+      <c r="Q16" s="100" t="e" vm="19">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -18444,19 +17947,19 @@
       <c r="I17" s="36"/>
       <c r="J17" s="36"/>
       <c r="K17" s="36"/>
-      <c r="M17" s="113" t="e" vm="20">
+      <c r="M17" s="100" t="e" vm="20">
         <v>#VALUE!</v>
       </c>
-      <c r="N17" s="113" t="e" vm="21">
+      <c r="N17" s="100" t="e" vm="21">
         <v>#VALUE!</v>
       </c>
-      <c r="O17" s="113" t="e" vm="22">
+      <c r="O17" s="100" t="e" vm="22">
         <v>#VALUE!</v>
       </c>
-      <c r="P17" s="113" t="e" vm="23">
+      <c r="P17" s="100" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
-      <c r="Q17" s="113" t="e" vm="24">
+      <c r="Q17" s="100" t="e" vm="24">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -18471,19 +17974,19 @@
       <c r="I18" s="36"/>
       <c r="J18" s="36"/>
       <c r="K18" s="36"/>
-      <c r="M18" s="113" t="e" vm="25">
+      <c r="M18" s="100" t="e" vm="25">
         <v>#VALUE!</v>
       </c>
-      <c r="N18" s="113" t="e" vm="26">
+      <c r="N18" s="100" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
-      <c r="O18" s="113" t="e" vm="27">
+      <c r="O18" s="100" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
-      <c r="P18" s="113" t="e" vm="28">
+      <c r="P18" s="100" t="e" vm="28">
         <v>#VALUE!</v>
       </c>
-      <c r="Q18" s="113" t="e" vm="29">
+      <c r="Q18" s="100" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -18498,19 +18001,19 @@
       <c r="I19" s="36"/>
       <c r="J19" s="36"/>
       <c r="K19" s="36"/>
-      <c r="M19" s="113" t="e" vm="30">
+      <c r="M19" s="100" t="e" vm="30">
         <v>#VALUE!</v>
       </c>
-      <c r="N19" s="113" t="e" vm="31">
+      <c r="N19" s="100" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
-      <c r="O19" s="113" t="e" vm="32">
+      <c r="O19" s="100" t="e" vm="32">
         <v>#VALUE!</v>
       </c>
-      <c r="P19" s="113" t="e" vm="33">
+      <c r="P19" s="100" t="e" vm="33">
         <v>#VALUE!</v>
       </c>
-      <c r="Q19" s="113" t="e" vm="34">
+      <c r="Q19" s="100" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -18979,27 +18482,27 @@
       <c r="C19" s="45" t="e" vm="46">
         <v>#VALUE!</v>
       </c>
-      <c r="G19" s="113" t="e" cm="1" vm="47">
+      <c r="G19" s="100" t="e" cm="1" vm="47">
         <f t="array" ref="G19:H21">Windowedλ(Elevation,3,4)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H19" s="113" t="e" vm="48">
+      <c r="H19" s="100" t="e" vm="48">
         <v>#VALUE!</v>
       </c>
       <c r="I19" s="45"/>
       <c r="J19" s="45"/>
       <c r="K19" s="3"/>
-      <c r="L19" s="113" t="e" cm="1" vm="49">
+      <c r="L19" s="100" t="e" cm="1" vm="49">
         <f t="array" ref="L19:O22">Windowedλ(Elevation,2)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M19" s="113" t="e" vm="50">
+      <c r="M19" s="100" t="e" vm="50">
         <v>#VALUE!</v>
       </c>
-      <c r="N19" s="113" t="e" vm="51">
+      <c r="N19" s="100" t="e" vm="51">
         <v>#VALUE!</v>
       </c>
-      <c r="O19" s="113" t="e" vm="52">
+      <c r="O19" s="100" t="e" vm="52">
         <v>#VALUE!</v>
       </c>
       <c r="P19" s="3"/>
@@ -19011,25 +18514,25 @@
       <c r="C20" s="45" t="e" vm="54">
         <v>#VALUE!</v>
       </c>
-      <c r="G20" s="113" t="e" vm="55">
+      <c r="G20" s="100" t="e" vm="55">
         <v>#VALUE!</v>
       </c>
-      <c r="H20" s="113" t="e" vm="56">
+      <c r="H20" s="100" t="e" vm="56">
         <v>#VALUE!</v>
       </c>
       <c r="I20" s="45"/>
       <c r="J20" s="45"/>
       <c r="K20" s="3"/>
-      <c r="L20" s="113" t="e" vm="57">
+      <c r="L20" s="100" t="e" vm="57">
         <v>#VALUE!</v>
       </c>
-      <c r="M20" s="113" t="e" vm="58">
+      <c r="M20" s="100" t="e" vm="58">
         <v>#VALUE!</v>
       </c>
-      <c r="N20" s="113" t="e" vm="59">
+      <c r="N20" s="100" t="e" vm="59">
         <v>#VALUE!</v>
       </c>
-      <c r="O20" s="113" t="e" vm="60">
+      <c r="O20" s="100" t="e" vm="60">
         <v>#VALUE!</v>
       </c>
       <c r="P20" s="3"/>
@@ -19037,25 +18540,25 @@
     <row r="21" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
-      <c r="G21" s="113" t="e" vm="61">
+      <c r="G21" s="100" t="e" vm="61">
         <v>#VALUE!</v>
       </c>
-      <c r="H21" s="113" t="e" vm="62">
+      <c r="H21" s="100" t="e" vm="62">
         <v>#VALUE!</v>
       </c>
       <c r="I21" s="45"/>
       <c r="J21" s="45"/>
       <c r="K21" s="3"/>
-      <c r="L21" s="113" t="e" vm="63">
+      <c r="L21" s="100" t="e" vm="63">
         <v>#VALUE!</v>
       </c>
-      <c r="M21" s="113" t="e" vm="64">
+      <c r="M21" s="100" t="e" vm="64">
         <v>#VALUE!</v>
       </c>
-      <c r="N21" s="113" t="e" vm="65">
+      <c r="N21" s="100" t="e" vm="65">
         <v>#VALUE!</v>
       </c>
-      <c r="O21" s="113" t="e" vm="66">
+      <c r="O21" s="100" t="e" vm="66">
         <v>#VALUE!</v>
       </c>
       <c r="P21" s="3"/>
@@ -19068,16 +18571,16 @@
       <c r="I22" s="45"/>
       <c r="J22" s="45"/>
       <c r="K22" s="3"/>
-      <c r="L22" s="113" t="e" vm="67">
+      <c r="L22" s="100" t="e" vm="67">
         <v>#VALUE!</v>
       </c>
-      <c r="M22" s="113" t="e" vm="68">
+      <c r="M22" s="100" t="e" vm="68">
         <v>#VALUE!</v>
       </c>
-      <c r="N22" s="113" t="e" vm="69">
+      <c r="N22" s="100" t="e" vm="69">
         <v>#VALUE!</v>
       </c>
-      <c r="O22" s="113" t="e" vm="70">
+      <c r="O22" s="100" t="e" vm="70">
         <v>#VALUE!</v>
       </c>
       <c r="P22" s="3"/>
@@ -19151,7 +18654,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuACAAIABfAF8AXwBfACAAIAAgACAAXwAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAF8AXwBfAF8AIAAgACAAIAAgACAAIAAgACAAIAAgAF8AIAAgACAAXwAgACAAIABfACAAXABuACAAfAAgACAAXwAgAFwAXAAgACAAKABfACkAIAAgACAAIAAgACAAIAAgACAAIAAvACAAXwBfAF8AXwB8ACAAIAAgACAAIAAgACAAIAAgACgAXwApACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAfABfACkAIAB8ACAAIABfACAAIAAgACAAXwBfACAAXwAgACAAfAAgACgAXwBfAF8AIAAgACAAIABfACAAXwBfACAAIAAgACAAXwAgACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAIABfACAAPAAgACAAfAAgAHwAIAAgAC8AIABfAGAAIAB8ACAAIABcAFwAXwBfAF8AIABcAFwAIAAgAHwAIAAnAF8AIABcAFwAIAAgAHwAIAB8ACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAfABfACkAIAB8ACAAfAAgAHwAIAB8ACAAKABfAHwAIAB8ACAAIABfAF8AXwBfACkAIAB8ACAAfAAgAHwAXwApACAAfAAgAHwAIAB8ACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8AF8AXwBfAF8ALwAgACAAfABfAHwAIAAgAFwAXABfAF8ALAAgAHwAIAB8AF8AXwBfAF8AXwAvACAAIAB8ACAALgBfAF8ALwAgACAAfABfAHwAIAB8AF8AfAAgAHwAXwB8AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAF8ALwAgAHwAIAAgACAAIAAgACAAIAAgACAAIAB8ACAAfAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAfABfAF8AXwAvACAAIAAgACAAIAAgACAAIAAgACAAIAB8AF8AfAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgBcAG4ATQBvAGQAdQBsAGUAOgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEIAaQBnAFMAcABpAGwAbAAgAEEATABQAEgAQQBcAG4ATABpAGMAZQBuAHMAZQA6ACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBUACAAKABzAGUAZQAgAEwASQBDAEUATgBTAEUAIABmAGkAbABlACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBEAGEAdABlADoAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQAwAC8ANgAvADIAMAAyADYAXABuAFwAbgBHAGkAcwB0ACAAKABJAG0AcABvAHIAdAAgAG8AbgBsAHkAKQA6ACAAaAB0AHQAcABzADoALwAvAGcAaQBzAHQALgBnAGkAdABoAHUAYgAuAGMAbwBtAC8AUABhAHQAcgBpAGMAawAyADcAOAA4AC8AYQAxADIANgA1ADAANABmADkAYQAzAGYANABjADkAZgBhAGQAOAA3ADEANQBjAGEAMgA1ADgANwAzADAANgBlAFwAbgBcAG4AQQAgAGMAbwBsAGwAZQBjAHQAaQBvAG4AIABvAGYAIABCAGkAZwBTAHAAaQBsAGwAIABmAHUAbgBjAHQAaQBvAG4AcwAgAHIAZQB2AGkAcwBlAGQAIAB0AG8AIABsAGUAdgBlAHIAYQBnAGUAIABzAHUAcABwAG8AcgB0ACAAbwBmACAAbgBlAHMAdABlAGQAIABhAHIAcgBhAHkAcwAuAFwAbgBUAGgAZQBzAGUAIABhAHIAZQAgAHcAbwByAGsAaQBuAGcAIABwAHIAbwB0AG8AdAB5AHAAZQBzACAAYQBuAGQAIABzAGgAbwB1AGwAZAAgAG4AbwB0ACAAYgBlACAAYwBvAG4AcwBpAGQAZQByAGUAZAAgAGYAaQBuAGEAbAAuAFwAbgBcAG4AfAAgAFMAaQBtAHAAbABpAGYAaQBlAGQAIABmAHUAbgBjAHQAaQBvAG4AcwAgAHwAXABuAFwAbgBNAGEAZwBuAGkAZgB5ALsDIAAgACAAIAAtACAARQB4AHAAYQBuAGQAcwAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAaQBuAHQAbwAgAGEAIABkAGUAcAB0AGgA1wB3AGkAZAB0AGgAIABiAGwAbwBjAGsALgBcAG4AXABuAEEAbABpAGcAbgBSAG8AdwBzALsDIAAgAC0AIABTAG8AcgB0AHMAIABlAGEAYwBoACAAcgBvAHcAIABhAGwAcABoAGEAYgBlAHQAaQBjAGEAbABsAHkAIABvAHIAIABiAHkAIABzAG8AcgB0ACAAbwByAGQAZQByAC4AIABSAGUAdgBpAHMAZQBkACAAQQBsAGkAZwBuALsDLgBcAG4AXABuAEEAbABpAGcAbgBDAG8AbABzALsDIAAgAC0AIABTAG8AcgB0AHMAIABlAGEAYwBoACAAYwBvAGwAdQBtAG4AIABhAGwAcABoAGEAYgBlAHQAaQBjAGEAbABsAHkAIABvAHIAIABiAHkAIABzAG8AcgB0ACAAbwByAGQAZQByAC4AIABSAGUAdgBpAHMAZQBkACAAQQBsAGkAZwBuALsDLgBcAG4AXABuAEYAbwBsAGQAuwMgACAAIAAgACAAIAAgAC0AIABHAHIAbwB1AHAAcwAgAGkAZABlAG4AdABpAGMAYQBsACAAcgBvAHcAcwAgAGEAbgBkACAAYQBwAHAAbABpAGUAcwAgAGEAbgAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAHIAZQBkAHUAYwBlAHIALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYAYQBzAHQAZQByACAAdgBpAGEAIABzAGkAbQBwAGwAaQBmAGkAZQBkACAAQQBsAGkAZwBuAFIAbwB3AHMAuwMuAFwAbgBcAG4AWgBpAHAAuwMgACAAIAAgACAAIAAgACAALQAgAFoAaQBwAHMAIAAxABMgNAAgAGEAcgByAGEAeQBzACAAaQBuAHQAbwAgAHIAbwB3ABEgcgBlAGMAbwByAGQAcwAuACAATgBvAHcAIAByAGUAdAB1AHIAbgBzACAAYQAgAGwAaQBzAHQALgBcAG4AXABuAFAAYQBpAHIAdwBpAHMAZQC7AyAAIAAgAC0AIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAYQBpAHIAaQBuAGcAIABvAGYAIAB0AHcAbwAgAGkAbgBwAHUAdABzAC4AXABuAFwAbgBUAHIAaQBwAGwAZQB3AGkAcwBlALsDIAAtACAAQwBhAHIAdABlAHMAaQBhAG4AIABwAHIAbwBkAHUAYwB0ACAAbwBmACAAMwAgAHMAZQB0AHMALgBcAG4AXABuAFEAdQBhAGQAdwBpAHMAZQC7AyAAIAAgAC0AIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAcgBvAGQAdQBjAHQAIABvAGYAIAA0ACAAcwBlAHQAcwAuAFwAbgBcAG4ARQBjAGgAbwC7AyAAIAAgACAAIAAgACAALQAgAFIAZQBwAGUAYQB0AHMAIABlAGEAYwBoACAAZQBsAGUAbQBlAG4AdAAgAGEAYwBjAG8AcgBkAGkAbgBnACAAdABvACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAuAFwAbgBcAG4AQwBvAG4AdgBvAGwAdgBlALsDIAAgACAALQAgAFMAbABpAGQAaQBuAGcAESB3AGkAbgBkAG8AdwAgAGMAbwBuAHYAbwBsAHUAdABpAG8AbgAgAHUAcwBpAG4AZwAgAGEAIAByAGUAZAB1AGMAZQByAC4AXABuAFwAbgB8ACAATgBlAHcAIABwAHIAbwB0AG8AdAB5AHAAZQBzACAAfABcAG4AXABuAEIAbABvAGMAawBzALsDIAAgACAAIAAgAC0AIABQAGEAcgB0AGkAdABpAG8AbgBzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABkAGUAcAB0AGgA1wB3AGkAZAB0AGgAIABiAGwAbwBjAGsAcwAuAFwAbgBcAG4AVwBpAG4AZABvAHcAZQBkALsDIAAgACAALQAgAEUAeAB0AHIAYQBjAHQAcwAgAG8AdgBlAHIAbABhAHAAcABpAG4AZwAgAGQAZQBwAHQAaADXAHcAaQBkAHQAaAAgAHcAaQBuAGQAbwB3AHMALgBcAG4AXABuAEcAcgBpAGQATABvAG8AawB1AHAAuwMgAC0AIAAyAEQAIABsAG8AbwBrAHUAcAAgAHIAZQB0AHUAcgBuAGkAbgBnACAAYwBvAHIAcgBlAHMAcABvAG4AZABpAG4AZwAgAHYAYQBsAHUAZQBzACAAZgByAG8AbQAgAGEAIABzAGUAYwBvAG4AZAAgAGcAcgBpAGQALgBcAG4AXABuAE4AYQB2AGkAZwBhAHQAZQAyAEQAuwMgAC0AIABMAG8AYwBhAHQAZQBzACAAYQAgAGsAZQByAG4AZQBsACAAaQBuACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGEAbgBkACAAcgBlAHQAdQByAG4AcwAgAGEAIABNAG8AbwByAGUAESBuAGUAaQBnAGgAYgBvAHIAaABvAG8AZAAgAHMAaABhAHAAZQAuAFwAbgBcAG4ATQBhAHQAYwBoADIARAC7AyAAIAAgACAALQAgAEwAbwBjAGEAdABlAHMAIABhACAAawBlAHIAbgBlAGwAIABpAG4AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYQBuAGQAIAByAGUAdAB1AHIAbgBzACAAbQBhAHQAYwBoACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzAC4AXABuAFwAbgBWAFMAcABsAGkAdAC7AyAAIAAgACAAIAAtACAAUwBwAGwAaQB0AHMAIABhACAAMgBEACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAHYAZQByAHQAaQBjAGEAbAAgAHIAbwB3ABEgcwBlAGcAbQBlAG4AdABzACAAbwBmACAAcwBpAHoAZQAgAHMAcABsAGkAdABfAGkAbgB0AGUAcgB2AGEAbAAuAFwAbgBcAG4ASABTAHAAbABpAHQAuwMgACAAIAAgACAALQAgAFMAcABsAGkAdABzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABoAG8AcgBpAHoAbwBuAHQAYQBsACAAYwBvAGwAdQBtAG4AESBzAGUAZwBtAGUAbgB0AHMAIABvAGYAIABzAGkAegBlACAAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsAC4AXABuAFwAbgBcAG4AVQBuAGMAaABhAG4AZwBlAGQAIABmAHUAbgBjAHQAaQBvAG4AcwAuACAAQwBhAGwAbABlAGQAIABiAHkAIABzAG8AbQBlACAAbwBmACAAdABoAGUAIABhAGIAbwB2AGUAIABmAHUAbgBjAHQAaQBvAG4AcwAuAFwAbgAiICAATQBHAHIAaQBkALsDXABuACIgIABSAGUAcABlAGEAdABSAG8AdwBzALsDXABuACIgIABSAGUAcABlAGEAdABDAG8AbABzALsDXABuACIgIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4AXABuAC8AKgBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABNAGEAZwBuAGkAZgB5ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABUAEIARABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIABBAGwAcABoAGEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAcABhAG4AZABzACAAZQBhAGMAaAAgAGUAbABlAG0AZQBuAHQAIABvAGYAIABhAG4AIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIABpAG4AdABvACAAYQAgAGIAbABvAGMAawAgAG8AZgAgAHMAcABlAGMAaQBmAGkAZQBkACAAaABlAGkAZwBoAHQAIABhAG4AZABcAG4AIAAgACAAIAB3AGkAZAB0AGgAIAB1AHMAaQBuAGcAIABuAGUAYQByAGUAcwB0ABEgbgBlAGkAZwBoAGIAbwByACAAaQBuAHQAZQByAHAAbwBsAGEAdABpAG8AbgAuACAAUwB1AHAAcABvAHIAdABzACAAcwBjAGEAbABhAHIAcwAsACAAMQBEACAAYQByAHIAYQB5AHMALAAgAGEAbgBkAFwAbgAgACAAIAAgADIARAAgAGEAcgByAGEAeQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAALQAgAEkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAHQAbwAgAG0AYQBnAG4AaQBmAHkALgBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAgACAAIAAgACAAIAAtACAATgB1AG0AYgBlAHIAIABvAGYAIAByAG8AdwBzACAAZgBvAHIAIABlAGEAYwBoACAAbQBhAGcAbgBpAGYAaQBlAGQAIABlAGwAZQBtAGUAbgB0ACAAKABwAG8AcwBpAHQAaQB2AGUAIABzAGMAYQBsAGEAcgApAC4AXABuACAAIAAgACAAdwBpAGQAdABoACAAIAAgACAAIAAgACAALQAgAE4AdQBtAGIAZQByACAAbwBmACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAG0AYQBnAG4AaQBmAGkAZQBkACAAZQBsAGUAbQBlAG4AdAAgACgAcABvAHMAaQB0AGkAdgBlACAAcwBjAGEAbABhAHIAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAGgAZQBpAGcAaAB0ACAAYQBuAGQAIAB3AGkAZAB0AGgAIABtAHUAcwB0ACAAYgBlACAAcwBjAGEAbABhAHIALAAgAG4AdQBtAGUAcgBpAGMALAAgAGEAbgBkACAAPgAgADAALgBcAG4AIAAgACAAIAAiICAAVQBzAGUAcwAgAG4AZQBhAHIAZQBzAHQAESBuAGUAaQBnAGgAYgBvAHIAIABlAHgAcABhAG4AcwBpAG8AbgAgAHYAaQBhACAAaQBuAGQAZQB4ACAAcgBlAHAAbABpAGMAYQB0AGkAbwBuAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAE0AYQBnAG4AaQBmAHkAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAaABlAGkAZwBoAHQALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuAEkARgAoAE8AUgAoAEMATwBVAE4AVAAoAGgAZQBpAGcAaAB0ACkAIAA8AD4AIAAxACwAIABDAE8AVQBOAFQAKAB3AGkAZAB0AGgAKQAgADwAPgAgADEAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAGgAZQBpAGcAaAB0ACkALAAgAEkAUwBUAEUAWABUACgAdwBpAGQAdABoACkAKQAsAFwAIgAjAFQARQBYAFQAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABoAGUAaQBnAGgAdAAgADwAPQAgADAALAAgAHcAaQBkAHQAaAAgADwAPQAgADAAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABOAGUAYQByAGUAcwB0ACAAbgBlAGkAZwBoAGIAbwByACAAaQBuAHQAZQByAHAAbwBsAGEAdABpAG8AbgBcAG4AIAAgACAAIABtAGEAZwC7AywAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABlAGwAZQBtAGUAbgB0ACwARQBYAFAAQQBOAEQAKABlAGwAZQBtAGUAbgB0ACwAaABlAGkAZwBoAHQALAB3AGkAZAB0AGgALABlAGwAZQBtAGUAbgB0ACkAKQAsAFwAbgAgACAAIAAgAG0AYQBnAG4AaQBmAGkAZQBkACwAIABGAEwAQQBUAFQARQBOACgATQBBAFAAKABhAHIAcgBhAHkALABtAGEAZwC7AykAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAG0AYQBnAG4AaQBmAGkAZQBkAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABBAGwAaQBnAG4AUgBvAHcAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAQQBsAHAAaABhAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUwBvAHIAdABzACAAZQBhAGMAaAAgAHIAbwB3ACAAYQBsAHAAaABhAGIAZQB0AGkAYwBhAGwAbAB5ACAAKABkAGUAZgBhAHUAbAB0ACkAIABvAHIAIABiAHkAIAB0AGgAZQAgAHMAcABlAGMAaQBmAGkAZQBkACAAcwBvAHIAdAAgAG8AcgBkAGUAcgAuAFwAbgAgACAAIAAgAFMAbwByAHQAaQBuAGcAIABpAHMAIABsAGUAeABpAGMAbwBnAHIAYQBwAGgAaQBjACAAYQBuAGQAIABjAGEAcwBlABEgcwBlAG4AcwBpAHQAaQB2AGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABiAGUAIABhAGwAaQBnAG4AZQBkAC4AXABuACAAIAAgACAAWwBzAG8AcgB0AF8AbwByAGQAZQByAF0AIAAtACAAMQAgACgAQQBzAGMAZQBuAGQAaQBuAGcAKQAsACAALQAxACAAKABEAGUAcwBjAGUAbgBkAGkAbgBnACkALgAgAEQAZQBmAGEAdQBsAHQAIAA9ACAAMQAuAFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQQBsAGkAZwBuAFIAbwB3AHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBzAG8AcgB0AF8AbwByAGQAZQByAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIABzAG8AcgB0AF8AbwByAGQAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHMAbwByAHQAXwBvAHIAZABlAHIAKQAsACAAMQAsACAAcwBvAHIAdABfAG8AcgBkAGUAcgApACwAXABuACAAIAAgACAAcwBvAHIAdABlAGQALAAgACAAIAAgACAARgBMAEEAVABUAEUATgAoAEIAWQBSAE8AVwAoAGEAcgByAGEAeQAsACAATABBAE0AQgBEAEEAKAByAG8AdwAsACAAUwBPAFIAVAAoAHIAbwB3ACwALABzAG8AcgB0AF8AbwByAGQAZQByACwAVABSAFUARQApACkAKQApACwAXABuACAAIAAgACAAcwBvAHIAdABlAGQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABBAGwAaQBnAG4AQwBvAGwAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAQQBsAHAAaABhAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUwBvAHIAdABzACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAYQBsAHAAaABhAGIAZQB0AGkAYwBhAGwAbAB5ACAAKABkAGUAZgBhAHUAbAB0ACkAIABvAHIAIABiAHkAIAB0AGgAZQAgAHMAcABlAGMAaQBmAGkAZQBkACAAcwBvAHIAdAAgAG8AcgBkAGUAcgAuAFwAbgAgACAAIAAgAFMAbwByAHQAaQBuAGcAIABpAHMAIABsAGUAeABpAGMAbwBnAHIAYQBwAGgAaQBjACAAYQBuAGQAIABjAGEAcwBlABEgcwBlAG4AcwBpAHQAaQB2AGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABiAGUAIABhAGwAaQBnAG4AZQBkAC4AXABuACAAIAAgACAAWwBzAG8AcgB0AF8AbwByAGQAZQByAF0AIAAtACAAMQAgACgAQQBzAGMAZQBuAGQAaQBuAGcAKQAsACAALQAxACAAKABEAGUAcwBjAGUAbgBkAGkAbgBnACkALgAgAEQAZQBmAGEAdQBsAHQAIAA9ACAAMQAuAFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQQBsAGkAZwBuAEMAbwBsAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBzAG8AcgB0AF8AbwByAGQAZQByAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIABzAG8AcgB0AF8AbwByAGQAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHMAbwByAHQAXwBvAHIAZABlAHIAKQAsACAAMQAsACAAcwBvAHIAdABfAG8AcgBkAGUAcgApACwAXABuACAAIAAgACAAcwBvAHIAdABlAGQALAAgACAAIAAgACAARgBMAEEAVABUAEUATgAoAEIAWQBDAE8ATAAoAGEAcgByAGEAeQAsACAATABBAE0AQgBEAEEAKABjAG8AbAAsACAAUwBPAFIAVAAoAGMAbwBsACwALABzAG8AcgB0AF8AbwByAGQAZQByACkAKQApACkALABcAG4AIAAgACAAIABzAG8AcgB0AGUAZABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAQgBEAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARgBvAGwAZAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAQQBsAHAAaABhAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAAQQBsAGkAZwBuAFIAbwB3AHMAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBkAHUAYwBlAHMAIAByAGUAYwBvAHIAZABzACAAaQBuACAAYQBuACAAYQByAHIAYQB5ACAAYgB5ACAAZwByAG8AdQBwAGkAbgBnACAAaQBkAGUAbgB0AGkAYwBhAGwAIAByAG8AdwBzACAAYQBuAGQAIABhAHAAcABsAHkAaQBuAGcAIABhAG4AXABuACAAIAAgACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAZgB1AG4AYwB0AGkAbwBuACAAdABvACAAdABoAGUAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAZQBuAHQAcgBpAGUAcwAgAGkAbgAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5AC4AXABuAFwAbgAgACAAIAAgAEkAZgAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5ACAAaQBzACAAbwBtAGkAdAB0AGUAZAAsACAARgBvAGwAZAC7AyAAdQBzAGUAcwAgAHQAaABlACAAZgBpAHIAcwB0ACAAZgBpAGUAbABkACAAbwBmACAAZQBhAGMAaAAgAHIAZQBjAG8AcgBkACAAYQBzAFwAbgAgACAAIAAgAHQAaABlACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAdgBlAGMAdABvAHIALgAgAFQAaABpAHMAIABtAG8AZABlACAAaQBzACAAaQBuAHQAZQBuAGQAZQBkACAAZgBvAHIAIABDAE8AVQBOAFQAQQA7ACAAbwB0AGgAZQByACAAcgBlAGQAdQBjAGUAcgBzAFwAbgAgACAAIAAgAG0AYQB5ACAAcAByAG8AZAB1AGMAZQAgAHIAZQBzAHUAbAB0AHMAIABiAHUAdAAgAGEAcgBlACAAbgBvAHQAIABtAGUAYQBuAGkAbgBnAGYAdQBsAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAcgBvAHcAcwAgAGQAZQBmAGkAbgBlACAAZwByAG8AdQBwAGkAbgBnACAAawBlAHkAcwAuAFwAbgAgACAAIAAgAFsAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAG8AZgAgAHYAYQBsAHUAZQBzACAAdABvACAAYQBnAGcAcgBlAGcAYQB0AGUALgBcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACAAIAAgACAAIAAgAC0AIABSAGUAZAB1AGMAZQByACAATABBAE0AQgBEAEEAIABhAGMAYwBlAHAAdABpAG4AZwAgAGEAIAAxAEQAIAB2AGUAYwB0AG8AcgAgACgAZABlAGYAYQB1AGwAdAAgAD0AIABDAE8AVQBOAFQAQQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARgBvAGwAZAC7AyAAaABhAGwAdABzACAAdwBpAHQAaAAgACMAVgBBAEwAVQBFACEAIABpAGYAIABhAHIAcgBhAHkAIABhAG4AZAAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5ACAAaABlAGkAZwBoAHQAcwAgAGQAaQBmAGYAZQByAC4AXABuACAAIAAgACAAIiAgAEYAbwBsAGQAuwMgAGgAYQBsAHQAcwAgAHcAaQB0AGgAIAAjAEYAVQBOAEMAVABJAE8ATgAhACAAaQBmACAAcgBlAGQAdQBjAGUAcgAgAGkAcwAgAG4AbwB0ACAAYQAgAHYAYQBsAGkAZAAgAEwAQQBNAEIARABBAC4AXABuACAAIAAgACAAIiAgAEEAbABpAGcAbgBSAG8AdwBzALsDIABjAGEAbgBvAG4AaQBjAGEAbABpAHoAZQBzACAAcgBlAGMAbwByAGQAcwAgAHMAbwAgAGkAZABlAG4AdABpAGMAYQBsACAAcgBvAHcAcwAgAGcAcgBvAHUAcAAgAGMAbABlAGEAbgBsAHkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARgBvAGwAZAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5AF0ALABcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIAB2AGEAbAB1AGUAcwAgAGEAcgByAGEAeQBcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQApACwAIABUAEEASwBFACgAYQByAHIAYQB5ACwALAAxACkALAAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAYQB1AGwAdAAgAHIAZQBkAHUAYwBlAHIAXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACwAIAAgACAAIAAgAEkARgAoAE8AUgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgB1AG4AYwB0AGkAbwBuACkALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAKQApACwAIABDAE8AVQBOAFQAQQAsACAAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAEYAKABBAE4ARAAoAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAgADwAPgAgAFIATwBXAFMAKAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQApACkALAAgAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAIABcACIAIwBGAFUATgBDAFQASQBPAE4AIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAQwBhAG4AbwBuAGkAYwBhAGwAIABnAHIAbwB1AHAAaQBuAGcAIABrAGUAeQBzAFwAbgAgACAAIAAgAGEAbABpAGcAbgBlAGQALAAgAEEAbABpAGcAbgBSAG8AdwBzALsDKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAGcAZwByAGUAZwBhAHQAaQBvAG4AXABuACAAIAAgACAAYQBnAGcALAAgACAAIAAgAEcAUgBPAFUAUABCAFkAKABhAGwAaQBnAG4AZQBkACwAIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAsACAAZgB1AG4AYwB0AGkAbwBuACwALAAwACkALABcAG4AXABuACAAIAAgACAAYQBnAGcAXABuACkAKQApACkAXABuACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEEAUgAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABaAGkAcAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIABBAGwAcABoAGEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABaAGkAcABzACAAdABvAGcAZQB0AGgAZQByACAAMQAtADQAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABhACAAbABpAHMAdAAgAG8AZgAgAHIAbwB3ABEgcgBlAGMAbwByAGQAcwAuACAARQBhAGMAaAAgAGkAbgBwAHUAdAAgAGkAcwAgAGYAaQByAHMAdABcAG4AIAAgACAAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAdwBpAHQAaAAgAFQATwBDAE8ATAAgAHMAbwAgAHQAaABhAHQAIABzAGMAYQBsAGEAcgBzACwAIAAxAEQAIABhAHIAcgBhAHkAcwAsACAAYQBuAGQAIAAyAEQAIABhAHIAcgBhAHkAcwAgAGIAZQBoAGEAdgBlAFwAbgAgACAAIAAgAHUAbgBpAGYAbwByAG0AbAB5AC4AIABaAGkAcAC7AyAAdABoAGUAbgAgAGEAbABpAGcAbgBzACAAdABoAGUAIABpAG4AcAB1AHQAcwAgAGIAeQAgAGwAZQBuAGcAdABoACAAYQBuAGQAIABjAG8AbgBzAHQAcgB1AGMAdABzACAAbwBuAGUAIAByAGUAYwBvAHIAZABcAG4AIAAgACAAIABwAGUAcgAgAHIAbwB3ACAAdQBzAGkAbgBnACAAQgBZAFIATwBXAC4AXABuAFwAbgAgACAAIAAgAEkAbgAgAHMAdAByAGkAYwB0ACAAbQBvAGQAZQAgACgAZABlAGYAYQB1AGwAdAApACwAIABaAGkAcAC7AyAAcABhAGkAcgBzACAAZQBsAGUAbQBlAG4AdABzACAAbwBuAGwAeQAgAHUAcAAgAHQAbwAgAHQAaABlACAAbABlAG4AZwB0AGgAIABvAGYAIAB0AGgAZQBcAG4AIAAgACAAIABzAGgAbwByAHQAZQBzAHQAIABhAHIAcgBhAHkALgAgAEkAZgAgAHoAaQBwAF8AbABvAG4AZwBlAHMAdAAgAD0AIABUAFIAVQBFACwAIABaAGkAcAC7AyAAYwBvAG4AdABpAG4AdQBlAHMAIAB1AG4AdABpAGwAIAB0AGgAZQAgAGwAbwBuAGcAZQBzAHQAXABuACAAIAAgACAAYQByAHIAYQB5ACAAaQBzACAAYwBvAG4AcwB1AG0AZQBkACwAIABwAGEAZABkAGkAbgBnACAAcwBoAG8AcgB0AGUAcgAgAGEAcgByAGEAeQBzACAAdwBpAHQAaAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAIAAoAGQAZQBmAGEAdQBsAHQAOgAgACMATgAvAEEAKQAuAFwAbgBcAG4AIAAgACAAIABUAGgAZQAgAHIAZQBzAHUAbAB0ACAAaQBzACAAYQAgAGwAaQBzAHQAIABvAGYAIAByAGUAYwBvAHIAZABzACAAbwBmACAAdABoAGUAIABmAG8AcgBtADoAXABuACAAIAAgACAAIAAgACAAIAB7ACAAewBhAIEgLABiAIEgLABjAIEgLABkAIEgfQAsACAAewBhAIIgLABiAIIgLABjAIIgLABkAIIgfQAsACAAJiAgAH0AXABuACAAIAAgACAAVQBzAGUAIABGAEwAQQBUAFQARQBOACAAdABvACAAcwBwAGkAbABsACAAdABoAGUAIABsAGkAcwB0ACAAYQBzACAAYQAgADIARAAgAHQAYQBiAGwAZQAgAHcAaABlAG4AIAByAGUAcQB1AGkAcgBlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAxACAAIAAgACAAIAAgACAALQAgAEYAaQByAHMAdAAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgACgAcwBjAGEAbABhAHIALAAgADEARAAsACAAbwByACAAMgBEACkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADIAXQAgACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHMAZQBjAG8AbgBkACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwAzAF0AIAAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAB0AGgAaQByAGQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADQAXQAgACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAbwB1AHIAdABoACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwB6AGkAcABfAGwAbwBuAGcAZQBzAHQAXQAgAC0AIABUAFIAVQBFACAAdABvACAAegBpAHAAIAB1AG4AdABpAGwAIAB0AGgAZQAgAGwAbwBuAGcAZQBzAHQAIABhAHIAcgBhAHkAIABpAHMAIABjAG8AbgBzAHUAbQBlAGQALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAZgAgAG8AbQBpAHQAdABlAGQALAAgAFoAaQBwALsDIAB1AHMAZQBzACAAcwB0AHIAaQBjAHQAIABtAG8AZABlACAAKABzAGgAbwByAHQAZQBzAHQAIABhAHIAcgBhAHkAKQAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACAAIAAtACAAVgBhAGwAdQBlACAAdQBzAGUAZAAgAHQAbwAgAHAAYQBkACAAcwBoAG8AcgB0AGUAcgAgAGEAcgByAGEAeQBzACAAdwBoAGUAbgAgAHoAaQBwAF8AbABvAG4AZwBlAHMAdAAgAD0AIABUAFIAVQBFAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQQBsAGwAIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUAIAB1AHMAaQBuAGcAIABUAE8AQwBPAEwALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABpAHMAIABhACAAbABpAHMAdAAgAG8AZgAgAHMAdAByAHUAYwB0AHUAcgBlAGQAIAByAGUAYwBvAHIAZABzACwAIABuAG8AdAAgAGEAIABzAHAAaQBsAGwAZQBkACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAIiAgAEEAcABwAGwAeQAgAEYATABBAFQAVABFAE4AKAB6AGkAcABwAGUAZAApACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAHQAaABlACAAbABpAHMAdAAgAHQAbwAgAGEAIAAyAEQAIAB0AGEAYgBsAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AWgBpAHAAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAsAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMgBdACwAXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwAzAF0ALABcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADQAXQAsAFwAbgAgACAAIAAgAFsAegBpAHAAXwBsAG8AbgBnAGUAcwB0AF0ALABcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGUAdAAgAHoAaQBwACAAbQBvAGQAZQBcAG4AIAAgACAAIABaAGkAcABMAG8AbgBnAD8ALAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHoAaQBwAF8AbABvAG4AZwBlAHMAdAApACwAIABGAEEATABTAEUALAAgAHoAaQBwAF8AbABvAG4AZwBlAHMAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAdQBuAGMAdABpAG8AbgAgAGYAbwByACAAZABlAHQAZQByAG0AaQBuAGkAbgBnACAAegBpAHAAIABsAGUAbgBnAHQAaABcAG4AIAAgACAAIABmAG4AuwMsACAAIAAgACAAIAAgACAAIABJAEYAKABaAGkAcABMAG8AbgBnAD8ALAAgAE0AQQBYACwAIABNAEkATgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAaQBsAGwAIAB2AGEAbAB1AGUAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAsACAASQBGACgAWgBpAHAATABvAG4AZwA/ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAE4AQQAoACkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AQQAoACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHIAcgBhAHkAcwAgAHMAdQBwAHAAbABpAGUAZABcAG4AIAAgACAAIABUAHcAbwAsACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwAyACkAKQAsAFwAbgAgACAAIAAgAFQAaAByAGUAZQAsACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGEAcgByAGEAeQBfADMAKQApACwAXABuACAAIAAgACAARgBvAHUAcgAsACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8ANAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAHQAYQBsACAAYQByAHIAYQB5AHMAIABzAHUAcABwAGwAaQBlAGQAXABuACAAIAAgACAAbQAsACAASQBGACgARgBvAHUAcgAsACAANAAsAFwAbgAgACAAIAAgACAAIAAgACAAIABJAEYAKABUAGgAcgBlAGUALAAgADMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAVAB3AG8ALAAgADIALAAgADEAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADEALAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIALAAgAEkARgAoAG0AIAA+AD0AIAAyACwAIABUAE8AQwBPAEwAKABhAHIAcgBhAHkAXwAyACkALAAgAEYAQQBMAFMARQApACwAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMwAsACAASQBGACgAbQAgAD4APQAgADMALAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQBfADMAKQAsACAARgBBAEwAUwBFACkALABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwA0ACwAIABJAEYAKABtACAAPQAgACAANAAsACAAVABPAEMATwBMACgAYQByAHIAYQB5AF8ANAApACwAIABGAEEATABTAEUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAGUAbgBnAHQAaABzAFwAbgAgACAAIAAgAGsAgSAsACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADEAKQAsACAAIAAgAGsAgiAsACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAGsAgyAsACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADMAKQAsACAAIAAgAGsAhCAsACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABaAGkAcAAgAGwAZQBuAGcAdABoAFwAbgAgACAAIAAgAEwAWgAsACAAQwBIAE8ATwBTAEUAKABtACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsAgSAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAG4AuwMoAGsAgSAsACAAawCCICkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBuALsDKABrAIEgLAAgAGsAgiAsACAAawCDICkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBuALsDKABrAIEgLAAgAGsAgiAsACAAawCDICwAIABrAIQgKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBhAHQAaQBvAG4AXABuACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMsACAATABBAE0AQgBEAEEAKABhAHIAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAWgBpAHAATABvAG4AZwA/ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAGEAcgByACwAIABMAFoALAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAYQByAHIALAAgAEwAWgApACkAKQAsAFwAbgBcAG4AIAAgACAAIABhACwAIABOAG8AcgBtAGEAbABpAHoAZQC7AygAYQByAHIAYQB5AF8AMQApACwAXABuACAAIAAgACAAYgAsACAATgBvAHIAbQBhAGwAaQB6AGUAuwMoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAGMALAAgAE4AbwByAG0AYQBsAGkAegBlALsDKABhAHIAcgBhAHkAXwAzACkALABcAG4AIAAgACAAIABkACwAIABOAG8AcgBtAGEAbABpAHoAZQC7AygAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAbgBnAGUAbQBlAG4AdABcAG4AIAAgACAAIABhAHIAcgBhAG4AZwBlAGQALAAgAEMASABPAE8AUwBFACgAbQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAsACAAYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAsACAAYgAsACAAYwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAsACAAYgAsACAAYwAsACAAZAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAWgBpAHAAIAB0AG8AIABsAGkAcwB0ACAAbwBmACAAcgBvAHcAESByAGUAYwBvAHIAZABzAFwAbgAgACAAIAAgAHoAaQBwAHAAZQBkACwAIABCAFkAUgBPAFcAKABhAHIAcgBhAG4AZwBlAGQALAAgAEwAQQBNAEIARABBACgAcgBvAHcALAAgAHsAcgBvAHcAfQApACkALABcAG4AXABuACAAIAAgACAAegBpAHAAcABlAGQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAEIARABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFAAYQBpAHIAdwBpAHMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMgAuADAAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAHIAZQBhAHQAZQBzACAAdgBlAHIAdABpAGMAYQBsACAAcABhAGkAcgBzACAAZgByAG8AbQAgAHQAdwBvACAAaQBuAHAAdQB0AHMAIAAoAHMAYwBhAGwAYQByAHMALAAgADEARAAgAGEAcgByAGEAeQBzACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAcwApAC4AXABuACAAIAAgACAAQgBvAHQAaAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAdwBpAHQAaAAgAFQATwBDAE8ATAAgAHMAbwAgAHQAaABhAHQAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AIABpAHMAIABjAG8AbgBzAGkAcwB0AGUAbgB0AFwAbgAgACAAIAAgAGEAbgBkACAAcABhAGkAcgBpAG4AZwAgAGIAZQBoAGEAdgBlAHMAIAB1AG4AaQBmAG8AcgBtAGwAeQAgAGEAYwByAG8AcwBzACAAcwBoAGEAcABlAHMALgBcAG4AXABuACAAIAAgACAAUABhAGkAcgB3AGkAcwBlALsDIABwAGUAcgBmAG8AcgBtAHMAIABhACAAQwBhAHIAdABlAHMAaQBhAG4AIABlAHgAcABhAG4AcwBpAG8AbgA6ACAAZQB2AGUAcgB5ACAAZQBsAGUAbQBlAG4AdAAgAG8AZgAgAHYAZQBjAHQAbwByAF8AMQAgAGkAcwBcAG4AIAAgACAAIABwAGEAaQByAGUAZAAgAHcAaQB0AGgAIABlAHYAZQByAHkAIABlAGwAZQBtAGUAbgB0ACAAbwBmACAAdgBlAGMAdABvAHIAXwAyAC4AIABUAGgAZQAgAHIAZQBzAHUAbAB0ACAAaQBzACAAYQAgADIAESBjAG8AbAB1AG0AbgAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAYQBsAGwAIABvAHIAZABlAHIAZQBkACAAcABhAGkAcgBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAdgBlAGMAdABvAHIAXwAxACAAIAAgACAALQAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByAF8AMgAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAG4AcAB1AHQAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUAIAB1AHMAaQBuAGcAIABUAE8AQwBPAEwALgBcAG4AIAAgACAAIAAiICAAUABhAGkAcgB3AGkAcwBlALsDIABoAGEAbAB0AHMAIAB3AGkAdABoACAAIwBOAFUATQAhACAAaQBmACAAdABoAGUAIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAcgBvAGQAdQBjAHQAIABlAHgAYwBlAGUAZABzACAAMQAsADAAMAAwACwAMAAwADAAXABuACAAIAAgACAAIAAgAHIAbwB3AHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABhAGkAcgB3AGkAcwBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByAF8AMQAsAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByAF8AMgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0AHMAXABuACAAIAAgACAAdgAsACAAIABUAE8AQwBPAEwAKAB2AGUAYwB0AG8AcgBfADEAKQAsAFwAbgAgACAAIAAgAHYAgiAsACAAVABPAEMATwBMACgAdgBlAGMAdABvAHIAXwAyACkALABcAG4AXABuACAAIAAgACAALwAvACAARQBsAGUAbQBlAG4AdAAgAGMAbwB1AG4AdABzAFwAbgAgACAAIAAgAGsALAAgACAAQwBPAFUATgBUAEEAKAB2ACkALABcAG4AIAAgACAAIABrAIIgLAAgAEMATwBVAE4AVABBACgAdgCCICkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAHMAYwBlAG4AYQByAGkAbwBcAG4AIAAgACAAIABJAHMAMgBCAGkAZwA/ACwAIAAgACAAIABrACAAKgAgAGsAgiAgAD4AIAAxADAAMAAwADAAMAAwACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAcwAyAEIAaQBnAD8ALAAgACMATgBVAE0AIQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABDAGEAcgB0AGUAcwBpAGEAbgAgAGUAeABwAGEAbgBzAGkAbwBuAFwAbgAgACAAIAAgAEoAbwBpAG4AUABhAGkAcgBzALsDLAAgAEwAQQBNAEIARABBACgAZQBhAGMAaABfAGUAbABlAG0AZQBuAHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKABlAGEAYwBoAF8AZQBsAGUAbQBlAG4AdAAsACAAawCCICwALAAgAGUAYQBjAGgAXwBlAGwAZQBtAGUAbgB0ACkALAAgAHYAgiApACkALABcAG4AXABuACAAIAAgACAAcABhAGkAcgBzACwAIAAgACAAIAAgACAARgBMAEEAVABUAEUATgAoAE0AQQBQACgAdgAsACAASgBvAGkAbgBQAGEAaQByAHMAuwMpACkALABcAG4AXABuACAAIAAgACAAcABhAGkAcgBzAFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAQgBEAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAVAByAGkAcABsAGUAdwBpAHMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMgAuADAAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABQAGEAaQByAHcAaQBzAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAdABoAGUAIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAcgBvAGQAdQBjAHQAIABvAGYAIAAzACAAcwBlAHQAcwAuACAAQQBsAGwAIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQAIAB1AHMAaQBuAGcAXABuACAAIAAgACAAVABPAEMATwBMACAAcwBvACAAdABoAGEAdAAgAHMAYwBhAGwAYQByAHMALAAgADEARAAgAGEAcgByAGEAeQBzACwAIABhAG4AZAAgADIARAAgAGEAcgByAGEAeQBzACAAYgBlAGgAYQB2AGUAIAB1AG4AaQBmAG8AcgBtAGwAeQAuAFwAbgBcAG4AIAAgACAAIABUAHIAaQBwAGwAZQB3AGkAcwBlALsDIABlAHgAdABlAG4AZABzACAAUABhAGkAcgB3AGkAcwBlALsDIAB0AG8AIABhACAAMwARIGEAeABpAHMAIABmAGEAYgByAGkAYwA6AFwAbgAgACAAIAAgACAAIAAgACAAcwBlAHQAXwAxACAA1wAgAHMAZQB0AF8AMgAgANcAIABzAGUAdABfADMAXABuACAAIAAgACAAVABoAGUAIABvAHUAdABwAHUAdAAgAGkAcwAgAGEAIAAzABEgYwBvAGwAdQBtAG4AIABzAHAAaQBsAGwAIAB3AGgAZQByAGUAIABlAGEAYwBoACAAcgBvAHcAIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAIABvAHIAZABlAHIAZQBkACAAdAByAGkAcABsAGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABzAGUAdABfADEAIAAgACAAIAAtACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AIABGAGwAYQB0AHQAZQBuAGUAZAAgAHcAaQB0AGgAIABUAE8AQwBPAEwALgBcAG4AIAAgACAAIABzAGUAdABfADIAIAAgACAAIAAtACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AIABGAGwAYQB0AHQAZQBuAGUAZAAgAHcAaQB0AGgAIABUAE8AQwBPAEwALgBcAG4AIAAgACAAIABzAGUAdABfADMAIAAgACAAIAAtACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AIABGAGwAYQB0AHQAZQBuAGUAZAAgAHcAaQB0AGgAIABUAE8AQwBPAEwALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAG4AcAB1AHQAcwAgAGEAcgBlACAAbgBvAHIAbQBhAGwAaQB6AGUAZAAgAGMAbwBsAHUAbQBuABEgdwBpAHMAZQAgAHUAcwBpAG4AZwAgAFQATwBDAE8ATAAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAGkAcwAgAGEAIAAyAEQAIABzAHAAaQBsAGwAIABvAGYAIABvAHIAZABlAHIAZQBkACAAdAByAGkAcABsAGUAcwAuAFwAbgAgACAAIAAgACIgIABUAHIAaQBwAGwAZQB3AGkAcwBlALsDIABwAHIAZQBzAGUAcgB2AGUAcwAgAHQAaABlACAAbwByAGQAZQByACAAbwBmACAAdABoAGUAIABzAHUAcABwAGwAaQBlAGQAIABzAGUAdABzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFQAcgBpAHAAbABlAHcAaQBzAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcwBlAHQAXwAxACwAXABuACAAIAAgACAAcwBlAHQAXwAyACwAXABuACAAIAAgACAAcwBlAHQAXwAzACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAXABuACAAIAAgACAAcwBlAHQAXwAxACwAIABUAE8AQwBPAEwAKABzAGUAdABfADEAKQAsAFwAbgAgACAAIAAgAHMAZQB0AF8AMgAsACAAVABPAEMATwBMACgAcwBlAHQAXwAyACkALABcAG4AIAAgACAAIABzAGUAdABfADMALAAgAFQATwBDAE8ATAAoAHMAZQB0AF8AMwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAaQByAHMAdAAgAEMAYQByAHQAZQBzAGkAYQBuACAAcAByAG8AZAB1AGMAdABcAG4AIAAgACAAIABwAGEAaQByAHMALAAgAFAAYQBpAHIAdwBpAHMAZQC7AygAcwBlAHQAXwAxACwAIABzAGUAdABfADIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHAAbABpAHQAIABpAG4AdABvACAAYwBvAGwAdQBtAG4AcwBcAG4AIAAgACAAIABhACwAIAAgACAAIAAgAFQAQQBLAEUAKABwAGEAaQByAHMALAAsADEAKQAsAFwAbgAgACAAIAAgAGIALAAgACAAIAAgACAAVABBAEsARQAoAHAAYQBpAHIAcwAsACwALQAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGMAbwBuAGQAIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAcgBvAGQAdQBjAHQAIAAoAGEAIADXACAAcwBlAHQAXwAzACkAXABuACAAIAAgACAAcABfADEAMwAsACAAIABQAGEAaQByAHcAaQBzAGUAuwMoAGEALAAgAHMAZQB0AF8AMwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBjAG8AbgBkACAAQwBhAHIAdABlAHMAaQBhAG4AIABwAHIAbwBkAHUAYwB0ACAAKABiACAA1wAgAHMAZQB0AF8AMwApAFwAbgAgACAAIAAgAHAAXwAyADMALAAgACAAUABhAGkAcgB3AGkAcwBlALsDKABiACwAIABzAGUAdABfADMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAYwBvAGwAdQBtAG4AcwBcAG4AIAAgACAAIABhAF8ALAAgACAAIAAgAFQAQQBLAEUAKABwAF8AMQAzACwALAAxACkALABcAG4AIAAgACAAIABiAF8ALAAgACAAIAAgAFQAQQBLAEUAKABwAF8AMgAzACwALAAxACkALABcAG4AIAAgACAAIABjAF8ALAAgACAAIAAgAFQAQQBLAEUAKABwAF8AMQAzACwALAAtADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAGkAbgBhAGwAIAB0AHIAaQBwAGwAZQBcAG4AIAAgACAAIAB0AHIAaQBwAGwAZQAsAEgAUwBUAEEAQwBLACgAYQBfACwAIABiAF8ALAAgAGMAXwApACwAXABuACAAIAAgACAAdAByAGkAcABsAGUAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAQgBEAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAUQB1AGEAZAB3AGkAcwBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAEIARABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAyAC4AMABcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMsACAAUgBlAHMAaQB6AGUAuwMsACAAVAByAGkAcABsAGUAdwBpAHMAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIAB0AGgAZQAgAEMAYQByAHQAZQBzAGkAYQBuACAAcAByAG8AZAB1AGMAdAAgAG8AZgAgADQAIABzAGUAdABzAC4AIABBAGwAbAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAGEAbgBkAFwAbgAgACAAIAAgAHQAaABlACAAcgBlAHMAdQBsAHQAaQBuAGcAIABxAHUAYQBkAHIAdQBwAGwAZQBzACAAcAByAGUAcwBlAHIAdgBlACAAdABoAGUAIABvAHIAZABlAHIAIABvAGYAIAB0AGgAZQAgAHMAdQBwAHAAbABpAGUAZAAgAHMAZQB0AHMALgBcAG4AXABuACAAIAAgACAAUQB1AGEAZAB3AGkAcwBlALsDIABlAHgAdABlAG4AZABzACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AyAAdABvACAAYQAgADQAESBhAHgAaQBzACAAZgBhAGIAcgBpAGMAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABzAGUAdABfADEAIADXACAAcwBlAHQAXwAyACAA1wAgAHMAZQB0AF8AMwAgANcAIABzAGUAdABfADQAXABuACAAIAAgACAAVABoAGUAIABvAHUAdABwAHUAdAAgAGkAcwAgAGEAIABzAHAAaQBsAGwAIAByAGEAbgBnAGUAIAB3AGgAZQByAGUAIABlAGEAYwBoACAAcgBvAHcAIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAIABvAHIAZABlAHIAZQBkACAAcQB1AGEAZAByAHUAcABsAGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABzAGUAdABfADEAIAAgACAAIABTAGMAYQBsAGEAcgBzACAAYQBuAGQAIABhAHIAcgBhAHkAcwAgACgAMQBEACAAbwByACAAMgBEACkAIABhAHIAZQAgAGEAYwBjAGUAcAB0AGUAZAAuACAAQQBsAGwAIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQALgBcAG4AIAAgACAAIABzAGUAdABfADIAXABuACAAIAAgACAAcwBlAHQAXwAzAFwAbgAgACAAIAAgAHMAZQB0AF8ANABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUQB1AGEAZAB3AGkAcwBlALsDPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABzAGUAdABfADEALABcAG4AIAAgACAAIABzAGUAdABfADIALABcAG4AIAAgACAAIABzAGUAdABfADMALABcAG4AIAAgACAAIABzAGUAdABfADQALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAYQBsAGwAIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIABzAGUAdABfADEALAAgACAAVABPAEMATwBMACgAcwBlAHQAXwAxACkALABcAG4AIAAgACAAIABzAGUAdABfADIALAAgACAAVABPAEMATwBMACgAcwBlAHQAXwAyACkALABcAG4AIAAgACAAIABzAGUAdABfADMALAAgACAAVABPAEMATwBMACgAcwBlAHQAXwAzACkALABcAG4AIAAgACAAIABzAGUAdABfADQALAAgACAAVABPAEMATwBMACgAcwBlAHQAXwA0ACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHAAYQBuAHMAaQBvAG4AIABjAG8AdQBuAHQAXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgAFIATwBXAFMAKABzAGUAdABfADQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAHMAZQB0ACAANAAgAGkAZgAgAHMAYwBhAGwAYQByACAAdABvACAAYQB2AG8AaQBkACAAVABPAEMATwBMACAAaABhAG4AZABvAGYAZgAgAHQAbwAgAFIAZQBzAGkAegBlALsDXABuACAAIAAgACAAZAAsACAAIAAgACAAIAAgAEkARgAoAGsAIAA8AD4AIAAxACwAcwBlAHQAXwA0ACwASQBOAEQARQBYACgAcwBlAHQAXwA0ACwAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAVAByAGkAcABsAGUAcwBcAG4AIAAgACAAIAB0AGgAcgBpAGMAZQAsACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AygAcwBlAHQAXwAxACwAcwBlAHQAXwAyACwAcwBlAHQAXwAzACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AZAAgAHQAcgBpAHAAbABlACAAcgBvAHcAcwAgAGIAeQAgAHQAbwB0AGEAbAAgAGkAdABlAG0AcwAgAGkAbgAgAHMAZQB0ACAANABcAG4AIAAgACAAIAB0AGgAcgBpAGMAZQBfACwAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AygAdABoAHIAaQBjAGUALABrACkALABcAG4AIAAgACAAIABrAIIgLAAgACAAIAAgACAAUgBPAFcAUwAoAHQAaAByAGkAYwBlAF8AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AZAAgAHMAZQB0ACAANAAgAHQAbwAgAG0AYQB0AGMAaAAgAGwAZQBuAGcAdABoACAAbwBmACAAdAByAGkAcABsAGUAXABuACAAIAAgACAAZgBvAHUAcgAsACAAIAAgAFIAZQBzAGkAegBlALsDKABkACwAawCCICAALwAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQBjAGsAIABhAG4AZAAgAGQAaQBzAHAAbABhAHkAXABuACAAIAAgACAAZgBpAG4AYQBsACwAIAAgAEgAUwBUAEEAQwBLACgAdABoAHIAaQBjAGUAXwAsAGYAbwB1AHIAKQAsAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAEIARABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEUAYwBoAG8AuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAQgBEAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADIALgAwAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHAAZQBhAHQAcwAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAaQBuACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgADEARAAgAGEAcgByAGEAeQAgAGEAYwBjAG8AcgBkAGkAbgBnACAAdABvACAAYQAgAHYAZQBjAHQAbwByACAAbwBmAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AHMALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAHUAcABwAG8AcgB0AGUAZAAuACAAUgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgAG0AdQBzAHQAIABiAGUAXABuACAAIAAgACAAbgB1AG0AZQByAGkAYwAgAGEAbgBkACAAZSIgADEALgBcAG4AXABuACAAIAAgACAARQBjAGgAbwC7AyAAbgBvAHIAbQBhAGwAaQB6AGUAcwAgAGIAbwB0AGgAIABpAG4AcAB1AHQAcwAgAHcAaQB0AGgAIABUAE8AQwBPAEwALAAgAGUAeAB0AGUAbgBkAHMAIAB0AGgAZQAgAHIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAIAB3AGgAZQBuAFwAbgAgACAAIAAgAG4AZQBjAGUAcwBzAGEAcgB5ACwAIABhAG4AZAAgAHUAcwBlAHMAIABNAEEAUAAgACsAIABFAFgAUABBAE4ARAAgAHQAbwAgAGcAZQBuAGUAcgBhAHQAZQAgAHQAaABlACAAZQBjAGgAbwBlAGQAIABvAHUAdABwAHUAdAAuACAAVABoAGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQAIABpAHMAIABhAGwAdwBhAHkAcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgAgACAAIAAtACAAUwBjAGEAbABhAHIAIABvAHIAIAAxAEQALwAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABiAGUAIABlAGMAaABvAGUAZAAuACAARgBsAGEAdAB0AGUAbgBlAGQAIAB3AGkAdABoACAAVABPAEMATwBMAC4AXABuACAAIAAgACAAcgBlAHAAZQBhAHQAIAAgACAALQAgADEARAAgAGEAcgByAGEAeQAgAG8AZgAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AHMAIAAoAG4AdQBtAGUAcgBpAGMALAAgAGUiIAAxACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAYQByAGUAIAB0AHIAZQBhAHQAZQBkACAAYQBzACAAMQDXADEAIABhAHIAcgBhAHkAcwAuAFwAbgAgACAAIAAgACIgIABJAGYAIAByAGUAcABlAGEAdAAgAGgAYQBzACAAYQAgAGQAaQBmAGYAZQByAGUAbgB0ACAAbABlAG4AZwB0AGgAIAB0AGgAYQBuACAAdgBlAGMAdABvAHIALAAgAHQAaABlACAAbABhAHMAdAAgAHIAZQBwAGUAYQB0ACAAdgBhAGwAdQBlAFwAbgAgACAAIAAgACAAIABpAHMAIABlAHgAdABlAG4AZABlAGQAIAB0AG8AIABtAGEAdABjAGgAIAB0AGgAZQAgAHYAZQBjAHQAbwByACAAbABlAG4AZwB0AGgALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABpAHMAIABhAGwAdwBhAHkAcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARQBjAGgAbwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgAsAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAXABuAFwAbgBJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAHIAZQBwAGUAYQB0ACkALAAgAHIAZQBwAGUAYQB0ACAAPAA9ACAAMAApACwAIABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgAsACAAVABPAEMATwBMACgAdgBlAGMAdABvAHIAKQAsAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAIABUAE8AQwBPAEwAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAVgBoACwAIAAgACAAIAAgAFIATwBXAFMAKAB2AGUAYwB0AG8AcgApACwAXABuACAAIAAgACAAUgBoACwAIAAgACAAIAAgAFIATwBXAFMAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAIAAoAGUAeAB0AGUAbgBkACAAbABhAHMAdAAgAHYAYQBsAHUAZQAgAGkAZgAgAG4AZQBlAGQAZQBkACkAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgAEkARgAoAFYAaAAgADwAPgAgAFIAaAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAcgBlAHAAZQBhAHQALAAgAFYAaAAsACwAIABAAFQAQQBLAEUAKAByAGUAcABlAGEAdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AcwBpAG8AbgAgAGUAbgBnAGkAbgBlAFwAbgAgACAAIAAgAEUAeAB0AGUAbgBkALsDLABMAEEATQBCAEQAQQAoAGUAYQBjAGgAXwBlAGwAZQBtAGUAbgB0ACwAIAByAF8ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAZQBhAGMAaABfAGUAbABlAG0AZQBuAHQALAAgAHIAXwAsACwAIABlAGEAYwBoAF8AZQBsAGUAbQBlAG4AdAApACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGwAaQB2AGUAcgAgAGUAYwBoAG8AZQBkACAAbwB1AHQAcAB1AHQAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsAEYATABBAFQAVABFAE4AKABNAEEAUAAoAHYAZQBjAHQAbwByACwAIAByACwAIABFAHgAdABlAG4AZAC7AykAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAQgBEAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAQgBsAG8AYwBrAHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAQgBEAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAHQAbwB0AHkAcABlAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAATgBvAG4AZQAgACgAcgBlAHAAdQByAHAAbwBzAGUAZAAgAEcAcgBhAGkAbgC7AykAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABQAGEAcgB0AGkAdABpAG8AbgBzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIAByAGUAYwB0AGEAbgBnAHUAbABhAHIAIABiAGwAbwBjAGsAcwAgAG8AZgAgAHMAaQB6AGUAIABkAGUAcAB0AGgAIADXACAAdwBpAGQAdABoAC4AXABuACAAIAAgACAARQBhAGMAaAAgAGIAbABvAGMAawAgAGkAcwAgAGUAeAB0AHIAYQBjAHQAZQBkACAAYQBzACAAYQAgAG4AZQBzAHQAZQBkACAAYQByAHIAYQB5ACAAYQBuAGQAIAB3AHIAYQBwAHAAZQBkACAAaQBuACAAYQAgAGwAaQBzAHQAIABsAGkAdABlAHIAYQBsACwAXABuACAAIAAgACAAcAByAG8AZAB1AGMAaQBuAGcAIABhACAAbABpAHMAdAARIG8AZgARIGwAaQBzAHQAcwAgAHMAdAByAHUAYwB0AHUAcgBlADoAXABuAFwAbgAgACAAIAAgACAAIAAgACAAewAgAHsAYgBsAG8AYwBrAIEgfQAsACAAewBiAGwAbwBjAGsAgiB9ACwAIAAmICAAfQBcAG4AXABuACAAIAAgACAAQgBsAG8AYwBrAHMAuwMgAHIAbwB1AG4AZABzACAAdQBwACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGIAbABvAGMAawBzACAAcwBvACAAcABhAHIAdABpAGEAbAAgAGUAZABnAGUAIABiAGwAbwBjAGsAcwAgAGEAcgBlAFwAbgAgACAAIAAgAGkAbgBjAGwAdQBkAGUAZAAuACAARQBhAGMAaAAgAGIAbABvAGMAawAgAGkAcwAgAGUAeAB0AHIAYQBjAHQAZQBkACAAdQBzAGkAbgBnACAASQBOAEQARQBYACAAbwB2AGUAcgAgAGcAZQBuAGUAcgBhAHQAZQBkACAAcgBvAHcALwBjAG8AbAB1AG0AbgBcAG4AIAAgACAAIABhAG4AYwBoAG8AcgAgAGcAcgBpAGQAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAcABhAHIAdABpAHQAaQBvAG4ALgBcAG4AIAAgACAAIABkAGUAcAB0AGgAIAAgACAAIAAgACAALQAgAEIAbABvAGMAawAgAGgAZQBpAGcAaAB0AC4AXABuACAAIAAgACAAdwBpAGQAdABoACAAIAAgACAAIAAgAC0AIABCAGwAbwBjAGsAIAB3AGkAZAB0AGgALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAGkAcwAgAGEAIABsAGkAcwB0ACAAbwBmACAAbgBlAHMAdABlAGQAIABhAHIAcgBhAHkAcwAsACAAbgBvAHQAIABhACAAcwBwAGkAbABsAGUAZAAgADIARAAgAGcAcgBpAGQALgBcAG4AIAAgACAAIAAiICAAVQBzAGUAIABGAEwAQQBUAFQARQBOACAAdABvACAAcwBwAGkAbABsACAAYgBsAG8AYwBrAHMAIABpAG4AdABvACAAYQAgAHQAYQBiAGwAZQAgAGkAZgAgAG4AZQBlAGQAZQBkAC4AXABuACAAIAAgACAAIiAgAFQAaABpAHMAIABvAHAAZQByAGEAdABvAHIAIABpAHMAIABlAHgAcABlAHIAaQBtAGUAbgB0AGEAbAAgAGEAbgBkACAAaQBuAHQAZQBuAGQAZQBkACAAZgBvAHIAIABuAGUAcwB0AGUAZAARIGEAcgByAGEAeQAgAHQAZQBzAHQAaQBuAGcALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQgBsAG8AYwBrAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACwAXABuACAAIAAgACAAZABlAHAAdABoACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AXABuACAAIAAgACAALwAvACAATgB1AG0AYgBlAHIAIABvAGYAIABiAGwAbwBjAGsAcwAgACgAcgBvAHUAbgBkAGUAZAAgAHUAcAApAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIABSAE8AVQBOAEQAVQBQACgAaAAgAC8AIABkAGUAcAB0AGgALAAgADAAKQAsAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIABSAE8AVQBOAEQAVQBQACgAdwAgAC8AIAB3AGkAZAB0AGgALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGwAbwBjAGsAIABhAG4AYwBoAG8AcgAgAGcAcgBpAGQAcwAgACgAZABlAGYAZQByAHIAZQBkACkAXABuACAAIAAgACAAZABvAHcAbgAsACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAeAAsACwAMQAsAGQAZQBwAHQAaAApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAeQAsADEALAAwACkAKQAsAFwAbgAgACAAIAAgAGEAYwByAG8AcwBzACwAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoACwAeQAsADEALAB3AGkAZAB0AGgAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAB4ACwALAAxACwAMAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG4AdgBlAHIAdAAgAG0AYQB0AHIAaQBjAGUAcwAgAHQAbwAgAGwAaQBzAHQAcwBcAG4AIAAgACAAIABUAG8ATABpAHMAdAC7AywAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAIABjACwAXABuACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABpACwAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABkAGUAcAB0AGgALAAsAHIAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsAHcAaQBkAHQAaAAsADEALAAwACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABqACwAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKAAsAHcAaQBkAHQAaAAsAGMAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKABkAGUAcAB0AGgALAAsADEALAAwACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsALAAgACAASQBOAEQARQBYACgAYQByAHIAYQB5AF8AMgBEACwAIABpACgAKQAsACAAagAoACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcwB1AGwAdAAsACAAewBiAGwAbwBjAGsAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcwB1AGwAdABcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbgB2AGUAcgB0ACAAbABlAHYAZQBsABEgMgAgAG0AYQB0AHIAaQBjAGUAcwAgAHQAbwAgAGwAaQBzAHQAcwBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIABNAEEAUAAoAGQAbwB3AG4AKAApACwAIABhAGMAcgBvAHMAcwAoACkALAAgAFQAbwBMAGkAcwB0ALsDKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABXAGkAbgBkAG8AdwBlAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAQgBEAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAATQBHAHIAaQBkALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABhAGwAbAAgAG8AdgBlAHIAbABhAHAAcABpAG4AZwAgAHcAaQBuAGQAbwB3AHMAIABvAGYAIABzAGkAegBlACAAZABlAHAAdABoACAA1wAgAHcAaQBkAHQAaAAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAARQBhAGMAaAAgAHcAaQBuAGQAbwB3ACAAaQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAYQAgAG4AZQBzAHQAZQBkACAAYQByAHIAYQB5ACAAdwByAGEAcABwAGUAZAAgAGkAbgAgAGEAIABsAGkAcwB0ACAAbABpAHQAZQByAGEAbAAsAFwAbgAgACAAIAAgAHAAcgBvAGQAdQBjAGkAbgBnACAAYQBuACAAYQByAHIAYQB5AC0AbwBmAC0AbABpAHMAdABzACAAcwB0AHIAdQBjAHQAdQByAGUALgBcAG4AXABuACAAIAAgACAAVwBpAG4AZABvAHcAZQBkALsDIAB1AHMAZQBzACAAbQBlAHMAaAAtAGcAcgBpAGQAIABvAGYAZgBzAGUAdABzACAAZwBlAG4AZQByAGEAdABlAGQAIABmAHIAbwBtACAATQBHAHIAaQBkALsDIAB0AG8AIABjAG8AbgBzAHQAcgB1AGMAdABcAG4AIAAgACAAIAB3AGkAbgBkAG8AdwAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAgAGEAbgBkACAATQBBAEsARQBBAFIAUgBBAFkAIAB0AG8AIABhAHMAcwBlAG0AYgBsAGUAIAB0AGgAZQAgAGYAdQBsAGwAIAB3AGkAbgBkAG8AdwAgAGYAYQBiAHIAaQBjAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAAoADEARAAgAGEAcgByAGEAeQBzACAAYQBuAGQAIABzAGMAYQBsAGEAcgBzACAAYQByAGUAIAByAGUAagBlAGMAdABlAGQAKQAuAFwAbgAgACAAIAAgAGQAZQBwAHQAaAAgACAAIAAgACAAIAAtACAAVABvAHQAYQBsACAAcgBvAHcAcwAgAGkAbgAgAGUAYQBjAGgAIAB3AGkAbgBkAG8AdwAuAFwAbgAgACAAIAAgAFsAdwBpAGQAdABoAF0AIAAgACAAIAAtACAAVABvAHQAYQBsACAAYwBvAGwAdQBtAG4AcwAgAGkAbgAgAGUAYQBjAGgAIAB3AGkAbgBkAG8AdwAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAZABlAHAAdABoAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABpAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABsAGkAcwB0AHMALAAgAG4AbwB0ACAAYQAgAHMAcABpAGwAbABlAGQAIAAyAEQAIABnAHIAaQBkAC4AXABuACAAIAAgACAAIiAgAFUAcwBlACAARgBMAEEAVABUAEUATgAgAHQAbwAgAHMAcABpAGwAbAAgAHcAaQBuAGQAbwB3AHMAIABpAG4AdABvACAAYQAgAHQAYQBiAGwAZQAgAGkAZgAgAG4AZQBlAGQAZQBkAC4AXABuACAAIAAgACAAIiAgAFIAZQBqAGUAYwB0AHMAIAAxAEQAIABhAHIAcgBhAHkAcwAgAGEAbgBkACAAcwBjAGEAbABhAHIAcwAgAHQAbwAgAHAAcgBlAHMAZQByAHYAZQAgADIARAAgAHcAaQBuAGQAbwB3ACAAcwBlAG0AYQBuAHQAaQBjAHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVwBpAG4AZABvAHcAZQBkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAsAFwAbgAgACAAIAAgAGQAZQBwAHQAaAAsAFwAbgAgACAAIAAgAFsAdwBpAGQAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIAB3AGkAZAB0AGgAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB3AGkAZAB0AGgAKQAsACAAZABlAHAAdABoACwAIAB3AGkAZAB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAZgBlAHIAZQBuAGMAZQAgAHMAaABhAHAAZQAgAGYAbwByACAAbQBlAHMAaAAgAGcAcgBpAGQAXABuACAAIAAgACAAawBlAHIAbgBlAGwALAAgACAAIAAgACAARQBYAFAAQQBOAEQAKAAwACwAIABkAGUAcAB0AGgALAAgAHcAaQBkAHQAaAAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADIARAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAYQBsAHQAaQBuAGcAIABzAGMAZQBuAGEAcgBpAG8AXABuACAAIAAgACAASQBuAFYAYQBsAGkAZABEAFcAPwAsACAATwBSACgASQBTAFQARQBYAFQAKABkAGUAcAB0AGgAKQAsACAASQBTAFQARQBYAFQAKAB3AGkAZAB0AGgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGQAZQBwAHQAaAAgADwAIAAxACwAIAB3AGkAZAB0AGgAIAA8ACAAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGQAZQBwAHQAaAAgAD4AIABoACwAIAB3AGkAZAB0AGgAIAA+ACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAcgBpAHYAaQBhAGwAIABjAGEAcwBlAFwAbgAgACAAIAAgAE8AbgBlAFcAaQBuAGQAbwB3AD8ALAAgAEEATgBEACgAaAAgAD0AIABkAGUAcAB0AGgALAAgAHcAIAA9ACAAdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAASQBGACgASQBuAFYAYQBsAGkAZABEAFcAPwAsACAAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIABJAEYAKABPAG4AZQBXAGkAbgBkAG8AdwA/ACwAIAB7AGEAcgByAGEAeQBfADIARAB9ACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAVwBpAG4AZABvAHcAIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABrAF8AaAAsACAAIAAgACAAIABoACAALQAgAGQAZQBwAHQAaAAgACsAIAAxACwAXABuACAAIAAgACAAawBfAHcALAAgACAAIAAgACAAdwAgAC0AIAB3AGkAZAB0AGgAIAArACAAMQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGUAcwBoACAAZwByAGkAZAAgAG8AZgBmAHMAZQB0AHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAASQBGACgAZABlAHAAdABoACAAPQAgADEALAAgAGsAZQByAG4AZQBsACwAIABNAEcAcgBpAGQAuwMoAGsAZQByAG4AZQBsACkAIAAtACAAMQApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAASQBGACgAdwBpAGQAdABoACAAPQAgADEALAAgAGsAZQByAG4AZQBsACwAIABNAEcAcgBpAGQAuwMoAGsAZQByAG4AZQBsACwAIAAxACkAIAAtACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFcAaQBuAGQAbwB3AGkAbgBnAFwAbgAgACAAIAAgAHcAaQBuAGQAbwB3AHMALAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAawBfAGgALAAgAGsAXwB3ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAGkALAAgAGoALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAYQByAHIAYQB5AF8AMgBEACwAIABpACAAKwAgAHgALAAgAGoAIAArACAAeQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAB3AGkAbgBkAG8AdwBzAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABDAG8AbgB2AG8AbAB2AGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAQgBEAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADIALgAwAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAAVwBpAG4AZABvAHcAZQBkALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABQAGUAcgBmAG8AcgBtAHMAIABhACAAcwBsAGkAZABpAG4AZwARIHcAaQBuAGQAbwB3ACAAYwBvAG4AdgBvAGwAdQB0AGkAbwBuACAAbwB2AGUAcgAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIAB1AHMAaQBuAGcAIABhACAAMgBEACAAawBlAHIAbgBlAGwALgBcAG4AIAAgACAAIABFAGEAYwBoACAAdwBpAG4AZABvAHcAIABlAHgAdAByAGEAYwB0AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAGgAYQBzACAAdABoAGUAIABzAGEAbQBlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAGEAcwAgAHQAaABlAFwAbgAgACAAIAAgAGsAZQByAG4AZQBsAC4AIABBACAAcgBlAGQAdQBjAGUAcgAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABlAGEAYwBoACAAdwBpAG4AZABvAHcAIAB0AG8AIABwAHIAbwBkAHUAYwBlACAAdABoAGUAIABvAHUAdABwAHUAdAAuAFwAbgBcAG4AIAAgACAAIABJAGYAIABuAG8AIAByAGUAZAB1AGMAZQByACAAZgB1AG4AYwB0AGkAbwBuACAAaQBzACAAcwB1AHAAcABsAGkAZQBkACwAIABDAG8AbgB2AG8AbAB2AGUAuwMgAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAGEAIABkAG8AdAARIHAAcgBvAGQAdQBjAHQAXABuACAAIAAgACAAcgBlAGQAdQBjAGUAcgA6ACAAUwBVAE0AKABGAEwAQQBUAFQARQBOACgAdgApACAAKgAgAGsAZQByAG4AZQBsACkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAdwBoAGkAYwBoACAAdABoAGUAIABrAGUAcgBuAGUAbAAgAGkAcwAgAGEAcABwAGwAaQBlAGQALgBcAG4AIAAgACAAIABrAGUAcgBuAGUAbAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAZABlAGYAaQBuAGkAbgBnACAAdABoAGUAIABzAGwAaQBkAGkAbgBnACAAdwBpAG4AZABvAHcAIABkAGkAbQBlAG4AcwBpAG8AbgBzAC4AXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHIAZQBkAHUAYwBlAHIAIABMAEEATQBCAEQAQQAgAGEAYwBjAGUAcAB0AGkAbgBnACAAYQAgAHMAaQBuAGcAbABlACAAYQByAHIAYQB5ACAAYQByAGcAdQBtAGUAbgB0AC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAFMAVQBNACgARgBMAEEAVABUAEUATgAoAHYAKQAgACoAIABrAGUAcgBuAGUAbAApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgAFwAIgAjAEsARQBSAE4ARQBMACEAXAAiACAAaQBmACAAdABoAGUAIABrAGUAcgBuAGUAbAAgAGkAcwAgAGwAYQByAGcAZQByACAAdABoAGEAbgAgAHQAaABlACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBGAFUATgBDAFQASQBPAE4AIQBcACIAIABpAGYAIAB0AGgAZQAgAHIAZQBkAHUAYwBlAHIAIABpAHMAIABuAG8AdAAgAGEAIAB2AGEAbABpAGQAIABMAEEATQBCAEQAQQAuAFwAbgAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAYQByAGUAIAB0AHIAZQBhAHQAZQBkACAAYQBzACAAMQDXADEAIABhAHIAcgBhAHkAcwAgAGEAbgBkACAAbQBhAHAAcABlAGQAIAB0AGgAcgBvAHUAZwBoACAAdABoAGUAIAByAGUAZAB1AGMAZQByAC4AXABuACAAIAAgACAAIiAgAFIAZQBkAHUAYwBlAHIAIABiAGUAaABhAHYAaQBvAHIAIABpAHMAIAB1AHMAZQByABEgZABlAGYAaQBuAGUAZAA7ACAAYQByAHIAYQB5AHMAIABuAGUAZQBkACAAbgBvAHQAIABiAGUAIABuAHUAbQBlAHIAaQBjAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEMAbwBuAHYAbwBsAHYAZQC7Az0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAawBlAHIAbgBlAGwALABcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAeQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsACAAIAAgACAAdwAsACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEsAZQByAG4AZQBsACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABrAGUAcgBuAGUAbABfAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAUgBPAFcAUwAoAGsAZQByAG4AZQBsACkALABcAG4AIAAgACAAIABrAGUAcgBuAGUAbABfAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGsAZQByAG4AZQBsACkALABcAG4AXABuACAAIAAgACAALwAvACAASwBlAHIAbgBlAGwAIABtAHUAcwB0ACAAZgBpAHQAIABpAG4AcwBpAGQAZQAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEsAZQByAG4AZQBsAD8ALAAgACAAIAAgACAATwBSACgAawBlAHIAbgBlAGwAXwBoAGUAaQBnAGgAdAAgAD4AIABoACwAIABrAGUAcgBuAGUAbABfAHcAaQBkAHQAaAAgAD4AIAB3ACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGEAbABhAHIAIABoAGEAbgBkAGwAaQBuAGcAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgBLAGUAcgBuAGUAbAA/ACwAIAAgACAAIABBAE4ARAAoAGsAZQByAG4AZQBsAF8AaABlAGkAZwBoAHQAIAA9ACAAMQAsACAAawBlAHIAbgBlAGwAXwB3AGkAZAB0AGgAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIAByAGUAZAB1AGMAZQByACAAPQAgAGQAbwB0ACAAcAByAG8AZAB1AGMAdABcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAHUAbgBjAHQAaQBvAG4AKQAsAEwAQQBNAEIARABBACgAdgAsACAAUwBVAE0AKABGAEwAQQBUAFQARQBOACgAdgApACAAKgAgAGsAZQByAG4AZQBsACkAKQAsAGYAdQBuAGMAdABpAG8AbgApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABGAHUAbgBjAHQAaQBvAG4APwAsACAAIAAgAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAbwByACAAcwBjAGEAbABhAHIAESBrAGUAcgBuAGUAbAAgAGMAYQBzAGUAIACSISAAcwBpAG0AcABsAGUAIABNAEEAUABcAG4AIAAgACAAIABTAHQAYQBuAGQAYQByAGQATQBhAHAALAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABNAEEAUAAoAGEAcgByAGEAeQAsACAAZgB1AG4AYwB0AGkAbwBuACkAKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEsAZQByAG4AZQBsAD8ALAAgAFwAIgAjAEsARQBSAE4ARQBMACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABGAHUAbgBjAHQAaQBvAG4APwAsAFwAIgAjAEYAVQBOAEMAVABJAE8ATgAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAKABJAHMAUwBjAGEAbABhAHIAPwApACAAKwAgACgASQBzAFMAYwBhAGwAYQByAEsAZQByAG4AZQBsAD8AKQAsAFMAdABhAG4AZABhAHIAZABNAGEAcAAoACkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAAdwBpAG4AZABvAHcAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFcAaQBuAGQAbwB3AGUAZAC7AygAYQByAHIAYQB5ACwAawBlAHIAbgBlAGwAXwBoAGUAaQBnAGgAdAAsAGsAZQByAG4AZQBsAF8AdwBpAGQAdABoACkALABcAG4AIAAgACAAIABjAG8AbgB2AG8AbAB1AHQAaQBvAG4ALAAgACAAIAAgACAAIAAgACAATQBBAFAAKAB3AGkAbgBkAG8AdwBzACwAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AIAAgACAAIABjAG8AbgB2AG8AbAB1AHQAaQBvAG4AXABuAFwAbgApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAQgBEAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARwByAGkAZABMAG8AbwBrAHUAcAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAGUAYQByAGMAaABlAHMAIABhACAAMgBEACAAYQByAHIAYQB5ACAAZgBvAHIAIABtAGEAdABjAGgAZQBzACAAYQBuAGQAIAByAGUAdAB1AHIAbgBzACAAdABoAGUAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAaQB0AGUAbQBzACAAZgByAG8AbQAgAGEAXABuACAAIAAgACAAcwBlAGMAbwBuAGQAIAAyAEQAIABhAHIAcgBhAHkALgAgAEcAcgBpAGQATABvAG8AawB1AHAAuwMgAHAAZQByAGYAbwByAG0AcwAgAGEAIABmAGwAYQB0AHQAZQBuAGUAZAAgAFgATQBBAFQAQwBIACAAbwB2AGUAcgAgAHQAaABlACAAcwBlAGEAcgBjAGgAXABuACAAIAAgACAAZwByAGkAZAAsACAAYwBvAG4AdgBlAHIAdABzACAAdABoAGUAIABsAGkAbgBlAGEAcgAgAGkAbgBkAGUAeAAgAGIAYQBjAGsAIAB0AG8AIAAyAEQAIABjAG8AbwByAGQAaQBuAGEAdABlAHMALAAgAGEAbgBkACAAcgBlAHQAcgBpAGUAdgBlAHMAIAB0AGgAZQBcAG4AIAAgACAAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAZQBsAGUAbQBlAG4AdAAgAGYAcgBvAG0AIAByAGUAdAB1AHIAbgBfAGEAcgByAGEAeQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGwAbwBvAGsAdQBwAF8AdgBhAGwAdQBlAHMAIAAgACAALQAgAFYAYQBsAHUAZQBzACAAdABvACAAcwBlAGEAcgBjAGgAIABmAG8AcgAgACgAcwBjAGEAbABhAHIAIABvAHIAIABhAHIAcgBhAHkAKQAuAFwAbgAgACAAIAAgAGwAbwBvAGsAdQBwAF8AYQByAHIAYQB5ACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAgAHQAbwAgAHMAZQBhAHIAYwBoAC4AXABuACAAIAAgACAAcgBlAHQAdQByAG4AXwBhAHIAcgBhAHkAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAZgByAG8AbQAgAHcAaABpAGMAaAAgAG0AYQB0AGMAaABlAGQAIABpAHQAZQBtAHMAIABhAHIAZQAgAHIAZQB0AHUAcgBuAGUAZAAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwAgACgAbQBhAHQAYwBoAGkAbgBnACAAWABMAE8ATwBLAFUAUAAvAFgATQBBAFQAQwBIACAAZABlAGYAYQB1AGwAdABzACkAOgBcAG4AIAAgACAAIABbAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkAF0AIAAgAC0AIABWAGEAbAB1AGUAIAByAGUAdAB1AHIAbgBlAGQAIABpAGYAIABuAG8AIABtAGEAdABjAGgAIABpAHMAIABmAG8AdQBuAGQALgAgAEQAZQBmAGEAdQBsAHQAIAA9ACAAIwBOAC8AQQAuAFwAbgAgACAAIAAgAFsAbQBhAHQAYwBoAF8AbQBvAGQAZQBdACAAIAAgACAALQAgAE0AYQB0AGMAaAAgAGIAZQBoAGEAdgBpAG8AcgAuACAARABlAGYAYQB1AGwAdAAgAD0AIAAwACAAKABlAHgAYQBjAHQAIABtAGEAdABjAGgAKQAuAFwAbgAgACAAIAAgAFsAcwBlAGEAcgBjAGgAXwBtAG8AZABlAF0AIAAgACAALQAgAFMAZQBhAHIAYwBoACAAZABpAHIAZQBjAHQAaQBvAG4ALgAgAEQAZQBmAGEAdQBsAHQAIAA9ACAAMQAgACgAZgBpAHIAcwB0ABEgdABvABEgbABhAHMAdAApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAgAGkAZgAgAGwAbwBvAGsAdQBwAF8AYQByAHIAYQB5ACAAYQBuAGQAIAByAGUAdAB1AHIAbgBfAGEAcgByAGEAeQAgAHMAaABhAHAAZQBzACAAZABpAGYAZgBlAHIALgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgAFwAIgAjAE4ALwBBAFwAIgAgAGkAZgAgAGwAbwBvAGsAdQBwAF8AdgBhAGwAdQBlAHMAIABhAHIAZQAgAG4AbwB0ACAAcAByAGUAcwBlAG4AdAAgAGkAbgAgAGwAbwBvAGsAdQBwAF8AYQByAHIAYQB5AC4AXABuACAAIAAgACAAIiAgAFUAcwBlAHMAIABYAE0AQQBUAEMASAAgAG8AdgBlAHIAIABUAE8AQwBPAEwAKABtAGEAdABjAGgAXwBhAHIAcgBhAHkAKQAgAGYAbwByACAAZgBsAGEAdAB0AGUAbgBlAGQAIABzAGUAYQByAGMAaAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBHAHIAaQBkAEwAbwBvAGsAdQBwALsDPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABsAG8AbwBrAHUAcABfAHYAYQBsAHUAZQBzACwAXABuACAAIAAgACAAbQBhAHQAYwBoAF8AYQByAHIAYQB5ACwAXABuACAAIAAgACAAcgBlAHQAdQByAG4AXwBhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkAF0ALABcAG4AIAAgACAAIABbAG0AYQB0AGMAaABfAG0AbwBkAGUAXQAsAFwAbgAgACAAIAAgAFsAcwBlAGEAcgBjAGgAXwBtAG8AZABlAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAcwBcAG4AIAAgACAAIABoAGUAaQBnAGgAdACBICwAIAAgACAAUgBPAFcAUwAoAG0AYQB0AGMAaABfAGEAcgByAGEAeQApACwAIAAgACAAIAAgAHcAaQBkAHQAaACBICwAIAAgAEMATwBMAFUATQBOAFMAKABtAGEAdABjAGgAXwBhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0AIIgLAAgACAAIABSAE8AVwBTACgAcgBlAHQAdQByAG4AXwBhAHIAcgBhAHkAKQAsACAAIAAgACAAdwBpAGQAdABoAIIgLAAgACAAQwBPAEwAVQBNAE4AUwAoAHIAZQB0AHUAcgBuAF8AYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMATQBhAHQAYwBoAD8ALAAgAE8AUgAoAGgAZQBpAGcAaAB0AIEgIAA8AD4AIABoAGUAaQBnAGgAdACCICwAdwBpAGQAdABoAIEgIAA8AD4AIAB3AGkAZAB0AGgAgiApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAYQByAGwAeQAgAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgAGkAZgAgAG0AZQBtAGIAZQByAHMAaABpAHAAIAA9ACAARgBBAEwAUwBFAFwAbgAgACAAIAAgAE4AbwB0AFAAcgBlAHMAZQBuAHQAPwAsACAAIAAgACAATgBPAFQAKABIAEEAUwBBAEwATAAoAG0AYQB0AGMAaABfAGEAcgByAGEAeQAsAGwAbwBvAGsAdQBwAF8AdgBhAGwAdQBlAHMAKQApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAE4AbwB0AFAAcgBlAHMAZQBuAHQAPwAsACMATgAvAEEALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABTAGgAYQBwAGUATQBpAHMATQBhAHQAYwBoAD8ALAAjAFYAQQBMAFUARQAhACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbABcAG4AIAAgACAAIABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAAsACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAaQBmAF8AbgBvAHQAXwBmAG8AdQBuAGQAKQAsAE4AQQAoACkALABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAApACwAXABuACAAIAAgACAAbQBhAHQAYwBoAF8AbQBvAGQAZQAsACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAG0AYQB0AGMAaABfAG0AbwBkAGUAKQAsADAALABtAGEAdABjAGgAXwBtAG8AZABlACkALABcAG4AIAAgACAAIABzAGUAYQByAGMAaABfAG0AbwBkAGUALAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcwBlAGEAcgBjAGgAXwBtAG8AZABlACkALAAxACwAcwBlAGEAcgBjAGgAXwBtAG8AZABlACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBhAHQAYwBoACAAcABvAGkAbgB0AHMAIABhAG4AZAAgAGkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAUgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAE0AQQBUAEMASAAoAGwAbwBvAGsAdQBwAF8AdgBhAGwAdQBlAHMALABUAE8AQwBPAEwAKABtAGEAdABjAGgAXwBhAHIAcgBhAHkAKQAsAG0AYQB0AGMAaABfAG0AbwBkAGUALABzAGUAYQByAGMAaABfAG0AbwBkAGUAKQAsAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUQBVAE8AVABJAEUATgBUACgAUgAgAC0AIAAxACwAdwBpAGQAdABoAIEgKQAgACsAIAAxACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAE8ARAAoAFIAIAAtACAAMQAsACAAdwBpAGQAdABoAIEgKQAgACsAMQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAcwB1AGwAdABcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgACAAIAAgAEkARgBOAEEAKABJAE4ARABFAFgAKAByAGUAdAB1AHIAbgBfAGEAcgByAGEAeQAsAGkALABqACkALABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAApACwAXABuACAAIAAgACAAXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAEIARABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIABOAGEAdgBpAGcAYQB0AGUAMgBEALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIABDAG8AbgB2AG8AbAB2AGUAuwMsACAARwByAGkAZABMAG8AbwBrAHUAcAC7AywAIABNAEcAcgBpAGQAuwMsACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEwAbwBjAGEAdABlAHMAIABhACAAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbAAgACgAMgBEACAAYQByAHIAYQB5ACkAIABpAG4AIABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQAIABhAG4AZAAgAHIAZQB0AHUAcgBuAHMAIABhACAAcwBoAGEAcABlACAAZgByAG8AbQAgAHQAaABlAFwAbgAgACAAIAAgAE0AbwBvAHIAZQAgAG4AZQBpAGcAaABiAG8AcgBoAG8AbwBkACAAcgBlAGwAYQB0AGkAdgBlACAAdABvACAAdABoAGUAIABtAGEAdABjAGgAIABsAG8AYwBhAHQAaQBvAG4ALgBcAG4AXABuACAAIAAgACAATQBvAG8AcgBlACAATgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAgACAAMgAgACAAIAAzAFwAbgAgACAAIAAgACAAIAAgACAANAAgACAAIAA1ACAAIAAgADYAXABuACAAIAAgACAAIAAgACAAIAA3ACAAIAAgADgAIAAgACAAOQBcAG4AIAAgACAAIABcAG4AIAAgACAAIAA1ACAAPQAgAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAIABpAG4AIABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQAXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbAAgACAAIAAgACAAIAAtACAAIAAgADIARAAgAHMAaABhAHAAZQAgAG8AcgAgAGEAcgByAGEAeQAgAHQAbwAgAGwAbwBjAGEAdABlAFwAbgAgACAAIAAgAG0AYQB0AGMAaABfAGEAcgByAGEAeQBfADIARAAgACAAIAAgACAALQAgACAAIAAyAEQAIABzAG8AdQByAGMAZQAgAGEAcgByAGEAeQAgAGkAbgAgAHcAaABpAGMAaAAgAHQAbwAgAGwAbwBjAGEAdABlACAAdABoAGUAIABrAGUAcgBuAGUAbABcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABbAHIAZQB0AHUAcgBuAF8AZABpAHIAZQBjAHQAaQBvAG4AXQAgAC0AIAAgACAASQBuAHQAZQBnAGUAcgAgACgAMQAgAHQAbwAgADkAKQAgAGkAbgBkAGkAYwBhAHQAaQBuAGcAIAB3AGgAaQBjAGgAIABNAG8AbwByAGUAIABuAGUAaQBnAGgAYgBvAHIAaABvAG8AZAAgAHQAbwAgAHIAZQB0AHUAcgBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAA4ACwAIABkAGkAcgBlAGMAdABsAHkAIABiAGUAbABvAHcAIAB0AGgAZQAgAG0AYQB0AGMAaABlAGQAIABrAGUAcgBuAGUAbAAuAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAFsAcgBlAHQAdQByAG4AXwBoAGUAaQBnAGgAdABdACAAIAAgACAALQAgACAAIABSAG8AdwBzACAAaQBuAGMAbAB1AGQAZQBkACAAaQBuACAAdABoAGUAIAByAGUAdAB1AHIAbgBcAG4AIAAgACAAIABbAHIAZQB0AHUAcgBuAF8AdwBpAGQAdABoAF0AIAAgACAAIAAgAC0AIAAgACAAQwBvAGwAdQBtAG4AcwAgAGkAbgBjAGwAdQBkAGUAZAAgAGkAbgAgAHQAaABlACAAcgBlAHQAdQByAG4AXABuAFwAbgAgACAAIAAgAEkAZgAgAGgAZQBpAGcAaAB0AC8AdwBpAGQAdABoACAAYQByAGUAIABvAG0AaQB0AHQAZQBkACAALQAgAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAGgAZQBpAGcAaAB0AC8AdwBpAGQAdABoACAAbwBmACAAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbABcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAiICAASQBmACAAYQBuACAAbwBwAHQAaQBvAG4AYQBsACAAYQByAGcAdQBtAGUAbgB0ACAAaQBzACAAYQBuACAAYQByAHIAYQB5ACAAbwByACAAcgBhAG4AZwBlACwAIABpAHQAcwAgAHQAbwBwAC0AbABlAGYAdAAgAHYAYQBsAHUAZQAgAGkAcwAgAHUAcwBlAGQALgBcAG4AIiAgAE4AdQBtAGUAcgBpAGMAIABvAHAAdABpAG8AbgBhAGwAIABhAHIAZwB1AG0AZQBuAHQAcwAgAGEAcgBlACAAcgBvAHUAbgBkAGUAZAAgAGQAbwB3AG4AIAB0AG8AIABpAG4AdABlAGcAZQByAHMAIAB3AGkAdABoACAASQBOAFQALgBcAG4AIiAgAEkAZgAgAG0AdQBsAHQAaQBwAGwAZQAgAGsAZQByAG4AZQBsACAAbQBhAHQAYwBoAGUAcwAgAGUAeABpAHMAdAAsACAAdABoAGUAIABmAGkAcgBzAHQAIABtAGEAdABjAGgAIABpAG4AIABHAHIAaQBkAEwAbwBvAGsAdQBwALsDIABzAGMAYQBuACAAbwByAGQAZQByACAAaQBzACAAdQBzAGUAZAAuACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAE4AYQB2AGkAZwBhAHQAZQAyAEQAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwALABcAG4AIAAgACAAIABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQALABcAG4AIAAgACAAIABbAHIAZQB0AHUAcgBuAF8AZABpAHIAZQBjAHQAaQBvAG4AXQAsAFwAbgAgACAAIAAgAFsAcgBlAHQAdQByAG4AXwBoAGUAaQBnAGgAdABdACwAXABuACAAIAAgACAAWwByAGUAdAB1AHIAbgBfAHcAaQBkAHQAaABdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAaQBuAHAAdQB0AHMAIAAtACAAcwBjAGEAbABhAHIAXABuACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMsACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAaQBuAHAAdQB0ACwASQBOAFQAKABJAE4ARABFAFgAKABpAG4AcAB1AHQALAAxACwAMQApACkAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAC0AIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAA4ACAAKABiAGUAbABvAHcAKQAgAGkAZgAgAG8AbQBpAHQAdABlAGQAXABuACAAIAAgACAAcgBlAHQAdQByAG4AXwBkAGkAcgBlAGMAdABpAG8AbgAsAE4AbwByAG0AYQBsAGkAegBlALsDKABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHIAZQB0AHUAcgBuAF8AZABpAHIAZQBjAHQAaQBvAG4AKQAsADgALAByAGUAdAB1AHIAbgBfAGQAaQByAGUAYwB0AGkAbwBuACkAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAHMAaABhAHAAZQBzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0AIEgLAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAbQBhAHQAYwBoAF8AYQByAHIAYQB5AF8AMgBEACkALAAgACAAIAB3AGkAZAB0AGgAgSAsACAAIABDAE8ATABVAE0ATgBTACgAbQBhAHQAYwBoAF8AYQByAHIAYQB5AF8AMgBEACkALABcAG4AIAAgACAAIABoAGUAaQBnAGgAdACCICwAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAKQAsACAAIAAgACAAdwBpAGQAdABoAIIgLAAgACAAQwBPAEwAVQBNAE4AUwAoAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAHMAaQB6AGUAXABuACAAIAAgACAAcgBlAHQAdQByAG4AXwBoAGUAaQBnAGgAdAAsACAAIAAgAE4AbwByAG0AYQBsAGkAegBlALsDKABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHIAZQB0AHUAcgBuAF8AaABlAGkAZwBoAHQAKQAsAGgAZQBpAGcAaAB0AIIgLAByAGUAdAB1AHIAbgBfAGgAZQBpAGcAaAB0ACkAKQAsAFwAbgAgACAAIAAgAHIAZQB0AHUAcgBuAF8AdwBpAGQAdABoACwAIAAgACAAIABOAG8AcgBtAGEAbABpAHoAZQC7AygASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAByAGUAdAB1AHIAbgBfAHcAaQBkAHQAaAApACwAdwBpAGQAdABoAIIgLAByAGUAdAB1AHIAbgBfAHcAaQBkAHQAaAApACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAvAC8AIABFAGEAcgBsAHkAIAB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABCAGEAZABLAGUAcgBuAGUAbAA/ACwAIAAgACAAIAAgACAATwBSACgAaABlAGkAZwBoAHQAgiAgAD4AIABoAGUAaQBnAGgAdACBICwAdwBpAGQAdABoAIIgIAA+ACAAdwBpAGQAdABoAIEgKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAEIAYQBkAEQAaQByAD8ALAAgACAAIAAgACAAIAAgACAAIABPAFIAKAByAGUAdAB1AHIAbgBfAGQAaQByAGUAYwB0AGkAbwBuACAAPAAgADEALAAgAHIAZQB0AHUAcgBuAF8AZABpAHIAZQBjAHQAaQBvAG4AIAA+ACAAOQApACwAXABuACAAIAAgACAAXABuACAAIAAgACAAQgBhAGQAUgBlAHQAdQByAG4APwAsACAAIAAgACAAIAAgAE8AUgAoAHIAZQB0AHUAcgBuAF8AaABlAGkAZwBoAHQAIAA8ACAAMQAsAHIAZQB0AHUAcgBuAF8AdwBpAGQAdABoACAAPAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIABOAG8AdAAyAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAaABlAGkAZwBoAHQAgSAgAD0AIAAxACwAIAB3AGkAZAB0AGgAgSAgAD0AIAAxACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAvAC8AIABFAGEAcgBsAHkAIABlAHgAaQB0ACAAaQBmACAAZgBpAHIAcwB0ACAAZQBsAGUAbQBlAG4AdAAgAGkAcwAgAG0AaQBzAHMAaQBuAGcAXABuACAAIAAgACAATgBvAHQAUAByAGUAcwBlAG4AdAA/ACwAIAAgACAAIAAgAE4ATwBUACgASABBAFMAQQBMAEwAKABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQALABsAG8AbwBrAHUAcABfAGsAZQByAG4AZQBsACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAE4AbwB0ADIARAA/ACwAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEIAYQBkAEsAZQByAG4AZQBsAD8ALAAjAE4ALwBBACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABCAGEAZABEAGkAcgA/ACwAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABCAGEAZABSAGUAdAB1AHIAbgA/ACwAIwBWAEEATABVAEUAIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAHQAUAByAGUAcwBlAG4AdAA/ACwAIwBOAC8AQQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABMAG8AYwBhAHQAaQBvAG4AXABuACAAIAAgACAATQBhAHQAYwBoAEsAZQByAG4AZQBsALsDLABMAEEATQBCAEQAQQAoAHYALABBAE4ARAAoAEYATABBAFQAVABFAE4AKAB2ACkAIAA9ACAAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbAApACkALABcAG4AIAAgACAAIABGAG8AdQBuAGQAPwAsACAAIAAgACAAIAAgAEMAbwBuAHYAbwBsAHYAZQC7AygAbQBhAHQAYwBoAF8AYQByAHIAYQB5AF8AMgBEACwAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbAAsAE0AYQB0AGMAaABLAGUAcgBuAGUAbAC7AykALABcAG4AIAAgACAAIABGAG8AdQBuAGQAMQBEAD8ALAAgACAAIAAgAE8AUgAoAFIATwBXAFMAKABGAG8AdQBuAGQAPwApACAAPQAgADEALABDAE8ATABVAE0ATgBTACgARgBvAHUAbgBkAD8AKQAgAD0AIAAxACkALAAgACAAIAAgAFwAbgAgACAAIAAgAE4AbwB0AEYAbwB1AG4AZAA/ACwAIAAgACAATgBPAFQAKABPAFIAKABGAG8AdQBuAGQAPwApACkALAAgAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgARgBvAHUAbgBkADEARAA/ACwAWABNAEEAVABDAEgAKABUAFIAVQBFACwARgBvAHUAbgBkAD8AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARwByAGkAZABMAG8AbwBrAHUAcAC7AygAVABSAFUARQAsAEYAbwB1AG4AZAA/ACwATQBHAHIAaQBkALsDKABGAG8AdQBuAGQAPwApACkAKQAsAFwAbgBcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEYAbwB1AG4AZAAxAEQAPwAsADEALABHAHIAaQBkAEwAbwBvAGsAdQBwALsDKABUAFIAVQBFACwARgBvAHUAbgBkAD8ALABNAEcAcgBpAGQAuwMoAEYAbwB1AG4AZAA/ACwAMQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAGkAbgB0AGUAcgBzAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAKAByAGUAdAB1AHIAbgBfAGQAaQByAGUAYwB0AGkAbwBuACwAIAAgACAAIABpACAALQAgAGgAZQBpAGcAaAB0AIIgLABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQAgAC0AIABoAGUAaQBnAGgAdACCICwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAIAAtACAAaABlAGkAZwBoAHQAgiAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpACAAKwAgAGgAZQBpAGcAaAB0AIIgLABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQAgACsAIABoAGUAaQBnAGgAdACCICwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAIAArACAAaABlAGkAZwBoAHQAgiApACwAXABuAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAKAByAGUAdAB1AHIAbgBfAGQAaQByAGUAYwB0AGkAbwBuACwAIAAgACAAIABqACAALQAgAHcAaQBkAHQAaACCICwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAagAgACsAIAB3AGkAZAB0AGgAgiAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABqACAALQAgAHcAaQBkAHQAaACCICwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAagAgACsAIAB3AGkAZAB0AGgAgiAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABqACAALQAgAHcAaQBkAHQAaACCICwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAagAgACsAIAB3AGkAZAB0AGgAgiApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGEAbgBzAGkAbwBuACAAawBlAHIAbgBlAGwAcwBcAG4AIAAgACAAIAByAF8AawBlAHIAbgBlAGwALAAgACAAIABSAGUAcwBpAHoAZQC7AygASQBGACgAcgBlAHQAdQByAG4AXwBoAGUAaQBnAGgAdAAgAD0AIAAxACwAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAByAGUAdAB1AHIAbgBfAGgAZQBpAGcAaAB0ACwALAAwACwAMQApACkALAAsAHIAZQB0AHUAcgBuAF8AdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAAYwBfAGsAZQByAG4AZQBsACwAIAAgACAAUgBlAHMAaQB6AGUAuwMoAEkARgAoAHIAZQB0AHUAcgBuAF8AdwBpAGQAdABoACAAPQAgADEALAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoACwAcgBlAHQAdQByAG4AXwB3AGkAZAB0AGgALAAwACwAMQApACkALAByAGUAdAB1AHIAbgBfAGgAZQBpAGcAaAB0ACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAvAC8AIABDAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAeAAgACsAIAByAF8AawBlAHIAbgBlAGwALABcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIAB5ACAAKwAgAGMAXwBrAGUAcgBuAGUAbAAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAGEAcgByAGEAeQAgAGkAcwAgAG8AZgBmACAAZwByAGkAZABcAG4AIAAgACAAIABPAGYAZgBHAHIAaQBkAD8ALAAgACAAIABPAFIAKABNAEkATgAoAHIAKQAgADwAIAAxACwATQBJAE4AKABjACkAIAA8ACAAMQAsAE0AQQBYACgAcgApACAAPgAgAGgAZQBpAGcAaAB0AIEgLABNAEEAWAAoAGMAKQAgAD4AIAB3AGkAZAB0AGgAgSApACwAXABuACAAIAAgACAAXABuACAAIAAgACAAbQBzAGcALAAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG4AZQBsADoAIABSAFwAIgAmAGkAJgBcACIAQwBcACIAJgBqACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgAEkARgAoAE4AbwB0AEYAbwB1AG4AZAA/ACwAIwBOAC8AQQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATwBmAGYARwByAGkAZAA/ACwAbQBzAGcALABJAE4ARABFAFgAKABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQALAByACwAYwApACkAKQAsAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AXABuACkAKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwA/AD8APwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIABNAGEAdABjAGgAMgBEALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIABDAG8AbgB2AG8AbAB2AGUAuwMsACAARwByAGkAZABMAG8AbwBrAHUAcAC7AywAIABNAEcAcgBpAGQAuwMsACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEwAbwBjAGEAdABlAHMAIABhACAAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbAAgACgAMgBEACAAYQByAHIAYQB5ACkAIABpAG4AIABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQAIABhAG4AZAAgAHIAZQB0AHUAcgBuAHMAIABhACAAcwBoAGEAcABlACAAZgByAG8AbQAgAHQAaABlAFwAbgAgACAAIAAgAE0AbwBvAHIAZQAgAG4AZQBpAGcAaABiAG8AcgBoAG8AbwBkACAAcgBlAGwAYQB0AGkAdgBlACAAdABvACAAdABoAGUAIABtAGEAdABjAGgAIABsAG8AYwBhAHQAaQBvAG4ALgBcAG4AXABuACAAIAAgACAATQBvAG8AcgBlACAATgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAgACAAMgAgACAAIAAzAFwAbgAgACAAIAAgACAAIAAgACAANAAgACAAIAA1ACAAIAAgADYAXABuACAAIAAgACAAIAAgACAAIAA3ACAAIAAgADgAIAAgACAAOQBcAG4AIAAgACAAIABcAG4AIAAgACAAIAA1ACAAPQAgAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAIABpAG4AIABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQAXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbAAgACAAIAAgACAAIAAtACAAIAAgADIARAAgAHMAaABhAHAAZQAgAG8AcgAgAGEAcgByAGEAeQAgAHQAbwAgAGwAbwBjAGEAdABlAFwAbgAgACAAIAAgAG0AYQB0AGMAaABfAGEAcgByAGEAeQBfADIARAAgACAAIAAgACAALQAgACAAIAAyAEQAIABzAG8AdQByAGMAZQAgAGEAcgByAGEAeQAgAGkAbgAgAHcAaABpAGMAaAAgAHQAbwAgAGwAbwBjAGEAdABlACAAdABoAGUAIABrAGUAcgBuAGUAbABcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAiICAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAE0AYQB0AGMAaAAyAEQAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwALABcAG4AIAAgACAAIABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABpAG4AcAB1AHQAcwAgAC0AIABzAGMAYQBsAGEAcgBcAG4AIAAgACAAIABOAG8AcgBtAGEAbABpAHoAZQC7AywAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABpAG4AcAB1AHQALABJAE4AVAAoAEkATgBEAEUAWAAoAGkAbgBwAHUAdAAsADEALAAxACkAKQApACwAXABuAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAHMAaABhAHAAZQBzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0AIEgLAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAbQBhAHQAYwBoAF8AYQByAHIAYQB5AF8AMgBEACkALAAgACAAIAB3AGkAZAB0AGgAgSAsACAAIABDAE8ATABVAE0ATgBTACgAbQBhAHQAYwBoAF8AYQByAHIAYQB5AF8AMgBEACkALABcAG4AIAAgACAAIABoAGUAaQBnAGgAdACCICwAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAKQAsACAAIAAgACAAdwBpAGQAdABoAIIgLAAgACAAQwBPAEwAVQBNAE4AUwAoAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAEUAYQByAGwAeQAgAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgAHMAYwBlAG4AYQByAGkAbwBcAG4AIAAgACAAIABCAGEAZABLAGUAcgBuAGUAbAA/ACwAIAAgACAAIAAgACAATwBSACgAaABlAGkAZwBoAHQAgiAgAD4AIABoAGUAaQBnAGgAdACBICwAdwBpAGQAdABoAIIgIAA+ACAAdwBpAGQAdABoAIEgKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAEUAYQByAGwAeQAgAGUAeABpAHQAIABpAGYAIABtAGUAbQBiAGUAcgBzAGgAaQBwACAAPQAgAEYAQQBMAFMARQBcAG4AIAAgACAAIABOAG8AdABQAHIAZQBzAGUAbgB0AD8ALAAgACAAIAAgACAATgBPAFQAKABIAEEAUwBBAEwATAAoAG0AYQB0AGMAaABfAGEAcgByAGEAeQBfADIARAAsAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABCAGEAZABLAGUAcgBuAGUAbAA/ACwAIwBOAC8AQQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AdABQAHIAZQBzAGUAbgB0AD8ALAAjAE4ALwBBACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBjAGEAdABpAG8AbgBcAG4AIAAgACAAIABNAGEAdABjAGgASwBlAHIAbgBlAGwAuwMsAEwAQQBNAEIARABBACgAdgAsAEEATgBEACgARgBMAEEAVABUAEUATgAoAHYAKQAgAD0AIABsAG8AbwBrAHUAcABfAGsAZQByAG4AZQBsACkAKQAsAFwAbgAgACAAIAAgAEYAbwB1AG4AZAA/ACwAIAAgACAAIAAgACAAQwBvAG4AdgBvAGwAdgBlALsDKABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQALABsAG8AbwBrAHUAcABfAGsAZQByAG4AZQBsACwATQBhAHQAYwBoAEsAZQByAG4AZQBsALsDKQAsACAAIABcAG4AIAAgACAAIABGAG8AdQBuAGQAMQBEAD8ALAAgACAAIAAgAE8AUgAoAFIATwBXAFMAKABGAG8AdQBuAGQAPwApACAAPQAgADEALABDAE8ATABVAE0ATgBTACgARgBvAHUAbgBkAD8AKQAgAD0AIAAxACkALAAgACAAXABuACAAIAAgACAATgBvAHQARgBvAHUAbgBkAD8ALAAgACAAIABOAE8AVAAoAE8AUgAoAEYAbwB1AG4AZAA/ACkAKQAsACAAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABGAG8AdQBuAGQAMQBEAD8ALABYAE0AQQBUAEMASAAoAFQAUgBVAEUALABGAG8AdQBuAGQAPwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABHAHIAaQBkAEwAbwBvAGsAdQBwALsDKABUAFIAVQBFACwARgBvAHUAbgBkAD8ALABNAEcAcgBpAGQAuwMoAEYAbwB1AG4AZAA/ACkAKQApACwAXABuAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgARgBvAHUAbgBkADEARAA/ACwAMQAsAEcAcgBpAGQATABvAG8AawB1AHAAuwMoAFQAUgBVAEUALABGAG8AdQBuAGQAPwAsAE0ARwByAGkAZAC7AygARgBvAHUAbgBkAD8ALAAxACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBvAHIAZABpAG4AYQB0AGUAcwAgAGYAcgBvAG0AIABpAC8AagAgAG0AYQB0AGMAaAAgAHAAbwBpAG4AdABcAG4AIAAgACAAIABxACwAIAAgACAAIAAgACAAIAAgACAAIAAgAFEAdQBhAGQAdwBpAHMAZQC7AygAaQAsAGoALABTAEUAUQBVAEUATgBDAEUAKABoAGUAaQBnAGgAdACCICwALAAwACwAMQApACwAUwBFAFEAVQBFAE4AQwBFACgAdwBpAGQAdABoAIIgLAAsADAALAAxACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAHUAbABsACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAZgBvAHIAIAAyAEQAIABrAGUAcgBuAGUAbAAgAG0AYQB0AGMAaABcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAVABBAEsARQAoAHEALAAsADEAKQAgACsAIABDAEgATwBPAFMARQBDAE8ATABTACgAcQAsADMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAcQAsADIAKQAgACsAIABUAEEASwBFACgAcQAsACwALQAxACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqAFsAVABCAEQAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFYAUwBwAGwAaQB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABUAEIARABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAHAAbABpAHQAcwAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABpAG4AdABvACAAaABvAHIAaQB6AG8AbgB0AGEAbAAgAHIAbwB3ABEgcwBlAGcAbQBlAG4AdABzACAAbwBmACAAcwBpAHoAZQAgAHMAcABsAGkAdABfAGkAbgB0AGUAcgB2AGEAbAAuAFwAbgAgACAAIAAgAFQAaABlACAAcgBlAHMAdQBsAHQAIABpAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABsAGkAcwB0AHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAALQAgAEEAIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIAB3AGgAbwBzAGUAIABkAGkAbQBlAG4AcwBpAG8AbgBzACAAZABlAHQAZQByAG0AaQBuAGUAIAB0AGgAZQAgAG8AdQB0AHAAdQB0ACAAcwBpAHoAZQAuAFwAbgAgACAAIAAgAHMAcABsAGkAdABfAGkAbgB0AGUAcgB2AGEAbAAgAC0AIABBAG4AIABpAG4AdABlAGcAZQByACAAZABlAHMAaQBnAG4AYQB0AGkAbgBnACAAdABvAHQAYQBsACAAcgBvAHcAIABpAG4AIABlAGEAYwBoACAAcwBlAGcAbQBlAG4AdABcAG4AXABuAE8AcAB0AGkAbwBuAGEAbABcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACAAIAAgACAALQAgAEYAaQBsAGwAIAB2AGEAbAB1AGUAIAB1AHMAZQBkACAAdABvACAAcABhAGQAIABlAHgAcABhAG4AZABlAGQAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABlAHEAdQBhAGwAIABzAGUAZwBtAGUAbgB0AHMALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAZgAgAG8AbQBpAHQAdABlAGQALAAgAGQAZQBmAGEAdQBsAHQAIAA9ACAAIwBOAC8AQQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVgBTAHAAbABpAHQAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAHMAcABsAGkAdABfAGkAbgB0AGUAcgB2AGEAbAAsAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwAXABuACAAIAAgACAAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACwAIABJAE4ARABFAFgAKABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwALAAxACwAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoAGUAaQBnAGgAdAAgAD0AIAAxACwAdwBpAGQAdABoACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAHgATgA/ACwAIAAgACAAIAAgACAAIAAgACAAaABlAGkAZwBoAHQAIAA9ACAAMQAsAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAUwBwAGwAaQB0AD8ALAAgACAATwBSACgASQBTAFQARQBYAFQAKABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwAKQAsAHMAcABsAGkAdABfAGkAbgB0AGUAcgB2AGEAbAAgADwAPQAgADAAKQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABPAFIAKABJAHMAUwBjAGEAbABhAHIAPwAsAEkAcwAxAHgATgA/ACkALAB7AGEAcgByAGEAeQB9ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAFMAcABsAGkAdAA/ACwAIwBWAEEATABVAEUAIQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFAAYQBkACAAYQByAHIAYQB5ACAAdABvACAAcAByAGUAdgBlAG4AdAAgAHUAbgBlAHYAZQBuACAAcABhAHIAdABpAHQAaQBvAG4AcwBcAG4AIAAgACAAIABwAGEAZABfAHcAaQB0AGgALAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABwAGEAZABfAHcAaQB0AGgAKQAsAE4AQQAoACkALABJAE4ARABFAFgAKABwAGEAZABfAHcAaQB0AGgALAAxACwAMQApACkALABcAG4AIAAgACAAIABQAGEAZABSAG8AdwBzACwAIAAgACAAIAAgACAATQBPAEQAKAAtAGgAZQBpAGcAaAB0ACwAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACkALABcAG4AIAAgACAAIABuAGUAdwBfAGEAcgByAGEAeQAsACAAIAAgACAARQBYAFAAQQBOAEQAKABhAHIAcgBhAHkALABoAGUAaQBnAGgAdAAgACsAIABQAGEAZABSAG8AdwBzACwALABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAG4AYwBoAG8AcgBzACAAKwAgAHIAbwB3ACAAYQBkAGoAdQBzAHQAbQBlAG4AdABzAFwAbgAgACAAIAAgAGEAbgBjAGgAbwByAHMALAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAoAFAAYQBkAFIAbwB3AHMAIAArACAAaABlAGkAZwBoAHQAKQAgAC8AIABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwALAAsADEALABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwAKQAsAFwAbgAgACAAIAAgAHMAdABlAHAALAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwALAAsADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHAAbABpAHQAIABtAGEAdAByAGkAeAAgAGkAbgB0AG8AIABwAGEAcgB0AHMAXABuACAAIAAgACAAUABhAHIAdAC7AywAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAGQAeAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgAsACAAIAAgACAAIABpAGQAeAAgACsAIABzAHQAZQBwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAGEAcgB0ACwAIAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABuAGUAdwBfAGEAcgByAGEAeQAsAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABhAHIAdAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIABhAHMAIABsAGkAcwB0AHMAXABuACAAIAAgACAAbABpAHMAdABzACwAIAAgACAAIAAgACAAIAAgAE0AQQBQACgAYQBuAGMAaABvAHIAcwAsAFAAYQByAHQAuwMpACwAXABuACAAIAAgACAAbABpAHMAdABzAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgAvACoAWwBUAEIARABdAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAASABTAHAAbABpAHQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAFQAQgBEAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFMAcABsAGkAdABzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABoAG8AcgBpAHoAbwBuAHQAYQBsACAAYwBvAGwAdQBtAG4AESBzAGUAZwBtAGUAbgB0AHMAIABvAGYAIABzAGkAegBlACAAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsAC4AXABuACAAIAAgACAAVABoAGUAIAByAGUAcwB1AGwAdAAgAGkAcwAgAGEAbgAgAGEAcgByAGEAeQAgAG8AZgAgAGwAaQBzAHQAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAtACAAQQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAGUAdABlAHIAbQBpAG4AZQAgAHQAaABlACAAbwB1AHQAcAB1AHQAIABzAGkAegBlAC4AXABuACAAIAAgACAAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACAALQAgAEEAbgAgAGkAbgB0AGUAZwBlAHIAIABkAGUAcwBpAGcAbgBhAHQAaQBuAGcAIAB0AG8AdABhAGwAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAZQBhAGMAaAAgAHMAZQBnAG0AZQBuAHQAXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAAIAAgAC0AIABGAGkAbABsACAAdgBhAGwAdQBlACAAdQBzAGUAZAAgAHQAbwAgAHAAYQBkACAAZQB4AHAAYQBuAGQAZQBkACAAYQByAHIAYQB5AHMAIABpAG4AdABvACAAZQBxAHUAYQBsACAAcwBlAGcAbQBlAG4AdABzAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIABkAGUAZgBhAHUAbAB0ACAAPQAgACMATgAvAEEAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4ASABTAHAAbABpAHQAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAHMAcABsAGkAdABfAGkAbgB0AGUAcgB2AGEAbAAsAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwAXABuACAAIAAgACAAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACwAIABJAE4ARABFAFgAKABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwALAAxACwAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoAGUAaQBnAGgAdAAgAD0AIAAxACwAdwBpAGQAdABoACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBOAHgAMQA/ACwAIAAgACAAIAAgACAAIAAgACAAdwBpAGQAdABoACAAPQAgADEALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAFMAcABsAGkAdAA/ACwAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACkALABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwAIAA8AD0AIAAwACkALABcAG4AXABuACAAIAAgACAASQBGACgATwBSACgASQBzAFMAYwBhAGwAYQByAD8ALABJAHMATgB4ADEAPwApACwAewBhAHIAcgBhAHkAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABTAHAAbABpAHQAPwAsACMAVgBBAEwAVQBFACEALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABQAGEAZAAgAGEAcgByAGEAeQAgAHQAbwAgAHAAcgBlAHYAZQBuAHQAIAB1AG4AZQB2AGUAbgAgAHAAYQByAHQAaQB0AGkAbwBuAHMAXABuACAAIAAgACAAcABhAGQAXwB3AGkAdABoACwAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcABhAGQAXwB3AGkAdABoACkALABOAEEAKAApACwASQBOAEQARQBYACgAcABhAGQAXwB3AGkAdABoACwAMQAsADEAKQApACwAXABuACAAIAAgACAAUABhAGQAQwBvAGwAcwAsACAAIAAgACAAIAAgAE0ATwBEACgALQB3AGkAZAB0AGgALABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwAKQAsAFwAbgAgACAAIAAgAG4AZQB3AF8AYQByAHIAYQB5ACwAIAAgACAAIABFAFgAUABBAE4ARAAoAGEAcgByAGEAeQAsACwAdwBpAGQAdABoACAAKwAgAFAAYQBkAEMAbwBsAHMALABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAG4AYwBoAG8AcgBzACAAKwAgAHIAbwB3ACAAYQBkAGoAdQBzAHQAbQBlAG4AdABzAFwAbgAgACAAIAAgAGEAbgBjAGgAbwByAHMALAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAoAFAAYQBkAEMAbwBsAHMAIAArACAAdwBpAGQAdABoACkAIAAvACAAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACwALAAxACwAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACkALABcAG4AIAAgACAAIABzAHQAZQBwACwAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACwALAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBwAGwAaQB0ACAAbQBhAHQAcgBpAHgAIABpAG4AdABvACAAcABhAHIAdABzAFwAbgAgACAAIAAgAFAAYQByAHQAuwMsACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQBkAHgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIALAAgACAAIAAgACAAaQBkAHgAIAArACAAcwB0AGUAcAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABhAHIAdAAsACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAbgBlAHcAXwBhAHIAcgBhAHkALAByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAYQByAHQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAYQBzACAAbABpAHMAdABzAFwAbgAgACAAIAAgAGwAaQBzAHQAcwAsACAAIAAgACAAIAAgACAAIABNAEEAUAAoAGEAbgBjAGgAbwByAHMALABQAGEAcgB0ALsDKQAsAFwAbgAgACAAIAAgAGwAaQBzAHQAcwBcAG4AKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8ALwAgAFUAbgBjAGgAYQBuAGcAZQBkACAAZgB1AG4AYwB0AGkAbwBuAHMAIABjAGEAbABsAGUAZAAgAGIAeQAgAHQAaABlACAAZgB1AG4AYwB0AGkAbwBuAHMAIABhAGIAbwB2AGUALgBcAG4AXABuAC8AKgBbAEcAVwAwADMAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAE0ARwByAGkAZAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAB3AG8AcgBrAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAcgBvAHcAESBpAG4AZABlAHgAIABvAHIAIABjAG8AbAB1AG0AbgARIGkAbgBkAGUAeAAgAGcAcgBpAGQAcwAgAG0AYQB0AGMAaABpAG4AZwAgAHQAaABlACAAcwBoAGEAcABlACAAbwBmACAAYQAgAHMAdQBwAHAAbABpAGUAZABcAG4AIAAgACAAIABhAHIAcgBhAHkALgAgAFQAaABpAHMAIABpAHMAIAB0AGgAZQAgAEUAeABjAGUAbAAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABvAGYAIABNAEEAVABMAEEAQgAZIHMAIABtAGUAcwBoAGcAcgBpAGQAIABvAHIAIABOAHUAbQBQAHkAGSBzACAAaQBuAGQAaQBjAGUAcwAuAFwAbgBcAG4AIAAgACAAIABCAHkAIABkAGUAZgBhAHUAbAB0ACwAIABNAEcAcgBpAGQAuwMgAHIAZQB0AHUAcgBuAHMAIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMALgAgAFcAaABlAG4AIAB0AGgAZQAgAG8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByACAAaQBzACAAVABSAFUARQAsAFwAbgAgACAAIAAgAGkAdAAgAHIAZQB0AHUAcgBuAHMAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAIABpAG4AcwB0AGUAYQBkAC4AXABuAFwAbgAgACAAIAAgAFcAbwByAGsAcwAgAGYAbwByACAAYgBvAHQAaAAgADEARAAgAGEAbgBkACAAMgBEACAAYQByAHIAYQB5AHMALgAgAE8AdQB0AHAAdQB0ACAAYQBsAHcAYQB5AHMAIABtAGEAdABjAGgAZQBzACAAdABoAGUAIABnAGUAbwBtAGUAdAByAHkAIABvAGYAIAB0AGgAZQBcAG4AIAAgACAAIABpAG4AcAB1AHQAIABnAHIAaQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAZwByAGkAZAAgACAAIAAgACAAIAAgACAALQAgAEEAIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIAB3AGgAbwBzAGUAIABkAGkAbQBlAG4AcwBpAG8AbgBzACAAZABlAHQAZQByAG0AaQBuAGUAIAB0AGgAZQAgAG8AdQB0AHAAdQB0ACAAcwBpAHoAZQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBNAEcAcgBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABSAG8AdwBJAGQAeAA/ACwAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGkAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAZQByAHIAZQBkACAAaQBuAGQAZQB4ACAAZwByAGkAZABzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUgBlAHMAaQB6AGUAuwMoAFMARQBRAFUARQBOAEMARQAoAGgAKQAsACwAdwApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAAsAHcAKQAsAGgAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAASQBGACgAUgBvAHcASQBkAHgAPwAsACAAaQAoACkALAAgAGoAKAApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAQgBEAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAcABlAGEAdABzACAAZQBhAGMAaAAgAHIAbwB3ACAAbwBmACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgAGEAcgByAGEAeQAgAGEAYwBjAG8AcgBkAGkAbgBnACAAdABvACAAYQAgAHYAZQBjAHQAbwByACAAbwBmACAAcgBlAHAAZQBhAHQAXABuACAAIAAgACAAYwBvAHUAbgB0AHMALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAHUAcABwAG8AcgB0AGUAZAAuACAAUgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgAG0AdQBzAHQAIABiAGUAIABuAHUAbQBlAHIAaQBjAFwAbgAgACAAIAAgAGEAbgBkACAAZSIgADEALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAcgBvAHcAcwAgAHcAaQBsAGwAIABiAGUAIAByAGUAcABlAGEAdABlAGQALgBcAG4AIAAgACAAIAByAGUAcABlAGEAdAAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5ACAAbwBmACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgACgAbgB1AG0AZQByAGkAYwAsACAAZSIgADEAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAHIAZQBwAGUAYQB0ACAAaABhAHMAIABmAGUAdwBlAHIAIABlAG4AdAByAGkAZQBzACAAdABoAGEAbgAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIAByAG8AdwBzACwAIAB0AGgAZQAgAGwAYQBzAHQAIAByAGUAcABlAGEAdABcAG4AIAAgACAAIAAgACAAdgBhAGwAdQBlACAAaQBzACAAZQB4AHQAZQBuAGQAZQBkACAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIABhAHIAcgBhAHkAIABoAGUAaQBnAGgAdAAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAHAAcgBlAHMAZQByAHYAZQBzACAAdABoAGUAIABjAG8AbAB1AG0AbgAgAHMAdAByAHUAYwB0AHUAcgBlACAAbwBmACAAdABoAGUAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUgBlAHAAZQBhAHQAUgBvAHcAcwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIAByAGUAcABlAGEAdAAsAFwAbgBcAG4ASQBGACgATwBSACgASQBTAFQARQBYAFQAKAByAGUAcABlAGEAdAApACwAIAByAGUAcABlAGEAdAAgADwAPQAgADAAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAHIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAXABuACAAIAAgACAAcgBlAHAAZQBhAHQALAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAQQBoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABSAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AGUAbgBkACAAcgBlAHAAZQBhAHQAIAB2AGUAYwB0AG8AcgAgAGkAZgAgAG4AZQBlAGQAZQBkAFwAbgAgACAAIAAgAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQBoACAAPAA+ACAAUgBoACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAcgBlAHAAZQBhAHQALAAgAEEAaAAsACAALAAgAEAAVABBAEsARQAoAHIAZQBwAGUAYQB0ACwAIAAtADEAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBwAGUAYQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBhAHMAZQAgAHIAbwB3ACAAaQBuAGQAaQBjAGUAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAFIATwBXAFMAKAByACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGEAeABpAG0AdQBtACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAXABuACAAIAAgACAAbQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAHUAaQBsAGQAIABpAG4AZABlAHgAIAB2AGUAYwB0AG8AcgBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAVABPAEMATwBMACgASQBGACgAUwBJAEcATgAoAHIAIAAtACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAG0ALAAgADAAKQApACAAPQAgADEALABpACwATgBBACgAKQApACwAMgApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQBSAE8AVwBTACgAYQByAHIAYQB5ACwAIABpAGQAeAAoACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABSAGUAcABlAGEAdABDAG8AbABzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABUAEIARABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBwAGUAYQB0AHMAIABlAGEAYwBoACAAYwBvAGwAdQBtAG4AIABvAGYAIABhACAAcwB1AHAAcABsAGkAZQBkACAAYQByAHIAYQB5ACAAYQBjAGMAbwByAGQAaQBuAGcAIAB0AG8AIABhACAAdgBlAGMAdABvAHIAIABvAGYAIAByAGUAcABlAGEAdABcAG4AIAAgACAAIABjAG8AdQBuAHQAcwAuACAAUwBjAGEAbABhAHIAcwAgAGEAbgBkACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAHMAdQBwAHAAbwByAHQAZQBkAC4AIABSAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAbQB1AHMAdAAgAGIAZQAgAG4AdQBtAGUAcgBpAGMAXABuACAAIAAgACAAYQBuAGQAIABlIiAAMQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAB3AGgAbwBzAGUAIABjAG8AbAB1AG0AbgBzACAAdwBpAGwAbAAgAGIAZQAgAHIAZQBwAGUAYQB0AGUAZAAuAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAKABuAHUAbQBlAHIAaQBjACwAIABlIiAAMQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAASQBmACAAcgBlAHAAZQBhAHQAIABoAGEAcwAgAGYAZQB3AGUAcgAgAGUAbgB0AHIAaQBlAHMAIAB0AGgAYQBuACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGMAbwBsAHUAbQBuAHMALAAgAHQAaABlACAAbABhAHMAdAAgAHIAZQBwAGUAYQB0AFwAbgAgACAAIAAgACAAIAB2AGEAbAB1AGUAIABpAHMAIABlAHgAdABlAG4AZABlAGQAIAB0AG8AIABtAGEAdABjAGgAIAB0AGgAZQAgAGEAcgByAGEAeQAgAHcAaQBkAHQAaAAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAHAAcgBlAHMAZQByAHYAZQBzACAAdABoAGUAIAByAG8AdwAgAHMAdAByAHUAYwB0AHUAcgBlACAAbwBmACAAdABoAGUAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUgBlAHAAZQBhAHQAQwBvAGwAcwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIAByAGUAcABlAGEAdAAsAFwAbgBcAG4ASQBGACgATwBSACgASQBTAFQARQBYAFQAKAByAGUAcABlAGEAdAApACwAIAByAGUAcABlAGEAdAAgADwAPQAgADAAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAHIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAXABuACAAIAAgACAAcgBlAHAAZQBhAHQALAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAQQB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABSAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AGUAbgBkACAAcgBlAHAAZQBhAHQAIAB2AGUAYwB0AG8AcgAgAGkAZgAgAG4AZQBlAGQAZQBkAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQB3ACAAPAA+ACAAUgBoACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAcgBlAHAAZQBhAHQALAAgAEEAdwAsACAALAAgAEAAVABBAEsARQAoAHIAZQBwAGUAYQB0ACwAIAAtADEAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBwAGUAYQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBhAHMAZQAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAFIATwBXAFMAKABjACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGEAeABpAG0AdQBtACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAXABuACAAIAAgACAAbQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAGMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAHUAaQBsAGQAIABpAG4AZABlAHgAIAB2AGUAYwB0AG8AcgBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAVABPAEMATwBMACgASQBGACgAUwBJAEcATgAoAGMAIAAtACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAG0ALAAgADAAKQApACAAPQAgADEALABpACwATgBBACgAKQApACwAMgApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAYQByAHIAYQB5ACwAIABpAGQAeAAoACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABSAGUAcwBpAHoAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAcABlAGEAdABzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAHYAZQByAHQAaQBjAGEAbABsAHkAIABhAG4AZAAvAG8AcgAgAGgAbwByAGkAegBvAG4AdABhAGwAbAB5ACAAYgB5ACAAaQBuAHQAZQBnAGUAcgAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AHMALgBcAG4AIAAgACAAIABVAHMAZQByAHMAIABtAGEAeQAgAHMAcABlAGMAaQBmAHkAIABoAGUAaQBnAGgAdAAsACAAdwBpAGQAdABoACwAIABvAHIAIABiAG8AdABoAC4AIABJAGYAIABlAGkAdABoAGUAcgAgAHAAYQByAGEAbQBlAHQAZQByACAAaQBzACAAbwBtAGkAdAB0AGUAZAAsAFwAbgAgACAAIAAgAHQAaABlACAAbwBtAGkAdAB0AGUAZAAgAGQAaQBtAGUAbgBzAGkAbwBuACAAZABlAGYAYQB1AGwAdABzACAAdABvACAAMQAuACAARwBlAG8AbQBlAHQAcgB5ACAAaQBzACAAcAByAGUAcwBlAHIAdgBlAGQAOwAgAG4AbwAgAGYAbABhAHQAdABlAG4AaQBuAGcAXABuACAAIAAgACAAbwBjAGMAdQByAHMALgBcAG4AXABuAEUAeABhAG0AcABsAGUAOgBcAG4AIAAgACAAIABJAG4AcAB1AHQAOgBcAG4AIAAgACAAIAAgACAAIAAgAHsAMQAsADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAMwAsADQAfQBcAG4AXABuACAAIAAgACAAPQBSAGUAcwBpAHoAZQC7AygAYQByAHIAYQB5ACwAIAAyACwAIAAzACkAXABuAFwAbgAgACAAIAAgAE8AdQB0AHAAdQB0ADoAXABuACAAIAAgACAAIAAgACAAIAB7ADEALAAyACwAMQAsADIALAAxACwAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAzACwANAAsADMALAA0ACwAMwAsADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAMQAsADIALAAxACwAMgAsADEALAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgADMALAA0ACwAMwAsADQALAAzACwANAB9AFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAgAHQAbwAgAGIAZQAgAHIAZQBwAGUAYQB0AGUAZAAuAFwAbgAgACAAIAAgAFsAaABlAGkAZwBoAHQAXQAgACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHYAZQByAHQAaQBjAGEAbAAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAxAC4AXABuACAAIAAgACAAWwB3AGkAZAB0AGgAXQAgACAAIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAaABvAHIAaQB6AG8AbgB0AGEAbAAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAxAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHAAZQB0AGkAdABpAG8AbgAgAGkAcwAgAHAAZQByAGYAbwByAG0AZQBkACAAdgBpAGEAIABpAG4AZABlAHgAIAByAGUAbQBhAHAAcABpAG4AZwAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAGcAZQBvAG0AZQB0AHIAeQAgAGkAcwAgACgAaAAgANcAIABoAGUAaQBnAGgAdAApACAAYgB5ACAAKAB3ACAA1wAgAHcAaQBkAHQAaAApAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAZQBzAGkAegBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAaABlAGkAZwBoAHQAXQAsAFwAbgAgACAAIAAgAFsAdwBpAGQAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AbQBpAHMAcwBpAG8AbgAgAGMAaABlAGMAawBzAFwAbgAgACAAIAAgAEgAZQBpAGcAaAB0AE8AbQBpAHQAdABlAGQAPwAsACAAIABJAFMATwBNAEkAVABUAEUARAAoAGgAZQBpAGcAaAB0ACkALABcAG4AIAAgACAAIABXAGkAZAB0AGgATwBtAGkAdAB0AGUAZAA/ACwAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKAB3AGkAZAB0AGgAKQAsAFwAbgAgACAAIAAgAE4AbwBIAFcASQBuAHAAdQB0AD8ALAAgACAAIAAgACAAIABIAGUAaQBnAGgAdABPAG0AaQB0AHQAZQBkAD8AIAArACAAVwBpAGQAdABoAE8AbQBpAHQAdABlAGQAPwAgAD0AIAAyACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABOAG8ASABXAEkAbgBwAHUAdAA/ACwAIABIAGUAaQBnAGgAdABPAG0AaQB0AHQAZQBkAD8AKQAsACAAMQAsACAAaABlAGkAZwBoAHQAKQAsAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABOAG8ASABXAEkAbgBwAHUAdAA/ACwAIABXAGkAZAB0AGgATwBtAGkAdAB0AGUAZAA/ACkALAAgADEALAAgAHcAaQBkAHQAaAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAE4AbwBSAGUAcABlAGEAdAA/ACwAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAZQBpAGcAaAB0ACAAPQAgADEALAAgAHcAaQBkAHQAaAAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAARQB4AHAAYQBuAGQAUwBjAGEAbABhAHIALAAgACAAIAAgAEUAWABQAEEATgBEACgAYQByAHIAYQB5ACwAIABoAGUAaQBnAGgAdAAsACAAdwBpAGQAdABoACwAIABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAFIAZQBwAGUAYQB0AD8ALAAgACAATwBSACgASQBTAFQARQBYAFQAKABoAGUAaQBnAGgAdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBUAEUAWABUACgAdwBpAGQAdABoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAQQBOAEQAKABJAFMATgBVAE0AQgBFAFIAKABoAGUAaQBnAGgAdAApACwAIABoAGUAaQBnAGgAdAAgADwAPQAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAEkAUwBOAFUATQBCAEUAUgAoAHcAaQBkAHQAaAApACwAIAAgAHcAaQBkAHQAaAAgADwAPQAgADAAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABOAG8AUgBlAHAAZQBhAHQAPwAsACAAYQByAHIAYQB5ACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAEUAeABwAGEAbgBkAFMAYwBhAGwAYQByACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAFIAZQBwAGUAYQB0AD8ALAAgAGEAcgByAGEAeQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AZABlAGQAIABkAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGsALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABoACAAKgAgAGgAZQBpAGcAaAB0ACwAXABuACAAIAAgACAAawCCICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHcAIAAqACAAdwBpAGQAdABoACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBkAGkAYwBlAHMAIAAoAGQAZQBmAGUAcgByAGUAZAApAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoADEAIAArACAATQBPAEQAKABTAEUAUQBVAEUATgBDAEUAKABrACwALAAwACwAKQAsACAAaAApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAIABrAIIgLAAgADEALAAgADAAKQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAMQAgACsAIABNAE8ARAAoAFMARQBRAFUARQBOAEMARQAoACwAIABrAIIgLAAgADAAKQAsACAAdwApACAAKgAgAFMARQBRAFUARQBOAEMARQAoAGsALAAsACAAMQAsACAAMAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG4AcwB0AHIAdQBjAHQAIAByAGUAcABlAGEAdABlAGQAIABhAHIAcgBhAHkAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAaQAoACkALAAgAGoAKAApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApADsAXABuAFwAbgBcAG4ALwAvACAARQBuAGQAIABvAGYAIABNAG8AZAB1AGwAZQAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBNAGEAZwBuAGkAZgB5ALsDIgAsACIAQQBsAGkAZwBuAFIAbwB3AHMAuwMiACwAIgBBAGwAaQBnAG4AQwBvAGwAcwC7AyIALAAiAEYAbwBsAGQAuwMiACwAIgBaAGkAcAC7AyIALAAiAFAAYQBpAHIAdwBpAHMAZQC7AyIALAAiAFQAcgBpAHAAbABlAHcAaQBzAGUAuwMiACwAIgBRAHUAYQBkAHcAaQBzAGUAuwMiACwAIgBFAGMAaABvALsDIgAsACIAQgBsAG8AYwBrAHMAuwMiACwAIgBXAGkAbgBkAG8AdwBlAGQAuwMiACwAIgBDAG8AbgB2AG8AbAB2AGUAuwMiACwAIgBHAHIAaQBkAEwAbwBvAGsAdQBwALsDIgAsACIATgBhAHYAaQBnAGEAdABlADIARAC7AyIALAAiAE0AYQB0AGMAaAAyAEQAuwMiACwAIgBWAFMAcABsAGkAdAC7AyIALAAiAEgAUwBwAGwAaQB0ALsDIgAsACIATQBHAHIAaQBkALsDIgAsACIAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AyIALAAiAFIAZQBwAGUAYQB0AEMAbwBsAHMAuwMiACwAIgBSAGUAcwBpAHoAZQC7AyIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIATQBEAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuACAAIABfAF8AXwBfACAAIAAgACAAXwAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAF8AXwBfAF8AIAAgACAAIAAgACAAIAAgACAAIAAgAF8AIAAgACAAXwAgACAAIABfACAAXABuACAAfAAgACAAXwAgAFwAXAAgACAAKABfACkAIAAgACAAIAAgACAAIAAgACAAIAAvACAAXwBfAF8AXwB8ACAAIAAgACAAIAAgACAAIAAgACgAXwApACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAfABfACkAIAB8ACAAIABfACAAIAAgACAAXwBfACAAXwAgACAAfAAgACgAXwBfAF8AIAAgACAAIABfACAAXwBfACAAIAAgACAAXwAgACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAIABfACAAPAAgACAAfAAgAHwAIAAgAC8AIABfAGAAIAB8ACAAIABcAFwAXwBfAF8AIABcAFwAIAAgAHwAIAAnAF8AIABcAFwAIAAgAHwAIAB8ACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8ACAAfABfACkAIAB8ACAAfAAgAHwAIAB8ACAAKABfAHwAIAB8ACAAIABfAF8AXwBfACkAIAB8ACAAfAAgAHwAXwApACAAfAAgAHwAIAB8ACAAfAAgAHwAIAB8ACAAfABcAG4AIAB8AF8AXwBfAF8ALwAgACAAfABfAHwAIAAgAFwAXABfAF8ALAAgAHwAIAB8AF8AXwBfAF8AXwAvACAAIAB8ACAALgBfAF8ALwAgACAAfABfAHwAIAB8AF8AfAAgAHwAXwB8AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABfAF8ALwAgAHwAIAAgACAAIAAgACAAIAAgACAAIAB8ACAAfAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAfABfAF8AXwAvACAAIAAgACAAIAAgACAAIAAgACAAIAB8AF8AfAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgBcAG4ATQBvAGQAdQBsAGUAOgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEIAaQBnAFMAcABpAGwAbAAgAEEATABQAEgAQQBcAG4ATABpAGMAZQBuAHMAZQA6ACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBUACAAKABzAGUAZQAgAEwASQBDAEUATgBTAEUAIABmAGkAbABlACkAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBEAGEAdABlADoAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAMQAwAC8ANgAvADIAMAAyADYAXABuAFwAbgBHAGkAcwB0ACAAKABJAG0AcABvAHIAdAAgAG8AbgBsAHkAKQA6ACAAaAB0AHQAcABzADoALwAvAGcAaQBzAHQALgBnAGkAdABoAHUAYgAuAGMAbwBtAC8AUABhAHQAcgBpAGMAawAyADcAOAA4AC8AYQAxADIANgA1ADAANABmADkAYQAzAGYANABjADkAZgBhAGQAOAA3ADEANQBjAGEAMgA1ADgANwAzADAANgBlAFwAbgBcAG4AQQAgAGMAbwBsAGwAZQBjAHQAaQBvAG4AIABvAGYAIABCAGkAZwBTAHAAaQBsAGwAIABmAHUAbgBjAHQAaQBvAG4AcwAgAHIAZQB2AGkAcwBlAGQAIAB0AG8AIABsAGUAdgBlAHIAYQBnAGUAIABzAHUAcABwAG8AcgB0ACAAbwBmACAAbgBlAHMAdABlAGQAIABhAHIAcgBhAHkAcwAuAFwAbgBUAGgAZQBzAGUAIABhAHIAZQAgAHcAbwByAGsAaQBuAGcAIABwAHIAbwB0AG8AdAB5AHAAZQBzACAAYQBuAGQAIABzAGgAbwB1AGwAZAAgAG4AbwB0ACAAYgBlACAAYwBvAG4AcwBpAGQAZQByAGUAZAAgAGYAaQBuAGEAbAAuAFwAbgBcAG4AfAAgAFMAaQBtAHAAbABpAGYAaQBlAGQAIABmAHUAbgBjAHQAaQBvAG4AcwAgAHwAXABuAFwAbgBNAGEAZwBuAGkAZgB5ALsDIAAgACAAIAAtACAARQB4AHAAYQBuAGQAcwAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAaQBuAHQAbwAgAGEAIABkAGUAcAB0AGgA1wB3AGkAZAB0AGgAIABiAGwAbwBjAGsALgBcAG4AXABuAEEAbABpAGcAbgBSAG8AdwBzALsDIAAgAC0AIABTAG8AcgB0AHMAIABlAGEAYwBoACAAcgBvAHcAIABhAGwAcABoAGEAYgBlAHQAaQBjAGEAbABsAHkAIABvAHIAIABiAHkAIABzAG8AcgB0ACAAbwByAGQAZQByAC4AIABSAGUAdgBpAHMAZQBkACAAQQBsAGkAZwBuALsDLgBcAG4AXABuAEEAbABpAGcAbgBDAG8AbABzALsDIAAgAC0AIABTAG8AcgB0AHMAIABlAGEAYwBoACAAYwBvAGwAdQBtAG4AIABhAGwAcABoAGEAYgBlAHQAaQBjAGEAbABsAHkAIABvAHIAIABiAHkAIABzAG8AcgB0ACAAbwByAGQAZQByAC4AIABSAGUAdgBpAHMAZQBkACAAQQBsAGkAZwBuALsDLgBcAG4AXABuAEYAbwBsAGQAuwMgACAAIAAgACAAIAAgAC0AIABHAHIAbwB1AHAAcwAgAGkAZABlAG4AdABpAGMAYQBsACAAcgBvAHcAcwAgAGEAbgBkACAAYQBwAHAAbABpAGUAcwAgAGEAbgAgAGEAZwBnAHIAZQBnAGEAdABpAG8AbgAgAHIAZQBkAHUAYwBlAHIALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEYAYQBzAHQAZQByACAAdgBpAGEAIABzAGkAbQBwAGwAaQBmAGkAZQBkACAAQQBsAGkAZwBuAFIAbwB3AHMAuwMuAFwAbgBcAG4AWgBpAHAAuwMgACAAIAAgACAAIAAgACAALQAgAFoAaQBwAHMAIAAxABMgNAAgAGEAcgByAGEAeQBzACAAaQBuAHQAbwAgAHIAbwB3ABEgcgBlAGMAbwByAGQAcwAuACAATgBvAHcAIAByAGUAdAB1AHIAbgBzACAAYQAgAGwAaQBzAHQALgBcAG4AXABuAFAAYQBpAHIAdwBpAHMAZQC7AyAAIAAgAC0AIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAYQBpAHIAaQBuAGcAIABvAGYAIAB0AHcAbwAgAGkAbgBwAHUAdABzAC4AXABuAFwAbgBUAHIAaQBwAGwAZQB3AGkAcwBlALsDIAAtACAAQwBhAHIAdABlAHMAaQBhAG4AIABwAHIAbwBkAHUAYwB0ACAAbwBmACAAMwAgAHMAZQB0AHMALgBcAG4AXABuAFEAdQBhAGQAdwBpAHMAZQC7AyAAIAAgAC0AIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAcgBvAGQAdQBjAHQAIABvAGYAIAA0ACAAcwBlAHQAcwAuAFwAbgBcAG4ARQBjAGgAbwC7AyAAIAAgACAAIAAgACAALQAgAFIAZQBwAGUAYQB0AHMAIABlAGEAYwBoACAAZQBsAGUAbQBlAG4AdAAgAGEAYwBjAG8AcgBkAGkAbgBnACAAdABvACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAuAFwAbgBcAG4AQwBvAG4AdgBvAGwAdgBlALsDIAAgACAALQAgAFMAbABpAGQAaQBuAGcAESB3AGkAbgBkAG8AdwAgAGMAbwBuAHYAbwBsAHUAdABpAG8AbgAgAHUAcwBpAG4AZwAgAGEAIAByAGUAZAB1AGMAZQByAC4AXABuAFwAbgB8ACAATgBlAHcAIABwAHIAbwB0AG8AdAB5AHAAZQBzACAAfABcAG4AXABuAEIAbABvAGMAawBzALsDIAAgACAAIAAgAC0AIABQAGEAcgB0AGkAdABpAG8AbgBzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABkAGUAcAB0AGgA1wB3AGkAZAB0AGgAIABiAGwAbwBjAGsAcwAuAFwAbgBcAG4AVwBpAG4AZABvAHcAZQBkALsDIAAgACAALQAgAEUAeAB0AHIAYQBjAHQAcwAgAG8AdgBlAHIAbABhAHAAcABpAG4AZwAgAGQAZQBwAHQAaADXAHcAaQBkAHQAaAAgAHcAaQBuAGQAbwB3AHMALgBcAG4AXABuAEcAcgBpAGQATABvAG8AawB1AHAAuwMgAC0AIAAyAEQAIABsAG8AbwBrAHUAcAAgAHIAZQB0AHUAcgBuAGkAbgBnACAAYwBvAHIAcgBlAHMAcABvAG4AZABpAG4AZwAgAHYAYQBsAHUAZQBzACAAZgByAG8AbQAgAGEAIABzAGUAYwBvAG4AZAAgAGcAcgBpAGQALgBcAG4AXABuAE4AYQB2AGkAZwBhAHQAZQAyAEQAuwMgAC0AIABMAG8AYwBhAHQAZQBzACAAYQAgAGsAZQByAG4AZQBsACAAaQBuACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGEAbgBkACAAcgBlAHQAdQByAG4AcwAgAGEAIABNAG8AbwByAGUAESBuAGUAaQBnAGgAYgBvAHIAaABvAG8AZAAgAHMAaABhAHAAZQAuAFwAbgBcAG4ATQBhAHQAYwBoADIARAC7AyAAIAAgACAALQAgAEwAbwBjAGEAdABlAHMAIABhACAAawBlAHIAbgBlAGwAIABpAG4AIABhACAAMgBEACAAYQByAHIAYQB5ACAAYQBuAGQAIAByAGUAdAB1AHIAbgBzACAAbQBhAHQAYwBoACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzAC4AXABuAFwAbgBWAFMAcABsAGkAdAC7AyAAIAAgACAAIAAtACAAUwBwAGwAaQB0AHMAIABhACAAMgBEACAAYQByAHIAYQB5ACAAaQBuAHQAbwAgAHYAZQByAHQAaQBjAGEAbAAgAHIAbwB3ABEgcwBlAGcAbQBlAG4AdABzACAAbwBmACAAcwBpAHoAZQAgAHMAcABsAGkAdABfAGkAbgB0AGUAcgB2AGEAbAAuAFwAbgBcAG4ASABTAHAAbABpAHQAuwMgACAAIAAgACAALQAgAFMAcABsAGkAdABzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABoAG8AcgBpAHoAbwBuAHQAYQBsACAAYwBvAGwAdQBtAG4AESBzAGUAZwBtAGUAbgB0AHMAIABvAGYAIABzAGkAegBlACAAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsAC4AXABuAFwAbgBcAG4AVQBuAGMAaABhAG4AZwBlAGQAIABmAHUAbgBjAHQAaQBvAG4AcwAuACAAQwBhAGwAbABlAGQAIABiAHkAIABzAG8AbQBlACAAbwBmACAAdABoAGUAIABhAGIAbwB2AGUAIABmAHUAbgBjAHQAaQBvAG4AcwAuAFwAbgAiICAATQBHAHIAaQBkALsDXABuACIgIABSAGUAcABlAGEAdABSAG8AdwBzALsDXABuACIgIABSAGUAcABlAGEAdABDAG8AbABzALsDXABuACIgIABSAGUAcwBpAHoAZQC7A1wAbgBcAG4AXABuAC8AKgBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABNAGEAZwBuAGkAZgB5ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABUAEIARABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIABBAGwAcABoAGEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAcABhAG4AZABzACAAZQBhAGMAaAAgAGUAbABlAG0AZQBuAHQAIABvAGYAIABhAG4AIABpAG4AcAB1AHQAIABhAHIAcgBhAHkAIABpAG4AdABvACAAYQAgAGIAbABvAGMAawAgAG8AZgAgAHMAcABlAGMAaQBmAGkAZQBkACAAaABlAGkAZwBoAHQAIABhAG4AZABcAG4AIAAgACAAIAB3AGkAZAB0AGgAIAB1AHMAaQBuAGcAIABuAGUAYQByAGUAcwB0ABEgbgBlAGkAZwBoAGIAbwByACAAaQBuAHQAZQByAHAAbwBsAGEAdABpAG8AbgAuACAAUwB1AHAAcABvAHIAdABzACAAcwBjAGEAbABhAHIAcwAsACAAMQBEACAAYQByAHIAYQB5AHMALAAgAGEAbgBkAFwAbgAgACAAIAAgADIARAAgAGEAcgByAGEAeQBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAALQAgAEkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAHQAbwAgAG0AYQBnAG4AaQBmAHkALgBcAG4AIAAgACAAIABoAGUAaQBnAGgAdAAgACAAIAAgACAAIAAtACAATgB1AG0AYgBlAHIAIABvAGYAIAByAG8AdwBzACAAZgBvAHIAIABlAGEAYwBoACAAbQBhAGcAbgBpAGYAaQBlAGQAIABlAGwAZQBtAGUAbgB0ACAAKABwAG8AcwBpAHQAaQB2AGUAIABzAGMAYQBsAGEAcgApAC4AXABuACAAIAAgACAAdwBpAGQAdABoACAAIAAgACAAIAAgACAALQAgAE4AdQBtAGIAZQByACAAbwBmACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAG0AYQBnAG4AaQBmAGkAZQBkACAAZQBsAGUAbQBlAG4AdAAgACgAcABvAHMAaQB0AGkAdgBlACAAcwBjAGEAbABhAHIAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAGgAZQBpAGcAaAB0ACAAYQBuAGQAIAB3AGkAZAB0AGgAIABtAHUAcwB0ACAAYgBlACAAcwBjAGEAbABhAHIALAAgAG4AdQBtAGUAcgBpAGMALAAgAGEAbgBkACAAPgAgADAALgBcAG4AIAAgACAAIAAiICAAVQBzAGUAcwAgAG4AZQBhAHIAZQBzAHQAESBuAGUAaQBnAGgAYgBvAHIAIABlAHgAcABhAG4AcwBpAG8AbgAgAHYAaQBhACAAaQBuAGQAZQB4ACAAcgBlAHAAbABpAGMAYQB0AGkAbwBuAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAE0AYQBnAG4AaQBmAHkAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAaABlAGkAZwBoAHQALABcAG4AIAAgACAAIAB3AGkAZAB0AGgALABcAG4AXABuAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuAEkARgAoAE8AUgAoAEMATwBVAE4AVAAoAGgAZQBpAGcAaAB0ACkAIAA8AD4AIAAxACwAIABDAE8AVQBOAFQAKAB3AGkAZAB0AGgAKQAgADwAPgAgADEAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAGgAZQBpAGcAaAB0ACkALAAgAEkAUwBUAEUAWABUACgAdwBpAGQAdABoACkAKQAsAFwAIgAjAFQARQBYAFQAIQBcACIALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABoAGUAaQBnAGgAdAAgADwAPQAgADAALAAgAHcAaQBkAHQAaAAgADwAPQAgADAAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABOAGUAYQByAGUAcwB0ACAAbgBlAGkAZwBoAGIAbwByACAAaQBuAHQAZQByAHAAbwBsAGEAdABpAG8AbgBcAG4AIAAgACAAIABtAGEAZwC7AywAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABlAGwAZQBtAGUAbgB0ACwARQBYAFAAQQBOAEQAKABlAGwAZQBtAGUAbgB0ACwAaABlAGkAZwBoAHQALAB3AGkAZAB0AGgALABlAGwAZQBtAGUAbgB0ACkAKQAsAFwAbgAgACAAIAAgAG0AYQBnAG4AaQBmAGkAZQBkACwAIABGAEwAQQBUAFQARQBOACgATQBBAFAAKABhAHIAcgBhAHkALABtAGEAZwC7AykAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAG0AYQBnAG4AaQBmAGkAZQBkAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABBAGwAaQBnAG4AUgBvAHcAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAQQBsAHAAaABhAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUwBvAHIAdABzACAAZQBhAGMAaAAgAHIAbwB3ACAAYQBsAHAAaABhAGIAZQB0AGkAYwBhAGwAbAB5ACAAKABkAGUAZgBhAHUAbAB0ACkAIABvAHIAIABiAHkAIAB0AGgAZQAgAHMAcABlAGMAaQBmAGkAZQBkACAAcwBvAHIAdAAgAG8AcgBkAGUAcgAuAFwAbgAgACAAIAAgAFMAbwByAHQAaQBuAGcAIABpAHMAIABsAGUAeABpAGMAbwBnAHIAYQBwAGgAaQBjACAAYQBuAGQAIABjAGEAcwBlABEgcwBlAG4AcwBpAHQAaQB2AGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABiAGUAIABhAGwAaQBnAG4AZQBkAC4AXABuACAAIAAgACAAWwBzAG8AcgB0AF8AbwByAGQAZQByAF0AIAAtACAAMQAgACgAQQBzAGMAZQBuAGQAaQBuAGcAKQAsACAALQAxACAAKABEAGUAcwBjAGUAbgBkAGkAbgBnACkALgAgAEQAZQBmAGEAdQBsAHQAIAA9ACAAMQAuAFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQQBsAGkAZwBuAFIAbwB3AHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBzAG8AcgB0AF8AbwByAGQAZQByAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIABzAG8AcgB0AF8AbwByAGQAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHMAbwByAHQAXwBvAHIAZABlAHIAKQAsACAAMQAsACAAcwBvAHIAdABfAG8AcgBkAGUAcgApACwAXABuACAAIAAgACAAcwBvAHIAdABlAGQALAAgACAAIAAgACAARgBMAEEAVABUAEUATgAoAEIAWQBSAE8AVwAoAGEAcgByAGEAeQAsACAATABBAE0AQgBEAEEAKAByAG8AdwAsACAAUwBPAFIAVAAoAHIAbwB3ACwALABzAG8AcgB0AF8AbwByAGQAZQByACwAVABSAFUARQApACkAKQApACwAXABuACAAIAAgACAAcwBvAHIAdABlAGQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABBAGwAaQBnAG4AQwBvAGwAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAQQBsAHAAaABhAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUwBvAHIAdABzACAAZQBhAGMAaAAgAGMAbwBsAHUAbQBuACAAYQBsAHAAaABhAGIAZQB0AGkAYwBhAGwAbAB5ACAAKABkAGUAZgBhAHUAbAB0ACkAIABvAHIAIABiAHkAIAB0AGgAZQAgAHMAcABlAGMAaQBmAGkAZQBkACAAcwBvAHIAdAAgAG8AcgBkAGUAcgAuAFwAbgAgACAAIAAgAFMAbwByAHQAaQBuAGcAIABpAHMAIABsAGUAeABpAGMAbwBnAHIAYQBwAGgAaQBjACAAYQBuAGQAIABjAGEAcwBlABEgcwBlAG4AcwBpAHQAaQB2AGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABiAGUAIABhAGwAaQBnAG4AZQBkAC4AXABuACAAIAAgACAAWwBzAG8AcgB0AF8AbwByAGQAZQByAF0AIAAtACAAMQAgACgAQQBzAGMAZQBuAGQAaQBuAGcAKQAsACAALQAxACAAKABEAGUAcwBjAGUAbgBkAGkAbgBnACkALgAgAEQAZQBmAGEAdQBsAHQAIAA9ACAAMQAuAFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQQBsAGkAZwBuAEMAbwBsAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAWwBzAG8AcgB0AF8AbwByAGQAZQByAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIABzAG8AcgB0AF8AbwByAGQAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHMAbwByAHQAXwBvAHIAZABlAHIAKQAsACAAMQAsACAAcwBvAHIAdABfAG8AcgBkAGUAcgApACwAXABuACAAIAAgACAAcwBvAHIAdABlAGQALAAgACAAIAAgACAARgBMAEEAVABUAEUATgAoAEIAWQBDAE8ATAAoAGEAcgByAGEAeQAsACAATABBAE0AQgBEAEEAKABjAG8AbAAsACAAUwBPAFIAVAAoAGMAbwBsACwALABzAG8AcgB0AF8AbwByAGQAZQByACkAKQApACkALABcAG4AIAAgACAAIABzAG8AcgB0AGUAZABcAG4AKQApADsAXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAQgBEAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARgBvAGwAZAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAQQBsAHAAaABhAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAAQQBsAGkAZwBuAFIAbwB3AHMAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBkAHUAYwBlAHMAIAByAGUAYwBvAHIAZABzACAAaQBuACAAYQBuACAAYQByAHIAYQB5ACAAYgB5ACAAZwByAG8AdQBwAGkAbgBnACAAaQBkAGUAbgB0AGkAYwBhAGwAIAByAG8AdwBzACAAYQBuAGQAIABhAHAAcABsAHkAaQBuAGcAIABhAG4AXABuACAAIAAgACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAZgB1AG4AYwB0AGkAbwBuACAAdABvACAAdABoAGUAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAZQBuAHQAcgBpAGUAcwAgAGkAbgAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5AC4AXABuAFwAbgAgACAAIAAgAEkAZgAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5ACAAaQBzACAAbwBtAGkAdAB0AGUAZAAsACAARgBvAGwAZAC7AyAAdQBzAGUAcwAgAHQAaABlACAAZgBpAHIAcwB0ACAAZgBpAGUAbABkACAAbwBmACAAZQBhAGMAaAAgAHIAZQBjAG8AcgBkACAAYQBzAFwAbgAgACAAIAAgAHQAaABlACAAYQBnAGcAcgBlAGcAYQB0AGkAbwBuACAAdgBlAGMAdABvAHIALgAgAFQAaABpAHMAIABtAG8AZABlACAAaQBzACAAaQBuAHQAZQBuAGQAZQBkACAAZgBvAHIAIABDAE8AVQBOAFQAQQA7ACAAbwB0AGgAZQByACAAcgBlAGQAdQBjAGUAcgBzAFwAbgAgACAAIAAgAG0AYQB5ACAAcAByAG8AZAB1AGMAZQAgAHIAZQBzAHUAbAB0AHMAIABiAHUAdAAgAGEAcgBlACAAbgBvAHQAIABtAGUAYQBuAGkAbgBnAGYAdQBsAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5ACAAIAAgACAAIAAgACAAIAAgACAAIAAtACAAMQBEACAAbwByACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAcgBvAHcAcwAgAGQAZQBmAGkAbgBlACAAZwByAG8AdQBwAGkAbgBnACAAawBlAHkAcwAuAFwAbgAgACAAIAAgAFsAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAG8AZgAgAHYAYQBsAHUAZQBzACAAdABvACAAYQBnAGcAcgBlAGcAYQB0AGUALgBcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACAAIAAgACAAIAAgAC0AIABSAGUAZAB1AGMAZQByACAATABBAE0AQgBEAEEAIABhAGMAYwBlAHAAdABpAG4AZwAgAGEAIAAxAEQAIAB2AGUAYwB0AG8AcgAgACgAZABlAGYAYQB1AGwAdAAgAD0AIABDAE8AVQBOAFQAQQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAARgBvAGwAZAC7AyAAaABhAGwAdABzACAAdwBpAHQAaAAgACMAVgBBAEwAVQBFACEAIABpAGYAIABhAHIAcgBhAHkAIABhAG4AZAAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5ACAAaABlAGkAZwBoAHQAcwAgAGQAaQBmAGYAZQByAC4AXABuACAAIAAgACAAIiAgAEYAbwBsAGQAuwMgAGgAYQBsAHQAcwAgAHcAaQB0AGgAIAAjAEYAVQBOAEMAVABJAE8ATgAhACAAaQBmACAAcgBlAGQAdQBjAGUAcgAgAGkAcwAgAG4AbwB0ACAAYQAgAHYAYQBsAGkAZAAgAEwAQQBNAEIARABBAC4AXABuACAAIAAgACAAIiAgAEEAbABpAGcAbgBSAG8AdwBzALsDIABjAGEAbgBvAG4AaQBjAGEAbABpAHoAZQBzACAAcgBlAGMAbwByAGQAcwAgAHMAbwAgAGkAZABlAG4AdABpAGMAYQBsACAAcgBvAHcAcwAgAGcAcgBvAHUAcAAgAGMAbABlAGEAbgBsAHkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARgBvAGwAZAC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5AF0ALABcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIAB2AGEAbAB1AGUAcwAgAGEAcgByAGEAeQBcAG4AIAAgACAAIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQApACwAIABUAEEASwBFACgAYQByAHIAYQB5ACwALAAxACkALAAgAHYAYQBsAHUAZQBzAF8AYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAYQB1AGwAdAAgAHIAZQBkAHUAYwBlAHIAXABuACAAIAAgACAAZgB1AG4AYwB0AGkAbwBuACwAIAAgACAAIAAgAEkARgAoAE8AUgAoAEkAUwBPAE0ASQBUAFQARQBEACgAZgB1AG4AYwB0AGkAbwBuACkALAAgAEkAUwBPAE0ASQBUAFQARQBEACgAdgBhAGwAdQBlAHMAXwBhAHIAcgBhAHkAKQApACwAIABDAE8AVQBOAFQAQQAsACAAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABJAEYAKABBAE4ARAAoAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQApACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAgADwAPgAgAFIATwBXAFMAKAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQApACkALAAgAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAIABcACIAIwBGAFUATgBDAFQASQBPAE4AIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAQwBhAG4AbwBuAGkAYwBhAGwAIABnAHIAbwB1AHAAaQBuAGcAIABrAGUAeQBzAFwAbgAgACAAIAAgAGEAbABpAGcAbgBlAGQALAAgAEEAbABpAGcAbgBSAG8AdwBzALsDKABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAGcAZwByAGUAZwBhAHQAaQBvAG4AXABuACAAIAAgACAAYQBnAGcALAAgACAAIAAgAEcAUgBPAFUAUABCAFkAKABhAGwAaQBnAG4AZQBkACwAIAB2AGEAbAB1AGUAcwBfAGEAcgByAGEAeQAsACAAZgB1AG4AYwB0AGkAbwBuACwALAAwACkALABcAG4AXABuACAAIAAgACAAYQBnAGcAXABuACkAKQApACkAXABuACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAEEAUgAwADEAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABaAGkAcAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAQQByAHIAYQB5ACAAUwBoAGEAcABpAG4AZwBcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIABBAGwAcABoAGEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABaAGkAcABzACAAdABvAGcAZQB0AGgAZQByACAAMQAtADQAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABhACAAbABpAHMAdAAgAG8AZgAgAHIAbwB3ABEgcgBlAGMAbwByAGQAcwAuACAARQBhAGMAaAAgAGkAbgBwAHUAdAAgAGkAcwAgAGYAaQByAHMAdABcAG4AIAAgACAAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAdwBpAHQAaAAgAFQATwBDAE8ATAAgAHMAbwAgAHQAaABhAHQAIABzAGMAYQBsAGEAcgBzACwAIAAxAEQAIABhAHIAcgBhAHkAcwAsACAAYQBuAGQAIAAyAEQAIABhAHIAcgBhAHkAcwAgAGIAZQBoAGEAdgBlAFwAbgAgACAAIAAgAHUAbgBpAGYAbwByAG0AbAB5AC4AIABaAGkAcAC7AyAAdABoAGUAbgAgAGEAbABpAGcAbgBzACAAdABoAGUAIABpAG4AcAB1AHQAcwAgAGIAeQAgAGwAZQBuAGcAdABoACAAYQBuAGQAIABjAG8AbgBzAHQAcgB1AGMAdABzACAAbwBuAGUAIAByAGUAYwBvAHIAZABcAG4AIAAgACAAIABwAGUAcgAgAHIAbwB3ACAAdQBzAGkAbgBnACAAQgBZAFIATwBXAC4AXABuAFwAbgAgACAAIAAgAEkAbgAgAHMAdAByAGkAYwB0ACAAbQBvAGQAZQAgACgAZABlAGYAYQB1AGwAdAApACwAIABaAGkAcAC7AyAAcABhAGkAcgBzACAAZQBsAGUAbQBlAG4AdABzACAAbwBuAGwAeQAgAHUAcAAgAHQAbwAgAHQAaABlACAAbABlAG4AZwB0AGgAIABvAGYAIAB0AGgAZQBcAG4AIAAgACAAIABzAGgAbwByAHQAZQBzAHQAIABhAHIAcgBhAHkALgAgAEkAZgAgAHoAaQBwAF8AbABvAG4AZwBlAHMAdAAgAD0AIABUAFIAVQBFACwAIABaAGkAcAC7AyAAYwBvAG4AdABpAG4AdQBlAHMAIAB1AG4AdABpAGwAIAB0AGgAZQAgAGwAbwBuAGcAZQBzAHQAXABuACAAIAAgACAAYQByAHIAYQB5ACAAaQBzACAAYwBvAG4AcwB1AG0AZQBkACwAIABwAGEAZABkAGkAbgBnACAAcwBoAG8AcgB0AGUAcgAgAGEAcgByAGEAeQBzACAAdwBpAHQAaAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAIAAoAGQAZQBmAGEAdQBsAHQAOgAgACMATgAvAEEAKQAuAFwAbgBcAG4AIAAgACAAIABUAGgAZQAgAHIAZQBzAHUAbAB0ACAAaQBzACAAYQAgAGwAaQBzAHQAIABvAGYAIAByAGUAYwBvAHIAZABzACAAbwBmACAAdABoAGUAIABmAG8AcgBtADoAXABuACAAIAAgACAAIAAgACAAIAB7ACAAewBhAIEgLABiAIEgLABjAIEgLABkAIEgfQAsACAAewBhAIIgLABiAIIgLABjAIIgLABkAIIgfQAsACAAJiAgAH0AXABuACAAIAAgACAAVQBzAGUAIABGAEwAQQBUAFQARQBOACAAdABvACAAcwBwAGkAbABsACAAdABoAGUAIABsAGkAcwB0ACAAYQBzACAAYQAgADIARAAgAHQAYQBiAGwAZQAgAHcAaABlAG4AIAByAGUAcQB1AGkAcgBlAGQALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAXwAxACAAIAAgACAAIAAgACAALQAgAEYAaQByAHMAdAAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgACgAcwBjAGEAbABhAHIALAAgADEARAAsACAAbwByACAAMgBEACkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADIAXQAgACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHMAZQBjAG8AbgBkACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwAzAF0AIAAgACAAIAAgAC0AIABPAHAAdABpAG8AbgBhAGwAIAB0AGgAaQByAGQAIABhAHIAcgBhAHkALgBcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADQAXQAgACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAGYAbwB1AHIAdABoACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAWwB6AGkAcABfAGwAbwBuAGcAZQBzAHQAXQAgAC0AIABUAFIAVQBFACAAdABvACAAegBpAHAAIAB1AG4AdABpAGwAIAB0AGgAZQAgAGwAbwBuAGcAZQBzAHQAIABhAHIAcgBhAHkAIABpAHMAIABjAG8AbgBzAHUAbQBlAGQALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAZgAgAG8AbQBpAHQAdABlAGQALAAgAFoAaQBwALsDIAB1AHMAZQBzACAAcwB0AHIAaQBjAHQAIABtAG8AZABlACAAKABzAGgAbwByAHQAZQBzAHQAIABhAHIAcgBhAHkAKQAuAFwAbgAgACAAIAAgAFsAZgBpAGwAbABfAHYAYQBsAHUAZQBdACAAIAAtACAAVgBhAGwAdQBlACAAdQBzAGUAZAAgAHQAbwAgAHAAYQBkACAAcwBoAG8AcgB0AGUAcgAgAGEAcgByAGEAeQBzACAAdwBoAGUAbgAgAHoAaQBwAF8AbABvAG4AZwBlAHMAdAAgAD0AIABUAFIAVQBFAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAQQBsAGwAIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUAIAB1AHMAaQBuAGcAIABUAE8AQwBPAEwALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABpAHMAIABhACAAbABpAHMAdAAgAG8AZgAgAHMAdAByAHUAYwB0AHUAcgBlAGQAIAByAGUAYwBvAHIAZABzACwAIABuAG8AdAAgAGEAIABzAHAAaQBsAGwAZQBkACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAIiAgAEEAcABwAGwAeQAgAEYATABBAFQAVABFAE4AKAB6AGkAcABwAGUAZAApACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAHQAaABlACAAbABpAHMAdAAgAHQAbwAgAGEAIAAyAEQAIAB0AGEAYgBsAGUALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AWgBpAHAAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMQAsAFwAbgAgACAAIAAgAFsAYQByAHIAYQB5AF8AMgBdACwAXABuACAAIAAgACAAWwBhAHIAcgBhAHkAXwAzAF0ALABcAG4AIAAgACAAIABbAGEAcgByAGEAeQBfADQAXQAsAFwAbgAgACAAIAAgAFsAegBpAHAAXwBsAG8AbgBnAGUAcwB0AF0ALABcAG4AIAAgACAAIABbAGYAaQBsAGwAXwB2AGEAbAB1AGUAXQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGUAdAAgAHoAaQBwACAAbQBvAGQAZQBcAG4AIAAgACAAIABaAGkAcABMAG8AbgBnAD8ALAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHoAaQBwAF8AbABvAG4AZwBlAHMAdAApACwAIABGAEEATABTAEUALAAgAHoAaQBwAF8AbABvAG4AZwBlAHMAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAdQBuAGMAdABpAG8AbgAgAGYAbwByACAAZABlAHQAZQByAG0AaQBuAGkAbgBnACAAegBpAHAAIABsAGUAbgBnAHQAaABcAG4AIAAgACAAIABmAG4AuwMsACAAIAAgACAAIAAgACAAIABJAEYAKABaAGkAcABMAG8AbgBnAD8ALAAgAE0AQQBYACwAIABNAEkATgApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAaQBsAGwAIAB2AGEAbAB1AGUAXABuACAAIAAgACAAZgBpAGwAbABfAHYAYQBsAHUAZQAsACAASQBGACgAWgBpAHAATABvAG4AZwA/ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAGkAbABsAF8AdgBhAGwAdQBlACkALAAgAE4AQQAoACkALAAgAGYAaQBsAGwAXwB2AGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE4AQQAoACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAHIAcgBhAHkAcwAgAHMAdQBwAHAAbABpAGUAZABcAG4AIAAgACAAIABUAHcAbwAsACAAIAAgAE4ATwBUACgASQBTAE8ATQBJAFQAVABFAEQAKABhAHIAcgBhAHkAXwAyACkAKQAsAFwAbgAgACAAIAAgAFQAaAByAGUAZQAsACAATgBPAFQAKABJAFMATwBNAEkAVABUAEUARAAoAGEAcgByAGEAeQBfADMAKQApACwAXABuACAAIAAgACAARgBvAHUAcgAsACAAIABOAE8AVAAoAEkAUwBPAE0ASQBUAFQARQBEACgAYQByAHIAYQB5AF8ANAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAVABvAHQAYQBsACAAYQByAHIAYQB5AHMAIABzAHUAcABwAGwAaQBlAGQAXABuACAAIAAgACAAbQAsACAASQBGACgARgBvAHUAcgAsACAANAAsAFwAbgAgACAAIAAgACAAIAAgACAAIABJAEYAKABUAGgAcgBlAGUALAAgADMALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAVAB3AG8ALAAgADIALAAgADEAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAARgBsAGEAdAB0AGUAbgAgAGkAbgBwAHUAdABzAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADEALAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQBfADEAKQAsAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIALAAgAEkARgAoAG0AIAA+AD0AIAAyACwAIABUAE8AQwBPAEwAKABhAHIAcgBhAHkAXwAyACkALAAgAEYAQQBMAFMARQApACwAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMwAsACAASQBGACgAbQAgAD4APQAgADMALAAgAFQATwBDAE8ATAAoAGEAcgByAGEAeQBfADMAKQAsACAARgBBAEwAUwBFACkALABcAG4AIAAgACAAIABhAHIAcgBhAHkAXwA0ACwAIABJAEYAKABtACAAPQAgACAANAAsACAAVABPAEMATwBMACgAYQByAHIAYQB5AF8ANAApACwAIABGAEEATABTAEUAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAGUAbgBnAHQAaABzAFwAbgAgACAAIAAgAGsAgSAsACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADEAKQAsACAAIAAgAGsAgiAsACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAGsAgyAsACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADMAKQAsACAAIAAgAGsAhCAsACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABaAGkAcAAgAGwAZQBuAGcAdABoAFwAbgAgACAAIAAgAEwAWgAsACAAQwBIAE8ATwBTAEUAKABtACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGsAgSAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABmAG4AuwMoAGsAgSAsACAAawCCICkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBuALsDKABrAIEgLAAgAGsAgiAsACAAawCDICkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAZgBuALsDKABrAIEgLAAgAGsAgiAsACAAawCDICwAIABrAIQgKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBhAHQAaQBvAG4AXABuACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMsACAATABBAE0AQgBEAEEAKABhAHIAcgAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAWgBpAHAATABvAG4AZwA/ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABFAFgAUABBAE4ARAAoAGEAcgByACwAIABMAFoALAAsACAAZgBpAGwAbABfAHYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABUAEEASwBFACgAYQByAHIALAAgAEwAWgApACkAKQAsAFwAbgBcAG4AIAAgACAAIABhACwAIABOAG8AcgBtAGEAbABpAHoAZQC7AygAYQByAHIAYQB5AF8AMQApACwAXABuACAAIAAgACAAYgAsACAATgBvAHIAbQBhAGwAaQB6AGUAuwMoAGEAcgByAGEAeQBfADIAKQAsAFwAbgAgACAAIAAgAGMALAAgAE4AbwByAG0AYQBsAGkAegBlALsDKABhAHIAcgBhAHkAXwAzACkALABcAG4AIAAgACAAIABkACwAIABOAG8AcgBtAGEAbABpAHoAZQC7AygAYQByAHIAYQB5AF8ANAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAbgBnAGUAbQBlAG4AdABcAG4AIAAgACAAIABhAHIAcgBhAG4AZwBlAGQALAAgAEMASABPAE8AUwBFACgAbQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABhACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAsACAAYgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAsACAAYgAsACAAYwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAYQAsACAAYgAsACAAYwAsACAAZAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAWgBpAHAAIAB0AG8AIABsAGkAcwB0ACAAbwBmACAAcgBvAHcAESByAGUAYwBvAHIAZABzAFwAbgAgACAAIAAgAHoAaQBwAHAAZQBkACwAIABCAFkAUgBPAFcAKABhAHIAcgBhAG4AZwBlAGQALAAgAEwAQQBNAEIARABBACgAcgBvAHcALAAgAHsAcgBvAHcAfQApACkALABcAG4AXABuACAAIAAgACAAegBpAHAAcABlAGQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAEIARABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAFAAYQBpAHIAdwBpAHMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMgAuADAAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABDAHIAZQBhAHQAZQBzACAAdgBlAHIAdABpAGMAYQBsACAAcABhAGkAcgBzACAAZgByAG8AbQAgAHQAdwBvACAAaQBuAHAAdQB0AHMAIAAoAHMAYwBhAGwAYQByAHMALAAgADEARAAgAGEAcgByAGEAeQBzACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAcwApAC4AXABuACAAIAAgACAAQgBvAHQAaAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABuAG8AcgBtAGEAbABpAHoAZQBkACAAdwBpAHQAaAAgAFQATwBDAE8ATAAgAHMAbwAgAHQAaABhAHQAIABvAHIAaQBlAG4AdABhAHQAaQBvAG4AIABpAHMAIABjAG8AbgBzAGkAcwB0AGUAbgB0AFwAbgAgACAAIAAgAGEAbgBkACAAcABhAGkAcgBpAG4AZwAgAGIAZQBoAGEAdgBlAHMAIAB1AG4AaQBmAG8AcgBtAGwAeQAgAGEAYwByAG8AcwBzACAAcwBoAGEAcABlAHMALgBcAG4AXABuACAAIAAgACAAUABhAGkAcgB3AGkAcwBlALsDIABwAGUAcgBmAG8AcgBtAHMAIABhACAAQwBhAHIAdABlAHMAaQBhAG4AIABlAHgAcABhAG4AcwBpAG8AbgA6ACAAZQB2AGUAcgB5ACAAZQBsAGUAbQBlAG4AdAAgAG8AZgAgAHYAZQBjAHQAbwByAF8AMQAgAGkAcwBcAG4AIAAgACAAIABwAGEAaQByAGUAZAAgAHcAaQB0AGgAIABlAHYAZQByAHkAIABlAGwAZQBtAGUAbgB0ACAAbwBmACAAdgBlAGMAdABvAHIAXwAyAC4AIABUAGgAZQAgAHIAZQBzAHUAbAB0ACAAaQBzACAAYQAgADIAESBjAG8AbAB1AG0AbgAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAAYQBsAGwAIABvAHIAZABlAHIAZQBkACAAcABhAGkAcgBzAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAdgBlAGMAdABvAHIAXwAxACAAIAAgACAALQAgAFMAYwBhAGwAYQByACwAIAAxAEQAIABhAHIAcgBhAHkALAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAuAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByAF8AMgAgACAAIAAgAC0AIABTAGMAYQBsAGEAcgAsACAAMQBEACAAYQByAHIAYQB5ACwAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAG4AcAB1AHQAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQAIABjAG8AbAB1AG0AbgARIHcAaQBzAGUAIAB1AHMAaQBuAGcAIABUAE8AQwBPAEwALgBcAG4AIAAgACAAIAAiICAAUABhAGkAcgB3AGkAcwBlALsDIABoAGEAbAB0AHMAIAB3AGkAdABoACAAIwBOAFUATQAhACAAaQBmACAAdABoAGUAIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAcgBvAGQAdQBjAHQAIABlAHgAYwBlAGUAZABzACAAMQAsADAAMAAwACwAMAAwADAAXABuACAAIAAgACAAIAAgAHIAbwB3AHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUABhAGkAcgB3AGkAcwBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByAF8AMQAsAFwAbgAgACAAIAAgAHYAZQBjAHQAbwByAF8AMgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAaQBuAHAAdQB0AHMAXABuACAAIAAgACAAdgAsACAAIABUAE8AQwBPAEwAKAB2AGUAYwB0AG8AcgBfADEAKQAsAFwAbgAgACAAIAAgAHYAgiAsACAAVABPAEMATwBMACgAdgBlAGMAdABvAHIAXwAyACkALABcAG4AXABuACAAIAAgACAALwAvACAARQBsAGUAbQBlAG4AdAAgAGMAbwB1AG4AdABzAFwAbgAgACAAIAAgAGsALAAgACAAQwBPAFUATgBUAEEAKAB2ACkALABcAG4AIAAgACAAIABrAIIgLAAgAEMATwBVAE4AVABBACgAdgCCICkALABcAG4AXABuACAAIAAgACAALwAvACAASABhAGwAdABpAG4AZwAgAHMAYwBlAG4AYQByAGkAbwBcAG4AIAAgACAAIABJAHMAMgBCAGkAZwA/ACwAIAAgACAAIABrACAAKgAgAGsAgiAgAD4AIAAxADAAMAAwADAAMAAwACwAXABuAFwAbgAgACAAIAAgAEkARgAoAEkAcwAyAEIAaQBnAD8ALAAgACMATgBVAE0AIQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABDAGEAcgB0AGUAcwBpAGEAbgAgAGUAeABwAGEAbgBzAGkAbwBuAFwAbgAgACAAIAAgAEoAbwBpAG4AUABhAGkAcgBzALsDLAAgAEwAQQBNAEIARABBACgAZQBhAGMAaABfAGUAbABlAG0AZQBuAHQALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgARQBYAFAAQQBOAEQAKABlAGEAYwBoAF8AZQBsAGUAbQBlAG4AdAAsACAAawCCICwALAAgAGUAYQBjAGgAXwBlAGwAZQBtAGUAbgB0ACkALAAgAHYAgiApACkALABcAG4AXABuACAAIAAgACAAcABhAGkAcgBzACwAIAAgACAAIAAgACAARgBMAEEAVABUAEUATgAoAE0AQQBQACgAdgAsACAASgBvAGkAbgBQAGEAaQByAHMAuwMpACkALABcAG4AXABuACAAIAAgACAAcABhAGkAcgBzAFwAbgApACkAKQApADsAXABuAFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAQgBEAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAVAByAGkAcABsAGUAdwBpAHMAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMgAuADAAXABuAEQAZQBwAGUAbgBkAGUAbgBjAGkAZQBzADoAIAAgACAAIABQAGEAaQByAHcAaQBzAGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAdABoAGUAIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAcgBvAGQAdQBjAHQAIABvAGYAIAAzACAAcwBlAHQAcwAuACAAQQBsAGwAIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQAIAB1AHMAaQBuAGcAXABuACAAIAAgACAAVABPAEMATwBMACAAcwBvACAAdABoAGEAdAAgAHMAYwBhAGwAYQByAHMALAAgADEARAAgAGEAcgByAGEAeQBzACwAIABhAG4AZAAgADIARAAgAGEAcgByAGEAeQBzACAAYgBlAGgAYQB2AGUAIAB1AG4AaQBmAG8AcgBtAGwAeQAuAFwAbgBcAG4AIAAgACAAIABUAHIAaQBwAGwAZQB3AGkAcwBlALsDIABlAHgAdABlAG4AZABzACAAUABhAGkAcgB3AGkAcwBlALsDIAB0AG8AIABhACAAMwARIGEAeABpAHMAIABmAGEAYgByAGkAYwA6AFwAbgAgACAAIAAgACAAIAAgACAAcwBlAHQAXwAxACAA1wAgAHMAZQB0AF8AMgAgANcAIABzAGUAdABfADMAXABuACAAIAAgACAAVABoAGUAIABvAHUAdABwAHUAdAAgAGkAcwAgAGEAIAAzABEgYwBvAGwAdQBtAG4AIABzAHAAaQBsAGwAIAB3AGgAZQByAGUAIABlAGEAYwBoACAAcgBvAHcAIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAIABvAHIAZABlAHIAZQBkACAAdAByAGkAcABsAGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABzAGUAdABfADEAIAAgACAAIAAtACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AIABGAGwAYQB0AHQAZQBuAGUAZAAgAHcAaQB0AGgAIABUAE8AQwBPAEwALgBcAG4AIAAgACAAIABzAGUAdABfADIAIAAgACAAIAAtACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AIABGAGwAYQB0AHQAZQBuAGUAZAAgAHcAaQB0AGgAIABUAE8AQwBPAEwALgBcAG4AIAAgACAAIABzAGUAdABfADMAIAAgACAAIAAtACAAUwBjAGEAbABhAHIALAAgADEARAAgAGEAcgByAGEAeQAsACAAbwByACAAMgBEACAAYQByAHIAYQB5AC4AIABGAGwAYQB0AHQAZQBuAGUAZAAgAHcAaQB0AGgAIABUAE8AQwBPAEwALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABJAG4AcAB1AHQAcwAgAGEAcgBlACAAbgBvAHIAbQBhAGwAaQB6AGUAZAAgAGMAbwBsAHUAbQBuABEgdwBpAHMAZQAgAHUAcwBpAG4AZwAgAFQATwBDAE8ATAAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAGkAcwAgAGEAIAAyAEQAIABzAHAAaQBsAGwAIABvAGYAIABvAHIAZABlAHIAZQBkACAAdAByAGkAcABsAGUAcwAuAFwAbgAgACAAIAAgACIgIABUAHIAaQBwAGwAZQB3AGkAcwBlALsDIABwAHIAZQBzAGUAcgB2AGUAcwAgAHQAaABlACAAbwByAGQAZQByACAAbwBmACAAdABoAGUAIABzAHUAcABwAGwAaQBlAGQAIABzAGUAdABzAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFQAcgBpAHAAbABlAHcAaQBzAGUAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAcwBlAHQAXwAxACwAXABuACAAIAAgACAAcwBlAHQAXwAyACwAXABuACAAIAAgACAAcwBlAHQAXwAzACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAXABuACAAIAAgACAAcwBlAHQAXwAxACwAIABUAE8AQwBPAEwAKABzAGUAdABfADEAKQAsAFwAbgAgACAAIAAgAHMAZQB0AF8AMgAsACAAVABPAEMATwBMACgAcwBlAHQAXwAyACkALABcAG4AIAAgACAAIABzAGUAdABfADMALAAgAFQATwBDAE8ATAAoAHMAZQB0AF8AMwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEYAaQByAHMAdAAgAEMAYQByAHQAZQBzAGkAYQBuACAAcAByAG8AZAB1AGMAdABcAG4AIAAgACAAIABwAGEAaQByAHMALAAgAFAAYQBpAHIAdwBpAHMAZQC7AygAcwBlAHQAXwAxACwAIABzAGUAdABfADIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHAAbABpAHQAIABpAG4AdABvACAAYwBvAGwAdQBtAG4AcwBcAG4AIAAgACAAIABhACwAIAAgACAAIAAgAFQAQQBLAEUAKABwAGEAaQByAHMALAAsADEAKQAsAFwAbgAgACAAIAAgAGIALAAgACAAIAAgACAAVABBAEsARQAoAHAAYQBpAHIAcwAsACwALQAxACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBlAGMAbwBuAGQAIABDAGEAcgB0AGUAcwBpAGEAbgAgAHAAcgBvAGQAdQBjAHQAIAAoAGEAIADXACAAcwBlAHQAXwAzACkAXABuACAAIAAgACAAcABfADEAMwAsACAAIABQAGEAaQByAHcAaQBzAGUAuwMoAGEALAAgAHMAZQB0AF8AMwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBjAG8AbgBkACAAQwBhAHIAdABlAHMAaQBhAG4AIABwAHIAbwBkAHUAYwB0ACAAKABiACAA1wAgAHMAZQB0AF8AMwApAFwAbgAgACAAIAAgAHAAXwAyADMALAAgACAAUABhAGkAcgB3AGkAcwBlALsDKABiACwAIABzAGUAdABfADMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAdAByAGEAYwB0ACAAYwBvAGwAdQBtAG4AcwBcAG4AIAAgACAAIABhAF8ALAAgACAAIAAgAFQAQQBLAEUAKABwAF8AMQAzACwALAAxACkALABcAG4AIAAgACAAIABiAF8ALAAgACAAIAAgAFQAQQBLAEUAKABwAF8AMgAzACwALAAxACkALABcAG4AIAAgACAAIABjAF8ALAAgACAAIAAgAFQAQQBLAEUAKABwAF8AMQAzACwALAAtADEAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAGkAbgBhAGwAIAB0AHIAaQBwAGwAZQBcAG4AIAAgACAAIAB0AHIAaQBwAGwAZQAsAEgAUwBUAEEAQwBLACgAYQBfACwAIABiAF8ALAAgAGMAXwApACwAXABuACAAIAAgACAAdAByAGkAcABsAGUAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAQgBEAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAUQB1AGEAZAB3AGkAcwBlALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAIABUAEIARABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAIAAyAC4AMABcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIAAgAFIAZQBwAGUAYQB0AFIAbwB3AHMAuwMsACAAUgBlAHMAaQB6AGUAuwMsACAAVAByAGkAcABsAGUAdwBpAHMAZQC7A1wAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAARwBlAG4AZQByAGEAdABlAHMAIAB0AGgAZQAgAEMAYQByAHQAZQBzAGkAYQBuACAAcAByAG8AZAB1AGMAdAAgAG8AZgAgADQAIABzAGUAdABzAC4AIABBAGwAbAAgAGkAbgBwAHUAdABzACAAYQByAGUAIABmAGwAYQB0AHQAZQBuAGUAZAAgAGEAbgBkAFwAbgAgACAAIAAgAHQAaABlACAAcgBlAHMAdQBsAHQAaQBuAGcAIABxAHUAYQBkAHIAdQBwAGwAZQBzACAAcAByAGUAcwBlAHIAdgBlACAAdABoAGUAIABvAHIAZABlAHIAIABvAGYAIAB0AGgAZQAgAHMAdQBwAHAAbABpAGUAZAAgAHMAZQB0AHMALgBcAG4AXABuACAAIAAgACAAUQB1AGEAZAB3AGkAcwBlALsDIABlAHgAdABlAG4AZABzACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AyAAdABvACAAYQAgADQAESBhAHgAaQBzACAAZgBhAGIAcgBpAGMAOgBcAG4AIAAgACAAIAAgACAAIAAgACIgIABzAGUAdABfADEAIADXACAAcwBlAHQAXwAyACAA1wAgAHMAZQB0AF8AMwAgANcAIABzAGUAdABfADQAXABuACAAIAAgACAAVABoAGUAIABvAHUAdABwAHUAdAAgAGkAcwAgAGEAIABzAHAAaQBsAGwAIAByAGEAbgBnAGUAIAB3AGgAZQByAGUAIABlAGEAYwBoACAAcgBvAHcAIAByAGUAcAByAGUAcwBlAG4AdABzACAAbwBuAGUAIABvAHIAZABlAHIAZQBkACAAcQB1AGEAZAByAHUAcABsAGUALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABzAGUAdABfADEAIAAgACAAIABTAGMAYQBsAGEAcgBzACAAYQBuAGQAIABhAHIAcgBhAHkAcwAgACgAMQBEACAAbwByACAAMgBEACkAIABhAHIAZQAgAGEAYwBjAGUAcAB0AGUAZAAuACAAQQBsAGwAIABpAG4AcAB1AHQAcwAgAGEAcgBlACAAZgBsAGEAdAB0AGUAbgBlAGQALgBcAG4AIAAgACAAIABzAGUAdABfADIAXABuACAAIAAgACAAcwBlAHQAXwAzAFwAbgAgACAAIAAgAHMAZQB0AF8ANABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUQB1AGEAZAB3AGkAcwBlALsDPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABzAGUAdABfADEALABcAG4AIAAgACAAIABzAGUAdABfADIALABcAG4AIAAgACAAIABzAGUAdABfADMALABcAG4AIAAgACAAIABzAGUAdABfADQALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABGAGwAYQB0AHQAZQBuACAAYQBsAGwAIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIABzAGUAdABfADEALAAgACAAVABPAEMATwBMACgAcwBlAHQAXwAxACkALABcAG4AIAAgACAAIABzAGUAdABfADIALAAgACAAVABPAEMATwBMACgAcwBlAHQAXwAyACkALABcAG4AIAAgACAAIABzAGUAdABfADMALAAgACAAVABPAEMATwBMACgAcwBlAHQAXwAzACkALABcAG4AIAAgACAAIABzAGUAdABfADQALAAgACAAVABPAEMATwBMACgAcwBlAHQAXwA0ACkALABcAG4AXABuACAAIAAgACAALwAvACAARQB4AHAAYQBuAHMAaQBvAG4AIABjAG8AdQBuAHQAXABuACAAIAAgACAAawAsACAAIAAgACAAIAAgAFIATwBXAFMAKABzAGUAdABfADQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAHMAZQB0ACAANAAgAGkAZgAgAHMAYwBhAGwAYQByACAAdABvACAAYQB2AG8AaQBkACAAVABPAEMATwBMACAAaABhAG4AZABvAGYAZgAgAHQAbwAgAFIAZQBzAGkAegBlALsDXABuACAAIAAgACAAZAAsACAAIAAgACAAIAAgAEkARgAoAGsAIAA8AD4AIAAxACwAcwBlAHQAXwA0ACwASQBOAEQARQBYACgAcwBlAHQAXwA0ACwAMQApACkALABcAG4AXABuACAAIAAgACAALwAvACAAVAByAGkAcABsAGUAcwBcAG4AIAAgACAAIAB0AGgAcgBpAGMAZQAsACAAVAByAGkAcABsAGUAdwBpAHMAZQC7AygAcwBlAHQAXwAxACwAcwBlAHQAXwAyACwAcwBlAHQAXwAzACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AZAAgAHQAcgBpAHAAbABlACAAcgBvAHcAcwAgAGIAeQAgAHQAbwB0AGEAbAAgAGkAdABlAG0AcwAgAGkAbgAgAHMAZQB0ACAANABcAG4AIAAgACAAIAB0AGgAcgBpAGMAZQBfACwAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AygAdABoAHIAaQBjAGUALABrACkALABcAG4AIAAgACAAIABrAIIgLAAgACAAIAAgACAAUgBPAFcAUwAoAHQAaAByAGkAYwBlAF8AKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AZAAgAHMAZQB0ACAANAAgAHQAbwAgAG0AYQB0AGMAaAAgAGwAZQBuAGcAdABoACAAbwBmACAAdAByAGkAcABsAGUAXABuACAAIAAgACAAZgBvAHUAcgAsACAAIAAgAFIAZQBzAGkAegBlALsDKABkACwAawCCICAALwAgAGsAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHQAYQBjAGsAIABhAG4AZAAgAGQAaQBzAHAAbABhAHkAXABuACAAIAAgACAAZgBpAG4AYQBsACwAIAAgAEgAUwBUAEEAQwBLACgAdABoAHIAaQBjAGUAXwAsAGYAbwB1AHIAKQAsAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAEIARABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIAAgAEUAYwBoAG8AuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAQgBEAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADIALgAwAFwAbgBcAG4ARABlAHMAYwByAGkAcAB0AGkAbwBuADoAXABuACAAIAAgACAAUgBlAHAAZQBhAHQAcwAgAGUAYQBjAGgAIABlAGwAZQBtAGUAbgB0ACAAaQBuACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgADEARAAgAGEAcgByAGEAeQAgAGEAYwBjAG8AcgBkAGkAbgBnACAAdABvACAAYQAgAHYAZQBjAHQAbwByACAAbwBmAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AHMALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAHUAcABwAG8AcgB0AGUAZAAuACAAUgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgAG0AdQBzAHQAIABiAGUAXABuACAAIAAgACAAbgB1AG0AZQByAGkAYwAgAGEAbgBkACAAZSIgADEALgBcAG4AXABuACAAIAAgACAARQBjAGgAbwC7AyAAbgBvAHIAbQBhAGwAaQB6AGUAcwAgAGIAbwB0AGgAIABpAG4AcAB1AHQAcwAgAHcAaQB0AGgAIABUAE8AQwBPAEwALAAgAGUAeAB0AGUAbgBkAHMAIAB0AGgAZQAgAHIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAIAB3AGgAZQBuAFwAbgAgACAAIAAgAG4AZQBjAGUAcwBzAGEAcgB5ACwAIABhAG4AZAAgAHUAcwBlAHMAIABNAEEAUAAgACsAIABFAFgAUABBAE4ARAAgAHQAbwAgAGcAZQBuAGUAcgBhAHQAZQAgAHQAaABlACAAZQBjAGgAbwBlAGQAIABvAHUAdABwAHUAdAAuACAAVABoAGUAXABuACAAIAAgACAAcgBlAHMAdQBsAHQAIABpAHMAIABhAGwAdwBhAHkAcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgAgACAAIAAtACAAUwBjAGEAbABhAHIAIABvAHIAIAAxAEQALwAyAEQAIABhAHIAcgBhAHkAIAB0AG8AIABiAGUAIABlAGMAaABvAGUAZAAuACAARgBsAGEAdAB0AGUAbgBlAGQAIAB3AGkAdABoACAAVABPAEMATwBMAC4AXABuACAAIAAgACAAcgBlAHAAZQBhAHQAIAAgACAALQAgADEARAAgAGEAcgByAGEAeQAgAG8AZgAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AHMAIAAoAG4AdQBtAGUAcgBpAGMALAAgAGUiIAAxACkALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAYQByAGUAIAB0AHIAZQBhAHQAZQBkACAAYQBzACAAMQDXADEAIABhAHIAcgBhAHkAcwAuAFwAbgAgACAAIAAgACIgIABJAGYAIAByAGUAcABlAGEAdAAgAGgAYQBzACAAYQAgAGQAaQBmAGYAZQByAGUAbgB0ACAAbABlAG4AZwB0AGgAIAB0AGgAYQBuACAAdgBlAGMAdABvAHIALAAgAHQAaABlACAAbABhAHMAdAAgAHIAZQBwAGUAYQB0ACAAdgBhAGwAdQBlAFwAbgAgACAAIAAgACAAIABpAHMAIABlAHgAdABlAG4AZABlAGQAIAB0AG8AIABtAGEAdABjAGgAIAB0AGgAZQAgAHYAZQBjAHQAbwByACAAbABlAG4AZwB0AGgALgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABpAHMAIABhAGwAdwBhAHkAcwAgAGEAIAB2AGUAcgB0AGkAYwBhAGwAIABhAHIAcgBhAHkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4ARQBjAGgAbwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgAsAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAXABuAFwAbgBJAEYAKABPAFIAKABJAFMAVABFAFgAVAAoAHIAZQBwAGUAYQB0ACkALAAgAHIAZQBwAGUAYQB0ACAAPAA9ACAAMAApACwAIABcACIAIwBWAEEATABVAEUAIQBcACIALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABpAG4AcAB1AHQAcwBcAG4AIAAgACAAIAB2AGUAYwB0AG8AcgAsACAAVABPAEMATwBMACgAdgBlAGMAdABvAHIAKQAsAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACwAIABUAE8AQwBPAEwAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAVgBoACwAIAAgACAAIAAgAFIATwBXAFMAKAB2AGUAYwB0AG8AcgApACwAXABuACAAIAAgACAAUgBoACwAIAAgACAAIAAgAFIATwBXAFMAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAIAAoAGUAeAB0AGUAbgBkACAAbABhAHMAdAAgAHYAYQBsAHUAZQAgAGkAZgAgAG4AZQBlAGQAZQBkACkAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgAEkARgAoAFYAaAAgADwAPgAgAFIAaAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAcgBlAHAAZQBhAHQALAAgAFYAaAAsACwAIABAAFQAQQBLAEUAKAByAGUAcABlAGEAdAAsACAALQAxACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgBlAHAAZQBhAHQAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AcwBpAG8AbgAgAGUAbgBnAGkAbgBlAFwAbgAgACAAIAAgAEUAeAB0AGUAbgBkALsDLABMAEEATQBCAEQAQQAoAGUAYQBjAGgAXwBlAGwAZQBtAGUAbgB0ACwAIAByAF8ALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAZQBhAGMAaABfAGUAbABlAG0AZQBuAHQALAAgAHIAXwAsACwAIABlAGEAYwBoAF8AZQBsAGUAbQBlAG4AdAApACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGwAaQB2AGUAcgAgAGUAYwBoAG8AZQBkACAAbwB1AHQAcAB1AHQAXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsAEYATABBAFQAVABFAE4AKABNAEEAUAAoAHYAZQBjAHQAbwByACwAIAByACwAIABFAHgAdABlAG4AZAC7AykAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAQgBEAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAAQgBsAG8AYwBrAHMAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAQgBEAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAHQAbwB0AHkAcABlAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAATgBvAG4AZQAgACgAcgBlAHAAdQByAHAAbwBzAGUAZAAgAEcAcgBhAGkAbgC7AykAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABQAGEAcgB0AGkAdABpAG8AbgBzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIAByAGUAYwB0AGEAbgBnAHUAbABhAHIAIABiAGwAbwBjAGsAcwAgAG8AZgAgAHMAaQB6AGUAIABkAGUAcAB0AGgAIADXACAAdwBpAGQAdABoAC4AXABuACAAIAAgACAARQBhAGMAaAAgAGIAbABvAGMAawAgAGkAcwAgAGUAeAB0AHIAYQBjAHQAZQBkACAAYQBzACAAYQAgAG4AZQBzAHQAZQBkACAAYQByAHIAYQB5ACAAYQBuAGQAIAB3AHIAYQBwAHAAZQBkACAAaQBuACAAYQAgAGwAaQBzAHQAIABsAGkAdABlAHIAYQBsACwAXABuACAAIAAgACAAcAByAG8AZAB1AGMAaQBuAGcAIABhACAAbABpAHMAdAARIG8AZgARIGwAaQBzAHQAcwAgAHMAdAByAHUAYwB0AHUAcgBlADoAXABuAFwAbgAgACAAIAAgACAAIAAgACAAewAgAHsAYgBsAG8AYwBrAIEgfQAsACAAewBiAGwAbwBjAGsAgiB9ACwAIAAmICAAfQBcAG4AXABuACAAIAAgACAAQgBsAG8AYwBrAHMAuwMgAHIAbwB1AG4AZABzACAAdQBwACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGIAbABvAGMAawBzACAAcwBvACAAcABhAHIAdABpAGEAbAAgAGUAZABnAGUAIABiAGwAbwBjAGsAcwAgAGEAcgBlAFwAbgAgACAAIAAgAGkAbgBjAGwAdQBkAGUAZAAuACAARQBhAGMAaAAgAGIAbABvAGMAawAgAGkAcwAgAGUAeAB0AHIAYQBjAHQAZQBkACAAdQBzAGkAbgBnACAASQBOAEQARQBYACAAbwB2AGUAcgAgAGcAZQBuAGUAcgBhAHQAZQBkACAAcgBvAHcALwBjAG8AbAB1AG0AbgBcAG4AIAAgACAAIABhAG4AYwBoAG8AcgAgAGcAcgBpAGQAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAcABhAHIAdABpAHQAaQBvAG4ALgBcAG4AIAAgACAAIABkAGUAcAB0AGgAIAAgACAAIAAgACAALQAgAEIAbABvAGMAawAgAGgAZQBpAGcAaAB0AC4AXABuACAAIAAgACAAdwBpAGQAdABoACAAIAAgACAAIAAgAC0AIABCAGwAbwBjAGsAIAB3AGkAZAB0AGgALgBcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAGkAcwAgAGEAIABsAGkAcwB0ACAAbwBmACAAbgBlAHMAdABlAGQAIABhAHIAcgBhAHkAcwAsACAAbgBvAHQAIABhACAAcwBwAGkAbABsAGUAZAAgADIARAAgAGcAcgBpAGQALgBcAG4AIAAgACAAIAAiICAAVQBzAGUAIABGAEwAQQBUAFQARQBOACAAdABvACAAcwBwAGkAbABsACAAYgBsAG8AYwBrAHMAIABpAG4AdABvACAAYQAgAHQAYQBiAGwAZQAgAGkAZgAgAG4AZQBlAGQAZQBkAC4AXABuACAAIAAgACAAIiAgAFQAaABpAHMAIABvAHAAZQByAGEAdABvAHIAIABpAHMAIABlAHgAcABlAHIAaQBtAGUAbgB0AGEAbAAgAGEAbgBkACAAaQBuAHQAZQBuAGQAZQBkACAAZgBvAHIAIABuAGUAcwB0AGUAZAARIGEAcgByAGEAeQAgAHQAZQBzAHQAaQBuAGcALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AQgBsAG8AYwBrAHMAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACwAXABuACAAIAAgACAAZABlAHAAdABoACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAXwAyAEQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5AF8AMgBEACkALABcAG4AXABuACAAIAAgACAALwAvACAATgB1AG0AYgBlAHIAIABvAGYAIABiAGwAbwBjAGsAcwAgACgAcgBvAHUAbgBkAGUAZAAgAHUAcAApAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIABSAE8AVQBOAEQAVQBQACgAaAAgAC8AIABkAGUAcAB0AGgALAAgADAAKQAsAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIABSAE8AVQBOAEQAVQBQACgAdwAgAC8AIAB3AGkAZAB0AGgALAAgADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAGwAbwBjAGsAIABhAG4AYwBoAG8AcgAgAGcAcgBpAGQAcwAgACgAZABlAGYAZQByAHIAZQBkACkAXABuACAAIAAgACAAZABvAHcAbgAsACAAIAAgAEwAQQBNAEIARABBACgAUwBFAFEAVQBFAE4AQwBFACgAeAAsACwAMQAsAGQAZQBwAHQAaAApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAeQAsADEALAAwACkAKQAsAFwAbgAgACAAIAAgAGEAYwByAG8AcwBzACwAIABMAEEATQBCAEQAQQAoAFMARQBRAFUARQBOAEMARQAoACwAeQAsADEALAB3AGkAZAB0AGgAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAB4ACwALAAxACwAMAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG4AdgBlAHIAdAAgAG0AYQB0AHIAaQBjAGUAcwAgAHQAbwAgAGwAaQBzAHQAcwBcAG4AIAAgACAAIABUAG8ATABpAHMAdAC7AywAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAIABjACwAXABuACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABpACwAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKABkAGUAcAB0AGgALAAsAHIAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKAAsAHcAaQBkAHQAaAAsADEALAAwACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABqACwAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABTAEUAUQBVAEUATgBDAEUAKAAsAHcAaQBkAHQAaAAsAGMAKQAgACoAIABTAEUAUQBVAEUATgBDAEUAKABkAGUAcAB0AGgALAAsADEALAAwACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABiAGwAbwBjAGsALAAgACAASQBOAEQARQBYACgAYQByAHIAYQB5AF8AMgBEACwAIABpACgAKQAsACAAagAoACkAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcwB1AGwAdAAsACAAewBiAGwAbwBjAGsAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAByAGUAcwB1AGwAdABcAG4AIAAgACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABDAG8AbgB2AGUAcgB0ACAAbABlAHYAZQBsABEgMgAgAG0AYQB0AHIAaQBjAGUAcwAgAHQAbwAgAGwAaQBzAHQAcwBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByACwAIABNAEEAUAAoAGQAbwB3AG4AKAApACwAIABhAGMAcgBvAHMAcwAoACkALAAgAFQAbwBMAGkAcwB0ALsDKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABXAGkAbgBkAG8AdwBlAGQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAQgBEAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAATQBHAHIAaQBkALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABFAHgAdAByAGEAYwB0AHMAIABhAGwAbAAgAG8AdgBlAHIAbABhAHAAcABpAG4AZwAgAHcAaQBuAGQAbwB3AHMAIABvAGYAIABzAGkAegBlACAAZABlAHAAdABoACAA1wAgAHcAaQBkAHQAaAAgAGYAcgBvAG0AIABhACAAMgBEACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAARQBhAGMAaAAgAHcAaQBuAGQAbwB3ACAAaQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAYQAgAG4AZQBzAHQAZQBkACAAYQByAHIAYQB5ACAAdwByAGEAcABwAGUAZAAgAGkAbgAgAGEAIABsAGkAcwB0ACAAbABpAHQAZQByAGEAbAAsAFwAbgAgACAAIAAgAHAAcgBvAGQAdQBjAGkAbgBnACAAYQBuACAAYQByAHIAYQB5AC0AbwBmAC0AbABpAHMAdABzACAAcwB0AHIAdQBjAHQAdQByAGUALgBcAG4AXABuACAAIAAgACAAVwBpAG4AZABvAHcAZQBkALsDIAB1AHMAZQBzACAAbQBlAHMAaAAtAGcAcgBpAGQAIABvAGYAZgBzAGUAdABzACAAZwBlAG4AZQByAGEAdABlAGQAIABmAHIAbwBtACAATQBHAHIAaQBkALsDIAB0AG8AIABjAG8AbgBzAHQAcgB1AGMAdABcAG4AIAAgACAAIAB3AGkAbgBkAG8AdwAgAGMAbwBvAHIAZABpAG4AYQB0AGUAcwAgAGEAbgBkACAATQBBAEsARQBBAFIAUgBBAFkAIAB0AG8AIABhAHMAcwBlAG0AYgBsAGUAIAB0AGgAZQAgAGYAdQBsAGwAIAB3AGkAbgBkAG8AdwAgAGYAYQBiAHIAaQBjAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAYQByAHIAYQB5AF8AMgBEACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAAoADEARAAgAGEAcgByAGEAeQBzACAAYQBuAGQAIABzAGMAYQBsAGEAcgBzACAAYQByAGUAIAByAGUAagBlAGMAdABlAGQAKQAuAFwAbgAgACAAIAAgAGQAZQBwAHQAaAAgACAAIAAgACAAIAAtACAAVABvAHQAYQBsACAAcgBvAHcAcwAgAGkAbgAgAGUAYQBjAGgAIAB3AGkAbgBkAG8AdwAuAFwAbgAgACAAIAAgAFsAdwBpAGQAdABoAF0AIAAgACAAIAAtACAAVABvAHQAYQBsACAAYwBvAGwAdQBtAG4AcwAgAGkAbgAgAGUAYQBjAGgAIAB3AGkAbgBkAG8AdwAuACAARABlAGYAYQB1AGwAdABzACAAdABvACAAZABlAHAAdABoAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAATwB1AHQAcAB1AHQAIABpAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABsAGkAcwB0AHMALAAgAG4AbwB0ACAAYQAgAHMAcABpAGwAbABlAGQAIAAyAEQAIABnAHIAaQBkAC4AXABuACAAIAAgACAAIiAgAFUAcwBlACAARgBMAEEAVABUAEUATgAgAHQAbwAgAHMAcABpAGwAbAAgAHcAaQBuAGQAbwB3AHMAIABpAG4AdABvACAAYQAgAHQAYQBiAGwAZQAgAGkAZgAgAG4AZQBlAGQAZQBkAC4AXABuACAAIAAgACAAIiAgAFIAZQBqAGUAYwB0AHMAIAAxAEQAIABhAHIAcgBhAHkAcwAgAGEAbgBkACAAcwBjAGEAbABhAHIAcwAgAHQAbwAgAHAAcgBlAHMAZQByAHYAZQAgADIARAAgAHcAaQBuAGQAbwB3ACAAcwBlAG0AYQBuAHQAaQBjAHMALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVwBpAG4AZABvAHcAZQBkALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQBfADIARAAsAFwAbgAgACAAIAAgAGQAZQBwAHQAaAAsAFwAbgAgACAAIAAgAFsAdwBpAGQAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABPAHAAdABpAG8AbgBhAGwAIAB3AGkAZAB0AGgAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAB3AGkAZAB0AGgAKQAsACAAZABlAHAAdABoACwAIAB3AGkAZAB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAZgBlAHIAZQBuAGMAZQAgAHMAaABhAHAAZQAgAGYAbwByACAAbQBlAHMAaAAgAGcAcgBpAGQAXABuACAAIAAgACAAawBlAHIAbgBlAGwALAAgACAAIAAgACAARQBYAFAAQQBOAEQAKAAwACwAIABkAGUAcAB0AGgALAAgAHcAaQBkAHQAaAAsACAAMAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQBfADIARAApACwAXABuACAAIAAgACAAdwAsACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQBfADIARAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEgAYQBsAHQAaQBuAGcAIABzAGMAZQBuAGEAcgBpAG8AXABuACAAIAAgACAASQBuAFYAYQBsAGkAZABEAFcAPwAsACAATwBSACgASQBTAFQARQBYAFQAKABkAGUAcAB0AGgAKQAsACAASQBTAFQARQBYAFQAKAB3AGkAZAB0AGgAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGQAZQBwAHQAaAAgADwAIAAxACwAIAB3AGkAZAB0AGgAIAA8ACAAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGQAZQBwAHQAaAAgAD4AIABoACwAIAB3AGkAZAB0AGgAIAA+ACAAdwApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFQAcgBpAHYAaQBhAGwAIABjAGEAcwBlAFwAbgAgACAAIAAgAE8AbgBlAFcAaQBuAGQAbwB3AD8ALAAgAEEATgBEACgAaAAgAD0AIABkAGUAcAB0AGgALAAgAHcAIAA9ACAAdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAASQBGACgASQBuAFYAYQBsAGkAZABEAFcAPwAsACAAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIABJAEYAKABPAG4AZQBXAGkAbgBkAG8AdwA/ACwAIAB7AGEAcgByAGEAeQBfADIARAB9ACwAXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAAVwBpAG4AZABvAHcAIABjAG8AdQBuAHQAcwBcAG4AIAAgACAAIABrAF8AaAAsACAAIAAgACAAIABoACAALQAgAGQAZQBwAHQAaAAgACsAIAAxACwAXABuACAAIAAgACAAawBfAHcALAAgACAAIAAgACAAdwAgAC0AIAB3AGkAZAB0AGgAIAArACAAMQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGUAcwBoACAAZwByAGkAZAAgAG8AZgBmAHMAZQB0AHMAXABuACAAIAAgACAAeAAsACAAIAAgACAAIAAgACAASQBGACgAZABlAHAAdABoACAAPQAgADEALAAgAGsAZQByAG4AZQBsACwAIABNAEcAcgBpAGQAuwMoAGsAZQByAG4AZQBsACkAIAAtACAAMQApACwAXABuACAAIAAgACAAeQAsACAAIAAgACAAIAAgACAASQBGACgAdwBpAGQAdABoACAAPQAgADEALAAgAGsAZQByAG4AZQBsACwAIABNAEcAcgBpAGQAuwMoAGsAZQByAG4AZQBsACwAIAAxACkAIAAtACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFcAaQBuAGQAbwB3AGkAbgBnAFwAbgAgACAAIAAgAHcAaQBuAGQAbwB3AHMALAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAawBfAGgALAAgAGsAXwB3ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAGkALAAgAGoALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAYQByAHIAYQB5AF8AMgBEACwAIABpACAAKwAgAHgALAAgAGoAIAArACAAeQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAB3AGkAbgBkAG8AdwBzAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIAAgACAAIABDAG8AbgB2AG8AbAB2AGUAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgACAAIAAgAFQAQgBEAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAgADIALgAwAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAIAAgACAAVwBpAG4AZABvAHcAZQBkALsDXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABQAGUAcgBmAG8AcgBtAHMAIABhACAAcwBsAGkAZABpAG4AZwARIHcAaQBuAGQAbwB3ACAAYwBvAG4AdgBvAGwAdQB0AGkAbwBuACAAbwB2AGUAcgAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIAB1AHMAaQBuAGcAIABhACAAMgBEACAAawBlAHIAbgBlAGwALgBcAG4AIAAgACAAIABFAGEAYwBoACAAdwBpAG4AZABvAHcAIABlAHgAdAByAGEAYwB0AGUAZAAgAGYAcgBvAG0AIAB0AGgAZQAgAGkAbgBwAHUAdAAgAGEAcgByAGEAeQAgAGgAYQBzACAAdABoAGUAIABzAGEAbQBlACAAZABpAG0AZQBuAHMAaQBvAG4AcwAgAGEAcwAgAHQAaABlAFwAbgAgACAAIAAgAGsAZQByAG4AZQBsAC4AIABBACAAcgBlAGQAdQBjAGUAcgAgAGYAdQBuAGMAdABpAG8AbgAgAGkAcwAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABlAGEAYwBoACAAdwBpAG4AZABvAHcAIAB0AG8AIABwAHIAbwBkAHUAYwBlACAAdABoAGUAIABvAHUAdABwAHUAdAAuAFwAbgBcAG4AIAAgACAAIABJAGYAIABuAG8AIAByAGUAZAB1AGMAZQByACAAZgB1AG4AYwB0AGkAbwBuACAAaQBzACAAcwB1AHAAcABsAGkAZQBkACwAIABDAG8AbgB2AG8AbAB2AGUAuwMgAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAGEAIABkAG8AdAARIHAAcgBvAGQAdQBjAHQAXABuACAAIAAgACAAcgBlAGQAdQBjAGUAcgA6ACAAUwBVAE0AKABGAEwAQQBUAFQARQBOACgAdgApACAAKgAgAGsAZQByAG4AZQBsACkALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdABvACAAdwBoAGkAYwBoACAAdABoAGUAIABrAGUAcgBuAGUAbAAgAGkAcwAgAGEAcABwAGwAaQBlAGQALgBcAG4AIAAgACAAIABrAGUAcgBuAGUAbAAgACAAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAZABlAGYAaQBuAGkAbgBnACAAdABoAGUAIABzAGwAaQBkAGkAbgBnACAAdwBpAG4AZABvAHcAIABkAGkAbQBlAG4AcwBpAG8AbgBzAC4AXABuACAAIAAgACAAWwBmAHUAbgBjAHQAaQBvAG4AXQAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHIAZQBkAHUAYwBlAHIAIABMAEEATQBCAEQAQQAgAGEAYwBjAGUAcAB0AGkAbgBnACAAYQAgAHMAaQBuAGcAbABlACAAYQByAHIAYQB5ACAAYQByAGcAdQBtAGUAbgB0AC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAFMAVQBNACgARgBMAEEAVABUAEUATgAoAHYAKQAgACoAIABrAGUAcgBuAGUAbAApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgAFwAIgAjAEsARQBSAE4ARQBMACEAXAAiACAAaQBmACAAdABoAGUAIABrAGUAcgBuAGUAbAAgAGkAcwAgAGwAYQByAGcAZQByACAAdABoAGEAbgAgAHQAaABlACAAaQBuAHAAdQB0ACAAYQByAHIAYQB5AC4AXABuACAAIAAgACAAIiAgAFIAZQB0AHUAcgBuAHMAIABcACIAIwBGAFUATgBDAFQASQBPAE4AIQBcACIAIABpAGYAIAB0AGgAZQAgAHIAZQBkAHUAYwBlAHIAIABpAHMAIABuAG8AdAAgAGEAIAB2AGEAbABpAGQAIABMAEEATQBCAEQAQQAuAFwAbgAgACAAIAAgACIgIABTAGMAYQBsAGEAcgBzACAAYQByAGUAIAB0AHIAZQBhAHQAZQBkACAAYQBzACAAMQDXADEAIABhAHIAcgBhAHkAcwAgAGEAbgBkACAAbQBhAHAAcABlAGQAIAB0AGgAcgBvAHUAZwBoACAAdABoAGUAIAByAGUAZAB1AGMAZQByAC4AXABuACAAIAAgACAAIiAgAFIAZQBkAHUAYwBlAHIAIABiAGUAaABhAHYAaQBvAHIAIABpAHMAIAB1AHMAZQByABEgZABlAGYAaQBuAGUAZAA7ACAAYQByAHIAYQB5AHMAIABuAGUAZQBkACAAbgBvAHQAIABiAGUAIABuAHUAbQBlAHIAaQBjAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAEMAbwBuAHYAbwBsAHYAZQC7Az0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQByAHIAYQB5ACwAXABuACAAIAAgACAAawBlAHIAbgBlAGwALABcAG4AIAAgACAAIABbAGYAdQBuAGMAdABpAG8AbgBdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEEAcgByAGEAeQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKABhAHIAcgBhAHkAKQAsACAAIAAgACAAdwAsACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEsAZQByAG4AZQBsACAAZABpAG0AZQBuAHMAaQBvAG4AcwBcAG4AIAAgACAAIABrAGUAcgBuAGUAbABfAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAUgBPAFcAUwAoAGsAZQByAG4AZQBsACkALABcAG4AIAAgACAAIABrAGUAcgBuAGUAbABfAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGsAZQByAG4AZQBsACkALABcAG4AXABuACAAIAAgACAALwAvACAASwBlAHIAbgBlAGwAIABtAHUAcwB0ACAAZgBpAHQAIABpAG4AcwBpAGQAZQAgAGEAcgByAGEAeQBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAEsAZQByAG4AZQBsAD8ALAAgACAAIAAgACAATwBSACgAawBlAHIAbgBlAGwAXwBoAGUAaQBnAGgAdAAgAD4AIABoACwAIABrAGUAcgBuAGUAbABfAHcAaQBkAHQAaAAgAD4AIAB3ACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBjAGEAbABhAHIAIABoAGEAbgBkAGwAaQBuAGcAXABuACAAIAAgACAASQBzAFMAYwBhAGwAYQByAD8ALAAgACAAIAAgACAAIAAgACAAIAAgAEEATgBEACgAaAAgAD0AIAAxACwAIAB3ACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgBLAGUAcgBuAGUAbAA/ACwAIAAgACAAIABBAE4ARAAoAGsAZQByAG4AZQBsAF8AaABlAGkAZwBoAHQAIAA9ACAAMQAsACAAawBlAHIAbgBlAGwAXwB3AGkAZAB0AGgAIAA9ACAAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIAByAGUAZAB1AGMAZQByACAAPQAgAGQAbwB0ACAAcAByAG8AZAB1AGMAdABcAG4AIAAgACAAIABmAHUAbgBjAHQAaQBvAG4ALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABmAHUAbgBjAHQAaQBvAG4AKQAsAEwAQQBNAEIARABBACgAdgAsACAAUwBVAE0AKABGAEwAQQBUAFQARQBOACgAdgApACAAKgAgAGsAZQByAG4AZQBsACkAKQAsAGYAdQBuAGMAdABpAG8AbgApACwAXABuACAAIAAgACAASQBuAHYAYQBsAGkAZABGAHUAbgBjAHQAaQBvAG4APwAsACAAIAAgAFQAWQBQAEUAKABmAHUAbgBjAHQAaQBvAG4AKQAgADwAPgAgADEAMgA4ACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBhAGwAYQByACAAbwByACAAcwBjAGEAbABhAHIAESBrAGUAcgBuAGUAbAAgAGMAYQBzAGUAIACSISAAcwBpAG0AcABsAGUAIABNAEEAUABcAG4AIAAgACAAIABTAHQAYQBuAGQAYQByAGQATQBhAHAALAAgACAAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABNAEEAUAAoAGEAcgByAGEAeQAsACAAZgB1AG4AYwB0AGkAbwBuACkAKQAsAFwAbgBcAG4ALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAEsAZQByAG4AZQBsAD8ALAAgAFwAIgAjAEsARQBSAE4ARQBMACEAXAAiACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABGAHUAbgBjAHQAaQBvAG4APwAsAFwAIgAjAEYAVQBOAEMAVABJAE8ATgAhAFwAIgAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAKABJAHMAUwBjAGEAbABhAHIAPwApACAAKwAgACgASQBzAFMAYwBhAGwAYQByAEsAZQByAG4AZQBsAD8AKQAsAFMAdABhAG4AZABhAHIAZABNAGEAcAAoACkALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAAdwBpAG4AZABvAHcAcwAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFcAaQBuAGQAbwB3AGUAZAC7AygAYQByAHIAYQB5ACwAawBlAHIAbgBlAGwAXwBoAGUAaQBnAGgAdAAsAGsAZQByAG4AZQBsAF8AdwBpAGQAdABoACkALABcAG4AIAAgACAAIABjAG8AbgB2AG8AbAB1AHQAaQBvAG4ALAAgACAAIAAgACAAIAAgACAATQBBAFAAKAB3AGkAbgBkAG8AdwBzACwAZgB1AG4AYwB0AGkAbwBuACkALABcAG4AIAAgACAAIABjAG8AbgB2AG8AbAB1AHQAaQBvAG4AXABuAFwAbgApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAQgBEAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAIAAgACAARwByAGkAZABMAG8AbwBrAHUAcAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAGUAYQByAGMAaABlAHMAIABhACAAMgBEACAAYQByAHIAYQB5ACAAZgBvAHIAIABtAGEAdABjAGgAZQBzACAAYQBuAGQAIAByAGUAdAB1AHIAbgBzACAAdABoAGUAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAaQB0AGUAbQBzACAAZgByAG8AbQAgAGEAXABuACAAIAAgACAAcwBlAGMAbwBuAGQAIAAyAEQAIABhAHIAcgBhAHkALgAgAEcAcgBpAGQATABvAG8AawB1AHAAuwMgAHAAZQByAGYAbwByAG0AcwAgAGEAIABmAGwAYQB0AHQAZQBuAGUAZAAgAFgATQBBAFQAQwBIACAAbwB2AGUAcgAgAHQAaABlACAAcwBlAGEAcgBjAGgAXABuACAAIAAgACAAZwByAGkAZAAsACAAYwBvAG4AdgBlAHIAdABzACAAdABoAGUAIABsAGkAbgBlAGEAcgAgAGkAbgBkAGUAeAAgAGIAYQBjAGsAIAB0AG8AIAAyAEQAIABjAG8AbwByAGQAaQBuAGEAdABlAHMALAAgAGEAbgBkACAAcgBlAHQAcgBpAGUAdgBlAHMAIAB0AGgAZQBcAG4AIAAgACAAIABjAG8AcgByAGUAcwBwAG8AbgBkAGkAbgBnACAAZQBsAGUAbQBlAG4AdAAgAGYAcgBvAG0AIAByAGUAdAB1AHIAbgBfAGEAcgByAGEAeQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGwAbwBvAGsAdQBwAF8AdgBhAGwAdQBlAHMAIAAgACAALQAgAFYAYQBsAHUAZQBzACAAdABvACAAcwBlAGEAcgBjAGgAIABmAG8AcgAgACgAcwBjAGEAbABhAHIAIABvAHIAIABhAHIAcgBhAHkAKQAuAFwAbgAgACAAIAAgAGwAbwBvAGsAdQBwAF8AYQByAHIAYQB5ACAAIAAgACAALQAgADIARAAgAGEAcgByAGEAeQAgAHQAbwAgAHMAZQBhAHIAYwBoAC4AXABuACAAIAAgACAAcgBlAHQAdQByAG4AXwBhAHIAcgBhAHkAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAZgByAG8AbQAgAHcAaABpAGMAaAAgAG0AYQB0AGMAaABlAGQAIABpAHQAZQBtAHMAIABhAHIAZQAgAHIAZQB0AHUAcgBuAGUAZAAuAFwAbgBcAG4ATwBwAHQAaQBvAG4AYQBsACAAcABhAHIAYQBtAGUAdABlAHIAcwAgACgAbQBhAHQAYwBoAGkAbgBnACAAWABMAE8ATwBLAFUAUAAvAFgATQBBAFQAQwBIACAAZABlAGYAYQB1AGwAdABzACkAOgBcAG4AIAAgACAAIABbAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkAF0AIAAgAC0AIABWAGEAbAB1AGUAIAByAGUAdAB1AHIAbgBlAGQAIABpAGYAIABuAG8AIABtAGEAdABjAGgAIABpAHMAIABmAG8AdQBuAGQALgAgAEQAZQBmAGEAdQBsAHQAIAA9ACAAIwBOAC8AQQAuAFwAbgAgACAAIAAgAFsAbQBhAHQAYwBoAF8AbQBvAGQAZQBdACAAIAAgACAALQAgAE0AYQB0AGMAaAAgAGIAZQBoAGEAdgBpAG8AcgAuACAARABlAGYAYQB1AGwAdAAgAD0AIAAwACAAKABlAHgAYQBjAHQAIABtAGEAdABjAGgAKQAuAFwAbgAgACAAIAAgAFsAcwBlAGEAcgBjAGgAXwBtAG8AZABlAF0AIAAgACAALQAgAFMAZQBhAHIAYwBoACAAZABpAHIAZQBjAHQAaQBvAG4ALgAgAEQAZQBmAGEAdQBsAHQAIAA9ACAAMQAgACgAZgBpAHIAcwB0ABEgdABvABEgbABhAHMAdAApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAgAGkAZgAgAGwAbwBvAGsAdQBwAF8AYQByAHIAYQB5ACAAYQBuAGQAIAByAGUAdAB1AHIAbgBfAGEAcgByAGEAeQAgAHMAaABhAHAAZQBzACAAZABpAGYAZgBlAHIALgBcAG4AIAAgACAAIAAiICAAUgBlAHQAdQByAG4AcwAgAFwAIgAjAE4ALwBBAFwAIgAgAGkAZgAgAGwAbwBvAGsAdQBwAF8AdgBhAGwAdQBlAHMAIABhAHIAZQAgAG4AbwB0ACAAcAByAGUAcwBlAG4AdAAgAGkAbgAgAGwAbwBvAGsAdQBwAF8AYQByAHIAYQB5AC4AXABuACAAIAAgACAAIiAgAFUAcwBlAHMAIABYAE0AQQBUAEMASAAgAG8AdgBlAHIAIABUAE8AQwBPAEwAKABtAGEAdABjAGgAXwBhAHIAcgBhAHkAKQAgAGYAbwByACAAZgBsAGEAdAB0AGUAbgBlAGQAIABzAGUAYQByAGMAaAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBHAHIAaQBkAEwAbwBvAGsAdQBwALsDPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABsAG8AbwBrAHUAcABfAHYAYQBsAHUAZQBzACwAXABuACAAIAAgACAAbQBhAHQAYwBoAF8AYQByAHIAYQB5ACwAXABuACAAIAAgACAAcgBlAHQAdQByAG4AXwBhAHIAcgBhAHkALABcAG4AIAAgACAAIABbAGkAZgBfAG4AbwB0AF8AZgBvAHUAbgBkAF0ALABcAG4AIAAgACAAIABbAG0AYQB0AGMAaABfAG0AbwBkAGUAXQAsAFwAbgAgACAAIAAgAFsAcwBlAGEAcgBjAGgAXwBtAG8AZABlAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABTAGgAYQBwAGUAcwBcAG4AIAAgACAAIABoAGUAaQBnAGgAdACBICwAIAAgACAAUgBPAFcAUwAoAG0AYQB0AGMAaABfAGEAcgByAGEAeQApACwAIAAgACAAIAAgAHcAaQBkAHQAaACBICwAIAAgAEMATwBMAFUATQBOAFMAKABtAGEAdABjAGgAXwBhAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0AIIgLAAgACAAIABSAE8AVwBTACgAcgBlAHQAdQByAG4AXwBhAHIAcgBhAHkAKQAsACAAIAAgACAAdwBpAGQAdABoAIIgLAAgACAAQwBPAEwAVQBNAE4AUwAoAHIAZQB0AHUAcgBuAF8AYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAAVgBhAGwAaQBkAGEAdABpAG8AbgBcAG4AIAAgACAAIABTAGgAYQBwAGUATQBpAHMATQBhAHQAYwBoAD8ALAAgAE8AUgAoAGgAZQBpAGcAaAB0AIEgIAA8AD4AIABoAGUAaQBnAGgAdACCICwAdwBpAGQAdABoAIEgIAA8AD4AIAB3AGkAZAB0AGgAgiApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAYQByAGwAeQAgAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgAGkAZgAgAG0AZQBtAGIAZQByAHMAaABpAHAAIAA9ACAARgBBAEwAUwBFAFwAbgAgACAAIAAgAE4AbwB0AFAAcgBlAHMAZQBuAHQAPwAsACAAIAAgACAATgBPAFQAKABIAEEAUwBBAEwATAAoAG0AYQB0AGMAaABfAGEAcgByAGEAeQAsAGwAbwBvAGsAdQBwAF8AdgBhAGwAdQBlAHMAKQApACwAXABuAFwAbgAgACAAIAAgAEkARgAoAE4AbwB0AFAAcgBlAHMAZQBuAHQAPwAsACMATgAvAEEALABcAG4AXABuACAAIAAgACAAIAAgACAAIABJAEYAKABTAGgAYQBwAGUATQBpAHMATQBhAHQAYwBoAD8ALAAjAFYAQQBMAFUARQAhACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbABcAG4AIAAgACAAIABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAAsACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAaQBmAF8AbgBvAHQAXwBmAG8AdQBuAGQAKQAsAE4AQQAoACkALABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAApACwAXABuACAAIAAgACAAbQBhAHQAYwBoAF8AbQBvAGQAZQAsACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAG0AYQB0AGMAaABfAG0AbwBkAGUAKQAsADAALABtAGEAdABjAGgAXwBtAG8AZABlACkALABcAG4AIAAgACAAIABzAGUAYQByAGMAaABfAG0AbwBkAGUALAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcwBlAGEAcgBjAGgAXwBtAG8AZABlACkALAAxACwAcwBlAGEAcgBjAGgAXwBtAG8AZABlACkALABcAG4AXABuACAAIAAgACAALwAvACAATQBhAHQAYwBoACAAcABvAGkAbgB0AHMAIABhAG4AZAAgAGkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAUgAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAE0AQQBUAEMASAAoAGwAbwBvAGsAdQBwAF8AdgBhAGwAdQBlAHMALABUAE8AQwBPAEwAKABtAGEAdABjAGgAXwBhAHIAcgBhAHkAKQAsAG0AYQB0AGMAaABfAG0AbwBkAGUALABzAGUAYQByAGMAaABfAG0AbwBkAGUAKQAsAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAUQBVAE8AVABJAEUATgBUACgAUgAgAC0AIAAxACwAdwBpAGQAdABoAIEgKQAgACsAIAAxACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAE8ARAAoAFIAIAAtACAAMQAsACAAdwBpAGQAdABoAIEgKQAgACsAMQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAcwB1AGwAdABcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgACAAIAAgAEkARgBOAEEAKABJAE4ARABFAFgAKAByAGUAdAB1AHIAbgBfAGEAcgByAGEAeQAsAGkALABqACkALABpAGYAXwBuAG8AdABfAGYAbwB1AG4AZAApACwAXABuACAAIAAgACAAXABuACAAIAAgACAAZgBpAG4AYQBsAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwBUAEIARABdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIABOAGEAdgBpAGcAYQB0AGUAMgBEALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIABDAG8AbgB2AG8AbAB2AGUAuwMsACAARwByAGkAZABMAG8AbwBrAHUAcAC7AywAIABNAEcAcgBpAGQAuwMsACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEwAbwBjAGEAdABlAHMAIABhACAAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbAAgACgAMgBEACAAYQByAHIAYQB5ACkAIABpAG4AIABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQAIABhAG4AZAAgAHIAZQB0AHUAcgBuAHMAIABhACAAcwBoAGEAcABlACAAZgByAG8AbQAgAHQAaABlAFwAbgAgACAAIAAgAE0AbwBvAHIAZQAgAG4AZQBpAGcAaABiAG8AcgBoAG8AbwBkACAAcgBlAGwAYQB0AGkAdgBlACAAdABvACAAdABoAGUAIABtAGEAdABjAGgAIABsAG8AYwBhAHQAaQBvAG4ALgBcAG4AXABuACAAIAAgACAATQBvAG8AcgBlACAATgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAgACAAMgAgACAAIAAzAFwAbgAgACAAIAAgACAAIAAgACAANAAgACAAIAA1ACAAIAAgADYAXABuACAAIAAgACAAIAAgACAAIAA3ACAAIAAgADgAIAAgACAAOQBcAG4AIAAgACAAIABcAG4AIAAgACAAIAA1ACAAPQAgAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAIABpAG4AIABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQAXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbAAgACAAIAAgACAAIAAtACAAIAAgADIARAAgAHMAaABhAHAAZQAgAG8AcgAgAGEAcgByAGEAeQAgAHQAbwAgAGwAbwBjAGEAdABlAFwAbgAgACAAIAAgAG0AYQB0AGMAaABfAGEAcgByAGEAeQBfADIARAAgACAAIAAgACAALQAgACAAIAAyAEQAIABzAG8AdQByAGMAZQAgAGEAcgByAGEAeQAgAGkAbgAgAHcAaABpAGMAaAAgAHQAbwAgAGwAbwBjAGEAdABlACAAdABoAGUAIABrAGUAcgBuAGUAbABcAG4AXABuAE8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABbAHIAZQB0AHUAcgBuAF8AZABpAHIAZQBjAHQAaQBvAG4AXQAgAC0AIAAgACAASQBuAHQAZQBnAGUAcgAgACgAMQAgAHQAbwAgADkAKQAgAGkAbgBkAGkAYwBhAHQAaQBuAGcAIAB3AGgAaQBjAGgAIABNAG8AbwByAGUAIABuAGUAaQBnAGgAYgBvAHIAaABvAG8AZAAgAHQAbwAgAHIAZQB0AHUAcgBuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAA4ACwAIABkAGkAcgBlAGMAdABsAHkAIABiAGUAbABvAHcAIAB0AGgAZQAgAG0AYQB0AGMAaABlAGQAIABrAGUAcgBuAGUAbAAuAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAFsAcgBlAHQAdQByAG4AXwBoAGUAaQBnAGgAdABdACAAIAAgACAALQAgACAAIABSAG8AdwBzACAAaQBuAGMAbAB1AGQAZQBkACAAaQBuACAAdABoAGUAIAByAGUAdAB1AHIAbgBcAG4AIAAgACAAIABbAHIAZQB0AHUAcgBuAF8AdwBpAGQAdABoAF0AIAAgACAAIAAgAC0AIAAgACAAQwBvAGwAdQBtAG4AcwAgAGkAbgBjAGwAdQBkAGUAZAAgAGkAbgAgAHQAaABlACAAcgBlAHQAdQByAG4AXABuAFwAbgAgACAAIAAgAEkAZgAgAGgAZQBpAGcAaAB0AC8AdwBpAGQAdABoACAAYQByAGUAIABvAG0AaQB0AHQAZQBkACAALQAgAGQAZQBmAGEAdQBsAHQAcwAgAHQAbwAgAGgAZQBpAGcAaAB0AC8AdwBpAGQAdABoACAAbwBmACAAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbABcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAiICAASQBmACAAYQBuACAAbwBwAHQAaQBvAG4AYQBsACAAYQByAGcAdQBtAGUAbgB0ACAAaQBzACAAYQBuACAAYQByAHIAYQB5ACAAbwByACAAcgBhAG4AZwBlACwAIABpAHQAcwAgAHQAbwBwAC0AbABlAGYAdAAgAHYAYQBsAHUAZQAgAGkAcwAgAHUAcwBlAGQALgBcAG4AIiAgAE4AdQBtAGUAcgBpAGMAIABvAHAAdABpAG8AbgBhAGwAIABhAHIAZwB1AG0AZQBuAHQAcwAgAGEAcgBlACAAcgBvAHUAbgBkAGUAZAAgAGQAbwB3AG4AIAB0AG8AIABpAG4AdABlAGcAZQByAHMAIAB3AGkAdABoACAASQBOAFQALgBcAG4AIiAgAEkAZgAgAG0AdQBsAHQAaQBwAGwAZQAgAGsAZQByAG4AZQBsACAAbQBhAHQAYwBoAGUAcwAgAGUAeABpAHMAdAAsACAAdABoAGUAIABmAGkAcgBzAHQAIABtAGEAdABjAGgAIABpAG4AIABHAHIAaQBkAEwAbwBvAGsAdQBwALsDIABzAGMAYQBuACAAbwByAGQAZQByACAAaQBzACAAdQBzAGUAZAAuACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAE4AYQB2AGkAZwBhAHQAZQAyAEQAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwALABcAG4AIAAgACAAIABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQALABcAG4AIAAgACAAIABbAHIAZQB0AHUAcgBuAF8AZABpAHIAZQBjAHQAaQBvAG4AXQAsAFwAbgAgACAAIAAgAFsAcgBlAHQAdQByAG4AXwBoAGUAaQBnAGgAdABdACwAXABuACAAIAAgACAAWwByAGUAdAB1AHIAbgBfAHcAaQBkAHQAaABdACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAE4AbwByAG0AYQBsAGkAegBlACAAaQBuAHAAdQB0AHMAIAAtACAAcwBjAGEAbABhAHIAXABuACAAIAAgACAATgBvAHIAbQBhAGwAaQB6AGUAuwMsACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAaQBuAHAAdQB0ACwASQBOAFQAKABJAE4ARABFAFgAKABpAG4AcAB1AHQALAAxACwAMQApACkAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAE8AcAB0AGkAbwBuAGEAbAAgAC0AIABkAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAA4ACAAKABiAGUAbABvAHcAKQAgAGkAZgAgAG8AbQBpAHQAdABlAGQAXABuACAAIAAgACAAcgBlAHQAdQByAG4AXwBkAGkAcgBlAGMAdABpAG8AbgAsAE4AbwByAG0AYQBsAGkAegBlALsDKABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHIAZQB0AHUAcgBuAF8AZABpAHIAZQBjAHQAaQBvAG4AKQAsADgALAByAGUAdAB1AHIAbgBfAGQAaQByAGUAYwB0AGkAbwBuACkAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAHMAaABhAHAAZQBzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0AIEgLAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAbQBhAHQAYwBoAF8AYQByAHIAYQB5AF8AMgBEACkALAAgACAAIAB3AGkAZAB0AGgAgSAsACAAIABDAE8ATABVAE0ATgBTACgAbQBhAHQAYwBoAF8AYQByAHIAYQB5AF8AMgBEACkALABcAG4AIAAgACAAIABoAGUAaQBnAGgAdACCICwAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAKQAsACAAIAAgACAAdwBpAGQAdABoAIIgLAAgACAAQwBPAEwAVQBNAE4AUwAoAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAHMAaQB6AGUAXABuACAAIAAgACAAcgBlAHQAdQByAG4AXwBoAGUAaQBnAGgAdAAsACAAIAAgAE4AbwByAG0AYQBsAGkAegBlALsDKABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAHIAZQB0AHUAcgBuAF8AaABlAGkAZwBoAHQAKQAsAGgAZQBpAGcAaAB0AIIgLAByAGUAdAB1AHIAbgBfAGgAZQBpAGcAaAB0ACkAKQAsAFwAbgAgACAAIAAgAHIAZQB0AHUAcgBuAF8AdwBpAGQAdABoACwAIAAgACAAIABOAG8AcgBtAGEAbABpAHoAZQC7AygASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKAByAGUAdAB1AHIAbgBfAHcAaQBkAHQAaAApACwAdwBpAGQAdABoAIIgLAByAGUAdAB1AHIAbgBfAHcAaQBkAHQAaAApACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAvAC8AIABFAGEAcgBsAHkAIAB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIABzAGMAZQBuAGEAcgBpAG8AcwBcAG4AIAAgACAAIABCAGEAZABLAGUAcgBuAGUAbAA/ACwAIAAgACAAIAAgACAATwBSACgAaABlAGkAZwBoAHQAgiAgAD4AIABoAGUAaQBnAGgAdACBICwAdwBpAGQAdABoAIIgIAA+ACAAdwBpAGQAdABoAIEgKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAEIAYQBkAEQAaQByAD8ALAAgACAAIAAgACAAIAAgACAAIABPAFIAKAByAGUAdAB1AHIAbgBfAGQAaQByAGUAYwB0AGkAbwBuACAAPAAgADEALAAgAHIAZQB0AHUAcgBuAF8AZABpAHIAZQBjAHQAaQBvAG4AIAA+ACAAOQApACwAXABuACAAIAAgACAAXABuACAAIAAgACAAQgBhAGQAUgBlAHQAdQByAG4APwAsACAAIAAgACAAIAAgAE8AUgAoAHIAZQB0AHUAcgBuAF8AaABlAGkAZwBoAHQAIAA8ACAAMQAsAHIAZQB0AHUAcgBuAF8AdwBpAGQAdABoACAAPAAgADEAKQAsAFwAbgBcAG4AIAAgACAAIABOAG8AdAAyAEQAPwAsACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAaABlAGkAZwBoAHQAgSAgAD0AIAAxACwAIAB3AGkAZAB0AGgAgSAgAD0AIAAxACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAvAC8AIABFAGEAcgBsAHkAIABlAHgAaQB0ACAAaQBmACAAZgBpAHIAcwB0ACAAZQBsAGUAbQBlAG4AdAAgAGkAcwAgAG0AaQBzAHMAaQBuAGcAXABuACAAIAAgACAATgBvAHQAUAByAGUAcwBlAG4AdAA/ACwAIAAgACAAIAAgAE4ATwBUACgASABBAFMAQQBMAEwAKABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQALABsAG8AbwBrAHUAcABfAGsAZQByAG4AZQBsACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABMAG8AZwBpAGMAIABnAGEAdABlAFwAbgAgACAAIAAgAEkARgAoAE4AbwB0ADIARAA/ACwAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEIAYQBkAEsAZQByAG4AZQBsAD8ALAAjAE4ALwBBACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABCAGEAZABEAGkAcgA/ACwAIwBWAEEATABVAEUAIQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABCAGEAZABSAGUAdAB1AHIAbgA/ACwAIwBWAEEATABVAEUAIQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATgBvAHQAUAByAGUAcwBlAG4AdAA/ACwAIwBOAC8AQQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABMAG8AYwBhAHQAaQBvAG4AXABuACAAIAAgACAATQBhAHQAYwBoAEsAZQByAG4AZQBsALsDLABMAEEATQBCAEQAQQAoAHYALABBAE4ARAAoAEYATABBAFQAVABFAE4AKAB2ACkAIAA9ACAAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbAApACkALABcAG4AIAAgACAAIABGAG8AdQBuAGQAPwAsACAAIAAgACAAIAAgAEMAbwBuAHYAbwBsAHYAZQC7AygAbQBhAHQAYwBoAF8AYQByAHIAYQB5AF8AMgBEACwAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbAAsAE0AYQB0AGMAaABLAGUAcgBuAGUAbAC7AykALABcAG4AIAAgACAAIABGAG8AdQBuAGQAMQBEAD8ALAAgACAAIAAgAE8AUgAoAFIATwBXAFMAKABGAG8AdQBuAGQAPwApACAAPQAgADEALABDAE8ATABVAE0ATgBTACgARgBvAHUAbgBkAD8AKQAgAD0AIAAxACkALAAgACAAIAAgAFwAbgAgACAAIAAgAE4AbwB0AEYAbwB1AG4AZAA/ACwAIAAgACAATgBPAFQAKABPAFIAKABGAG8AdQBuAGQAPwApACkALAAgAFwAbgBcAG4AIAAgACAAIAAvAC8AIABJAG4AZABpAGMAZQBzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgARgBvAHUAbgBkADEARAA/ACwAWABNAEEAVABDAEgAKABUAFIAVQBFACwARgBvAHUAbgBkAD8AKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAARwByAGkAZABMAG8AbwBrAHUAcAC7AygAVABSAFUARQAsAEYAbwB1AG4AZAA/ACwATQBHAHIAaQBkALsDKABGAG8AdQBuAGQAPwApACkAKQAsAFwAbgBcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEYAbwB1AG4AZAAxAEQAPwAsADEALABHAHIAaQBkAEwAbwBvAGsAdQBwALsDKABUAFIAVQBFACwARgBvAHUAbgBkAD8ALABNAEcAcgBpAGQAuwMoAEYAbwB1AG4AZAA/ACwAMQApACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAGkAbgB0AGUAcgBzAGUAYwB0AGkAbwBuAFwAbgAgACAAIAAgAHgALAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAKAByAGUAdAB1AHIAbgBfAGQAaQByAGUAYwB0AGkAbwBuACwAIAAgACAAIABpACAALQAgAGgAZQBpAGcAaAB0AIIgLABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQAgAC0AIABoAGUAaQBnAGgAdACCICwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAIAAtACAAaABlAGkAZwBoAHQAgiAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpACAAKwAgAGgAZQBpAGcAaAB0AIIgLABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQAgACsAIABoAGUAaQBnAGgAdACCICwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGkAIAArACAAaABlAGkAZwBoAHQAgiApACwAXABuAFwAbgAgACAAIAAgAHkALAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBIAE8ATwBTAEUAKAByAGUAdAB1AHIAbgBfAGQAaQByAGUAYwB0AGkAbwBuACwAIAAgACAAIABqACAALQAgAHcAaQBkAHQAaACCICwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAagAgACsAIAB3AGkAZAB0AGgAgiAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABqACAALQAgAHcAaQBkAHQAaACCICwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAagAgACsAIAB3AGkAZAB0AGgAgiAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABqACAALQAgAHcAaQBkAHQAaACCICwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAGoALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAagAgACsAIAB3AGkAZAB0AGgAgiApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeABwAGEAbgBzAGkAbwBuACAAawBlAHIAbgBlAGwAcwBcAG4AIAAgACAAIAByAF8AawBlAHIAbgBlAGwALAAgACAAIABSAGUAcwBpAHoAZQC7AygASQBGACgAcgBlAHQAdQByAG4AXwBoAGUAaQBnAGgAdAAgAD0AIAAxACwAMAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAByAGUAdAB1AHIAbgBfAGgAZQBpAGcAaAB0ACwALAAwACwAMQApACkALAAsAHIAZQB0AHUAcgBuAF8AdwBpAGQAdABoACkALABcAG4AXABuACAAIAAgACAAYwBfAGsAZQByAG4AZQBsACwAIAAgACAAUgBlAHMAaQB6AGUAuwMoAEkARgAoAHIAZQB0AHUAcgBuAF8AdwBpAGQAdABoACAAPQAgADEALAAwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoACwAcgBlAHQAdQByAG4AXwB3AGkAZAB0AGgALAAwACwAMQApACkALAByAGUAdAB1AHIAbgBfAGgAZQBpAGcAaAB0ACkALABcAG4AIAAgACAAIABcAG4AIAAgACAAIAAvAC8AIABDAG8AbwByAGQAaQBuAGEAdABlAHMAXABuACAAIAAgACAAcgAsACAAIAAgACAAIAAgACAAIAAgACAAeAAgACsAIAByAF8AawBlAHIAbgBlAGwALABcAG4AIAAgACAAIABjACwAIAAgACAAIAAgACAAIAAgACAAIAB5ACAAKwAgAGMAXwBrAGUAcgBuAGUAbAAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABSAGUAdAB1AHIAbgAgAGEAcgByAGEAeQAgAGkAcwAgAG8AZgBmACAAZwByAGkAZABcAG4AIAAgACAAIABPAGYAZgBHAHIAaQBkAD8ALAAgACAAIABPAFIAKABNAEkATgAoAHIAKQAgADwAIAAxACwATQBJAE4AKABjACkAIAA8ACAAMQAsAE0AQQBYACgAcgApACAAPgAgAGgAZQBpAGcAaAB0AIEgLABNAEEAWAAoAGMAKQAgAD4AIAB3AGkAZAB0AGgAgSApACwAXABuACAAIAAgACAAXABuACAAIAAgACAAbQBzAGcALAAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG4AZQBsADoAIABSAFwAIgAmAGkAJgBcACIAQwBcACIAJgBqACwAXABuAFwAbgAgACAAIAAgAGYAaQBuAGEAbAAsACAAIAAgACAAIAAgAEkARgAoAE4AbwB0AEYAbwB1AG4AZAA/ACwAIwBOAC8AQQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgATwBmAGYARwByAGkAZAA/ACwAbQBzAGcALABJAE4ARABFAFgAKABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQALAByACwAYwApACkAKQAsAFwAbgAgACAAIAAgAGYAaQBuAGEAbABcAG4AXABuACkAKQApACkAKQApACkAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4ALwAqACAAWwA/AD8APwBdACAALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgACAAIABNAGEAdABjAGgAMgBEALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgACAAIAAxAC4AMQBcAG4ARABlAHAAZQBuAGQAZQBuAGMAaQBlAHMAOgAgACAAIABDAG8AbgB2AG8AbAB2AGUAuwMsACAARwByAGkAZABMAG8AbwBrAHUAcAC7AywAIABNAEcAcgBpAGQAuwMsACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEwAbwBjAGEAdABlAHMAIABhACAAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbAAgACgAMgBEACAAYQByAHIAYQB5ACkAIABpAG4AIABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQAIABhAG4AZAAgAHIAZQB0AHUAcgBuAHMAIABhACAAcwBoAGEAcABlACAAZgByAG8AbQAgAHQAaABlAFwAbgAgACAAIAAgAE0AbwBvAHIAZQAgAG4AZQBpAGcAaABiAG8AcgBoAG8AbwBkACAAcgBlAGwAYQB0AGkAdgBlACAAdABvACAAdABoAGUAIABtAGEAdABjAGgAIABsAG8AYwBhAHQAaQBvAG4ALgBcAG4AXABuACAAIAAgACAATQBvAG8AcgBlACAATgBlAGkAZwBoAGIAbwByAGgAbwBvAGQAOgBcAG4AIAAgACAAIAAgACAAIAAgADEAIAAgACAAMgAgACAAIAAzAFwAbgAgACAAIAAgACAAIAAgACAANAAgACAAIAA1ACAAIAAgADYAXABuACAAIAAgACAAIAAgACAAIAA3ACAAIAAgADgAIAAgACAAOQBcAG4AIAAgACAAIABcAG4AIAAgACAAIAA1ACAAPQAgAHAAbwBzAGkAdABpAG8AbgAgAG8AZgAgAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAIABpAG4AIABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQAXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAbABvAG8AawB1AHAAXwBrAGUAcgBuAGUAbAAgACAAIAAgACAAIAAtACAAIAAgADIARAAgAHMAaABhAHAAZQAgAG8AcgAgAGEAcgByAGEAeQAgAHQAbwAgAGwAbwBjAGEAdABlAFwAbgAgACAAIAAgAG0AYQB0AGMAaABfAGEAcgByAGEAeQBfADIARAAgACAAIAAgACAALQAgACAAIAAyAEQAIABzAG8AdQByAGMAZQAgAGEAcgByAGEAeQAgAGkAbgAgAHcAaABpAGMAaAAgAHQAbwAgAGwAbwBjAGEAdABlACAAdABoAGUAIABrAGUAcgBuAGUAbABcAG4AXABuAE4AbwB0AGUAcwA6AFwAbgAiICAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAE0AYQB0AGMAaAAyAEQAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwALABcAG4AIAAgACAAIABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQALABcAG4AXABuAEwARQBUACgAXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABpAG4AcAB1AHQAcwAgAC0AIABzAGMAYQBsAGEAcgBcAG4AIAAgACAAIABOAG8AcgBtAGEAbABpAHoAZQC7AywAIAAgACAAIAAgACAATABBAE0AQgBEAEEAKABpAG4AcAB1AHQALABJAE4AVAAoAEkATgBEAEUAWAAoAGkAbgBwAHUAdAAsADEALAAxACkAKQApACwAXABuAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAHMAaABhAHAAZQBzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0AIEgLAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAbQBhAHQAYwBoAF8AYQByAHIAYQB5AF8AMgBEACkALAAgACAAIAB3AGkAZAB0AGgAgSAsACAAIABDAE8ATABVAE0ATgBTACgAbQBhAHQAYwBoAF8AYQByAHIAYQB5AF8AMgBEACkALABcAG4AIAAgACAAIABoAGUAaQBnAGgAdACCICwAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAKQAsACAAIAAgACAAdwBpAGQAdABoAIIgLAAgACAAQwBPAEwAVQBNAE4AUwAoAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAEUAYQByAGwAeQAgAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgAHMAYwBlAG4AYQByAGkAbwBcAG4AIAAgACAAIABCAGEAZABLAGUAcgBuAGUAbAA/ACwAIAAgACAAIAAgACAATwBSACgAaABlAGkAZwBoAHQAgiAgAD4AIABoAGUAaQBnAGgAdACBICwAdwBpAGQAdABoAIIgIAA+ACAAdwBpAGQAdABoAIEgKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAC8ALwAgAEUAYQByAGwAeQAgAGUAeABpAHQAIABpAGYAIABtAGUAbQBiAGUAcgBzAGgAaQBwACAAPQAgAEYAQQBMAFMARQBcAG4AIAAgACAAIABOAG8AdABQAHIAZQBzAGUAbgB0AD8ALAAgACAAIAAgACAATgBPAFQAKABIAEEAUwBBAEwATAAoAG0AYQB0AGMAaABfAGEAcgByAGEAeQBfADIARAAsAGwAbwBvAGsAdQBwAF8AawBlAHIAbgBlAGwAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBnAGkAYwAgAGcAYQB0AGUAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABCAGEAZABLAGUAcgBuAGUAbAA/ACwAIwBOAC8AQQAsAFwAbgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABOAG8AdABQAHIAZQBzAGUAbgB0AD8ALAAjAE4ALwBBACwAXABuAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAEwAbwBjAGEAdABpAG8AbgBcAG4AIAAgACAAIABNAGEAdABjAGgASwBlAHIAbgBlAGwAuwMsAEwAQQBNAEIARABBACgAdgAsAEEATgBEACgARgBMAEEAVABUAEUATgAoAHYAKQAgAD0AIABsAG8AbwBrAHUAcABfAGsAZQByAG4AZQBsACkAKQAsAFwAbgAgACAAIAAgAEYAbwB1AG4AZAA/ACwAIAAgACAAIAAgACAAQwBvAG4AdgBvAGwAdgBlALsDKABtAGEAdABjAGgAXwBhAHIAcgBhAHkAXwAyAEQALABsAG8AbwBrAHUAcABfAGsAZQByAG4AZQBsACwATQBhAHQAYwBoAEsAZQByAG4AZQBsALsDKQAsACAAIABcAG4AIAAgACAAIABGAG8AdQBuAGQAMQBEAD8ALAAgACAAIAAgAE8AUgAoAFIATwBXAFMAKABGAG8AdQBuAGQAPwApACAAPQAgADEALABDAE8ATABVAE0ATgBTACgARgBvAHUAbgBkAD8AKQAgAD0AIAAxACkALAAgACAAXABuACAAIAAgACAATgBvAHQARgBvAHUAbgBkAD8ALAAgACAAIABOAE8AVAAoAE8AUgAoAEYAbwB1AG4AZAA/ACkAKQAsACAAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBkAGkAYwBlAHMAXABuACAAIAAgACAAaQAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABGAG8AdQBuAGQAMQBEAD8ALABYAE0AQQBUAEMASAAoAFQAUgBVAEUALABGAG8AdQBuAGQAPwApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABHAHIAaQBkAEwAbwBvAGsAdQBwALsDKABUAFIAVQBFACwARgBvAHUAbgBkAD8ALABNAEcAcgBpAGQAuwMoAEYAbwB1AG4AZAA/ACkAKQApACwAXABuAFwAbgAgACAAIAAgAGoALAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgARgBvAHUAbgBkADEARAA/ACwAMQAsAEcAcgBpAGQATABvAG8AawB1AHAAuwMoAFQAUgBVAEUALABGAG8AdQBuAGQAPwAsAE0ARwByAGkAZAC7AygARgBvAHUAbgBkAD8ALAAxACkAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEMAbwBvAHIAZABpAG4AYQB0AGUAcwAgAGYAcgBvAG0AIABpAC8AagAgAG0AYQB0AGMAaAAgAHAAbwBpAG4AdABcAG4AIAAgACAAIABxACwAIAAgACAAIAAgACAAIAAgACAAIAAgAFEAdQBhAGQAdwBpAHMAZQC7AygAaQAsAGoALABTAEUAUQBVAEUATgBDAEUAKABoAGUAaQBnAGgAdACCICwALAAwACwAMQApACwAUwBFAFEAVQBFAE4AQwBFACgAdwBpAGQAdABoAIIgLAAsADAALAAxACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABGAHUAbABsACAAYwBvAG8AcgBkAGkAbgBhAHQAZQBzACAAZgBvAHIAIAAyAEQAIABrAGUAcgBuAGUAbAAgAG0AYQB0AGMAaABcAG4AIAAgACAAIABmAGkAbgBhAGwALAAgACAAIAAgACAAIAAgAEgAUwBUAEEAQwBLACgAVABBAEsARQAoAHEALAAsADEAKQAgACsAIABDAEgATwBPAFMARQBDAE8ATABTACgAcQAsADMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAcQAsADIAKQAgACsAIABUAEEASwBFACgAcQAsACwALQAxACkAKQAsAFwAbgBcAG4AIAAgACAAIABmAGkAbgBhAGwAXABuAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqAFsAVABCAEQAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAFYAUwBwAGwAaQB0ALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABUAEIARABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABTAHAAbABpAHQAcwAgAGEAIAAyAEQAIABhAHIAcgBhAHkAIABpAG4AdABvACAAaABvAHIAaQB6AG8AbgB0AGEAbAAgAHIAbwB3ABEgcwBlAGcAbQBlAG4AdABzACAAbwBmACAAcwBpAHoAZQAgAHMAcABsAGkAdABfAGkAbgB0AGUAcgB2AGEAbAAuAFwAbgAgACAAIAAgAFQAaABlACAAcgBlAHMAdQBsAHQAIABpAHMAIABhAG4AIABhAHIAcgBhAHkAIABvAGYAIABsAGkAcwB0AHMALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAgACAAIAAgACAALQAgAEEAIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIAB3AGgAbwBzAGUAIABkAGkAbQBlAG4AcwBpAG8AbgBzACAAZABlAHQAZQByAG0AaQBuAGUAIAB0AGgAZQAgAG8AdQB0AHAAdQB0ACAAcwBpAHoAZQAuAFwAbgAgACAAIAAgAHMAcABsAGkAdABfAGkAbgB0AGUAcgB2AGEAbAAgAC0AIABBAG4AIABpAG4AdABlAGcAZQByACAAZABlAHMAaQBnAG4AYQB0AGkAbgBnACAAdABvAHQAYQBsACAAcgBvAHcAIABpAG4AIABlAGEAYwBoACAAcwBlAGcAbQBlAG4AdABcAG4AXABuAE8AcAB0AGkAbwBuAGEAbABcAG4AIAAgACAAIABbAHAAYQBkAF8AdwBpAHQAaABdACAAIAAgACAALQAgAEYAaQBsAGwAIAB2AGEAbAB1AGUAIAB1AHMAZQBkACAAdABvACAAcABhAGQAIABlAHgAcABhAG4AZABlAGQAIABhAHIAcgBhAHkAcwAgAGkAbgB0AG8AIABlAHEAdQBhAGwAIABzAGUAZwBtAGUAbgB0AHMALgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAZgAgAG8AbQBpAHQAdABlAGQALAAgAGQAZQBmAGEAdQBsAHQAIAA9ACAAIwBOAC8AQQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AVgBTAHAAbABpAHQAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAHMAcABsAGkAdABfAGkAbgB0AGUAcgB2AGEAbAAsAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwAXABuACAAIAAgACAAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACwAIABJAE4ARABFAFgAKABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwALAAxACwAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoAGUAaQBnAGgAdAAgAD0AIAAxACwAdwBpAGQAdABoACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwAxAHgATgA/ACwAIAAgACAAIAAgACAAIAAgACAAaABlAGkAZwBoAHQAIAA9ACAAMQAsAFwAbgAgACAAIAAgAEkAbgB2AGEAbABpAGQAUwBwAGwAaQB0AD8ALAAgACAATwBSACgASQBTAFQARQBYAFQAKABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwAKQAsAHMAcABsAGkAdABfAGkAbgB0AGUAcgB2AGEAbAAgADwAPQAgADAAKQAsAFwAbgBcAG4AIAAgACAAIABJAEYAKABPAFIAKABJAHMAUwBjAGEAbABhAHIAPwAsAEkAcwAxAHgATgA/ACkALAB7AGEAcgByAGEAeQB9ACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAFMAcABsAGkAdAA/ACwAIwBWAEEATABVAEUAIQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFAAYQBkACAAYQByAHIAYQB5ACAAdABvACAAcAByAGUAdgBlAG4AdAAgAHUAbgBlAHYAZQBuACAAcABhAHIAdABpAHQAaQBvAG4AcwBcAG4AIAAgACAAIABwAGEAZABfAHcAaQB0AGgALAAgACAAIAAgACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABwAGEAZABfAHcAaQB0AGgAKQAsAE4AQQAoACkALABJAE4ARABFAFgAKABwAGEAZABfAHcAaQB0AGgALAAxACwAMQApACkALABcAG4AIAAgACAAIABQAGEAZABSAG8AdwBzACwAIAAgACAAIAAgACAATQBPAEQAKAAtAGgAZQBpAGcAaAB0ACwAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACkALABcAG4AIAAgACAAIABuAGUAdwBfAGEAcgByAGEAeQAsACAAIAAgACAARQBYAFAAQQBOAEQAKABhAHIAcgBhAHkALABoAGUAaQBnAGgAdAAgACsAIABQAGEAZABSAG8AdwBzACwALABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAG4AYwBoAG8AcgBzACAAKwAgAHIAbwB3ACAAYQBkAGoAdQBzAHQAbQBlAG4AdABzAFwAbgAgACAAIAAgAGEAbgBjAGgAbwByAHMALAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAoAFAAYQBkAFIAbwB3AHMAIAArACAAaABlAGkAZwBoAHQAKQAgAC8AIABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwALAAsADEALABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwAKQAsAFwAbgAgACAAIAAgAHMAdABlAHAALAAgACAAIAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwALAAsADAAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABTAHAAbABpAHQAIABtAGEAdAByAGkAeAAgAGkAbgB0AG8AIABwAGEAcgB0AHMAXABuACAAIAAgACAAUABhAHIAdAC7AywAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABpAGQAeAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcgAsACAAIAAgACAAIABpAGQAeAAgACsAIABzAHQAZQBwACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABwAGEAcgB0ACwAIAAgAEMASABPAE8AUwBFAFIATwBXAFMAKABuAGUAdwBfAGEAcgByAGEAeQAsAHIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABhAHIAdAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAUgBlAHQAdQByAG4AIABhAHMAIABsAGkAcwB0AHMAXABuACAAIAAgACAAbABpAHMAdABzACwAIAAgACAAIAAgACAAIAAgAE0AQQBQACgAYQBuAGMAaABvAHIAcwAsAFAAYQByAHQAuwMpACwAXABuACAAIAAgACAAbABpAHMAdABzAFwAbgApACkAKQApACkAOwBcAG4AXABuAFwAbgAvACoAWwBUAEIARABdAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAASABTAHAAbABpAHQAuwNcAG4AQwBhAHQAZQBnAG8AcgB5ADoAIAAgACAAIAAgAFQAQgBEAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFMAcABsAGkAdABzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAGkAbgB0AG8AIABoAG8AcgBpAHoAbwBuAHQAYQBsACAAYwBvAGwAdQBtAG4AESBzAGUAZwBtAGUAbgB0AHMAIABvAGYAIABzAGkAegBlACAAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsAC4AXABuACAAIAAgACAAVABoAGUAIAByAGUAcwB1AGwAdAAgAGkAcwAgAGEAbgAgAGEAcgByAGEAeQAgAG8AZgAgAGwAaQBzAHQAcwAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAAIAAtACAAQQAgADEARAAgAG8AcgAgADIARAAgAGEAcgByAGEAeQAgAHcAaABvAHMAZQAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAIABkAGUAdABlAHIAbQBpAG4AZQAgAHQAaABlACAAbwB1AHQAcAB1AHQAIABzAGkAegBlAC4AXABuACAAIAAgACAAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACAALQAgAEEAbgAgAGkAbgB0AGUAZwBlAHIAIABkAGUAcwBpAGcAbgBhAHQAaQBuAGcAIAB0AG8AdABhAGwAIABjAG8AbAB1AG0AbgBzACAAaQBuACAAZQBhAGMAaAAgAHMAZQBnAG0AZQBuAHQAXABuAFwAbgBPAHAAdABpAG8AbgBhAGwAXABuACAAIAAgACAAWwBwAGEAZABfAHcAaQB0AGgAXQAgACAAIAAgAC0AIABGAGkAbABsACAAdgBhAGwAdQBlACAAdQBzAGUAZAAgAHQAbwAgAHAAYQBkACAAZQB4AHAAYQBuAGQAZQBkACAAYQByAHIAYQB5AHMAIABpAG4AdABvACAAZQBxAHUAYQBsACAAcwBlAGcAbQBlAG4AdABzAC4AXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAGYAIABvAG0AaQB0AHQAZQBkACwAIABkAGUAZgBhAHUAbAB0ACAAPQAgACMATgAvAEEAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4ASABTAHAAbABpAHQAuwM9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAHMAcABsAGkAdABfAGkAbgB0AGUAcgB2AGEAbAAsAFwAbgAgACAAIAAgAFsAcABhAGQAXwB3AGkAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGEAcgByAGEAeQApACwAXABuACAAIAAgACAAdwBpAGQAdABoACwAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AXABuACAAIAAgACAALwAvACAATgBvAHIAbQBhAGwAaQB6AGUAIABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwAXABuACAAIAAgACAAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACwAIABJAE4ARABFAFgAKABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwALAAxACwAMQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAEkAcwBTAGMAYQBsAGEAcgA/ACwAIAAgACAAIAAgACAAQQBOAEQAKABoAGUAaQBnAGgAdAAgAD0AIAAxACwAdwBpAGQAdABoACAAPQAgADEAKQAsAFwAbgAgACAAIAAgAEkAcwBOAHgAMQA/ACwAIAAgACAAIAAgACAAIAAgACAAdwBpAGQAdABoACAAPQAgADEALABcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAFMAcABsAGkAdAA/ACwAIAAgAE8AUgAoAEkAUwBUAEUAWABUACgAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACkALABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwAIAA8AD0AIAAwACkALABcAG4AXABuACAAIAAgACAASQBGACgATwBSACgASQBzAFMAYwBhAGwAYQByAD8ALABJAHMATgB4ADEAPwApACwAewBhAHIAcgBhAHkAfQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgASQBuAHYAYQBsAGkAZABTAHAAbABpAHQAPwAsACMAVgBBAEwAVQBFACEALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABQAGEAZAAgAGEAcgByAGEAeQAgAHQAbwAgAHAAcgBlAHYAZQBuAHQAIAB1AG4AZQB2AGUAbgAgAHAAYQByAHQAaQB0AGkAbwBuAHMAXABuACAAIAAgACAAcABhAGQAXwB3AGkAdABoACwAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAcABhAGQAXwB3AGkAdABoACkALABOAEEAKAApACwASQBOAEQARQBYACgAcABhAGQAXwB3AGkAdABoACwAMQAsADEAKQApACwAXABuACAAIAAgACAAUABhAGQAQwBvAGwAcwAsACAAIAAgACAAIAAgAE0ATwBEACgALQB3AGkAZAB0AGgALABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwAKQAsAFwAbgAgACAAIAAgAG4AZQB3AF8AYQByAHIAYQB5ACwAIAAgACAAIABFAFgAUABBAE4ARAAoAGEAcgByAGEAeQAsACwAdwBpAGQAdABoACAAKwAgAFAAYQBkAEMAbwBsAHMALABwAGEAZABfAHcAaQB0AGgAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABBAG4AYwBoAG8AcgBzACAAKwAgAHIAbwB3ACAAYQBkAGoAdQBzAHQAbQBlAG4AdABzAFwAbgAgACAAIAAgAGEAbgBjAGgAbwByAHMALAAgACAAIAAgACAAIABTAEUAUQBVAEUATgBDAEUAKAAsACgAUABhAGQAQwBvAGwAcwAgACsAIAB3AGkAZAB0AGgAKQAgAC8AIABzAHAAbABpAHQAXwBpAG4AdABlAHIAdgBhAGwALAAxACwAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACkALABcAG4AIAAgACAAIABzAHQAZQBwACwAIAAgACAAIAAgACAAIAAgACAAUwBFAFEAVQBFAE4AQwBFACgAcwBwAGwAaQB0AF8AaQBuAHQAZQByAHYAYQBsACwALAAwACkALABcAG4AXABuACAAIAAgACAALwAvACAAUwBwAGwAaQB0ACAAbQBhAHQAcgBpAHgAIABpAG4AdABvACAAcABhAHIAdABzAFwAbgAgACAAIAAgAFAAYQByAHQAuwMsACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAaQBkAHgALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIALAAgACAAIAAgACAAaQBkAHgAIAArACAAcwB0AGUAcAAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAcABhAHIAdAAsACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAbgBlAHcAXwBhAHIAcgBhAHkALAByACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHAAYQByAHQAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAYQBzACAAbABpAHMAdABzAFwAbgAgACAAIAAgAGwAaQBzAHQAcwAsACAAIAAgACAAIAAgACAAIABNAEEAUAAoAGEAbgBjAGgAbwByAHMALABQAGEAcgB0ALsDKQAsAFwAbgAgACAAIAAgAGwAaQBzAHQAcwBcAG4AKQApACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8ALwAgAFUAbgBjAGgAYQBuAGcAZQBkACAAZgB1AG4AYwB0AGkAbwBuAHMAIABjAGEAbABsAGUAZAAgAGIAeQAgAHQAaABlACAAZgB1AG4AYwB0AGkAbwBuAHMAIABhAGIAbwB2AGUALgBcAG4AXABuAC8AKgBbAEcAVwAwADMAXQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ARgB1AG4AYwB0AGkAbwBuADoAIAAgACAAIAAgAE0ARwByAGkAZAC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAARwByAGkAZAB3AG8AcgBrAFwAbgBBAHUAdABoAG8AcgA6ACAAIAAgACAAIAAgACAAUABhAHQAcgBpAGMAawAgAEgALgBcAG4AVgBlAHIAcwBpAG8AbgA6ACAAIAAgACAAIAAgADEALgAxAFwAbgBEAGUAcABlAG4AZABlAG4AYwBpAGUAcwA6ACAAUgBlAHMAaQB6AGUAuwNcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAEcAZQBuAGUAcgBhAHQAZQBzACAAcgBvAHcAESBpAG4AZABlAHgAIABvAHIAIABjAG8AbAB1AG0AbgARIGkAbgBkAGUAeAAgAGcAcgBpAGQAcwAgAG0AYQB0AGMAaABpAG4AZwAgAHQAaABlACAAcwBoAGEAcABlACAAbwBmACAAYQAgAHMAdQBwAHAAbABpAGUAZABcAG4AIAAgACAAIABhAHIAcgBhAHkALgAgAFQAaABpAHMAIABpAHMAIAB0AGgAZQAgAEUAeABjAGUAbAAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABvAGYAIABNAEEAVABMAEEAQgAZIHMAIABtAGUAcwBoAGcAcgBpAGQAIABvAHIAIABOAHUAbQBQAHkAGSBzACAAaQBuAGQAaQBjAGUAcwAuAFwAbgBcAG4AIAAgACAAIABCAHkAIABkAGUAZgBhAHUAbAB0ACwAIABNAEcAcgBpAGQAuwMgAHIAZQB0AHUAcgBuAHMAIAByAG8AdwAgAGkAbgBkAGkAYwBlAHMALgAgAFcAaABlAG4AIAB0AGgAZQAgAG8AcAB0AGkAbwBuAGEAbAAgAHAAYQByAGEAbQBlAHQAZQByACAAaQBzACAAVABSAFUARQAsAFwAbgAgACAAIAAgAGkAdAAgAHIAZQB0AHUAcgBuAHMAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGkAYwBlAHMAIABpAG4AcwB0AGUAYQBkAC4AXABuAFwAbgAgACAAIAAgAFcAbwByAGsAcwAgAGYAbwByACAAYgBvAHQAaAAgADEARAAgAGEAbgBkACAAMgBEACAAYQByAHIAYQB5AHMALgAgAE8AdQB0AHAAdQB0ACAAYQBsAHcAYQB5AHMAIABtAGEAdABjAGgAZQBzACAAdABoAGUAIABnAGUAbwBtAGUAdAByAHkAIABvAGYAIAB0AGgAZQBcAG4AIAAgACAAIABpAG4AcAB1AHQAIABnAHIAaQBkAC4AXABuAFwAbgBQAGEAcgBhAG0AZQB0AGUAcgBzADoAXABuACAAIAAgACAAZwByAGkAZAAgACAAIAAgACAAIAAgACAALQAgAEEAIAAxAEQAIABvAHIAIAAyAEQAIABhAHIAcgBhAHkAIAB3AGgAbwBzAGUAIABkAGkAbQBlAG4AcwBpAG8AbgBzACAAZABlAHQAZQByAG0AaQBuAGUAIAB0AGgAZQAgAG8AdQB0AHAAdQB0ACAAcwBpAHoAZQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAqAC8AXABuAFwAbgBNAEcAcgBpAGQAuwMgAD0AXABuAEwAQQBNAEIARABBACgAXABuACAAIAAgACAAZwByAGkAZAAsAFwAbgAgACAAIAAgAFsAYwBvAGwAXwBpAG4AZABlAHgAXQAsAFwAbgBMAEUAVAAoAFwAbgAgACAAIAAgAC8ALwAgAFIAZQB0AHUAcgBuACAAbQBvAGQAZQBcAG4AIAAgACAAIABSAG8AdwBJAGQAeAA/ACwAIABJAFMATwBNAEkAVABUAEUARAAoAGMAbwBsAF8AaQBuAGQAZQB4ACkALABcAG4AXABuACAAIAAgACAALwAvACAARwByAGkAZAAgAGQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAaAAsACAAIAAgACAAIAAgACAAUgBPAFcAUwAoAGcAcgBpAGQAKQAsAFwAbgAgACAAIAAgAHcALAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOAFMAKABnAHIAaQBkACkALABcAG4AXABuACAAIAAgACAALwAvACAARABlAGYAZQByAHIAZQBkACAAaQBuAGQAZQB4ACAAZwByAGkAZABzAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAUgBlAHMAaQB6AGUAuwMoAFMARQBRAFUARQBOAEMARQAoAGgAKQAsACwAdwApACkALABcAG4AIAAgACAAIABqACwAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAFIAZQBzAGkAegBlALsDKABTAEUAUQBVAEUATgBDAEUAKAAsAHcAKQAsAGgAKQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAZQBsAGUAYwB0ACAAcgBvAHcAIABvAHIAIABjAG8AbAB1AG0AbgAgAGkAbgBkAGUAeAAgAGcAcgBpAGQAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAASQBGACgAUgBvAHcASQBkAHgAPwAsACAAaQAoACkALAAgAGoAKAApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABbAFQAQgBEAF0AIAAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBGAHUAbgBjAHQAaQBvAG4AOgAgACAAIAAgACAAUgBlAHAAZQBhAHQAUgBvAHcAcwC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAcABlAGEAdABzACAAZQBhAGMAaAAgAHIAbwB3ACAAbwBmACAAYQAgAHMAdQBwAHAAbABpAGUAZAAgAGEAcgByAGEAeQAgAGEAYwBjAG8AcgBkAGkAbgBnACAAdABvACAAYQAgAHYAZQBjAHQAbwByACAAbwBmACAAcgBlAHAAZQBhAHQAXABuACAAIAAgACAAYwBvAHUAbgB0AHMALgAgAFMAYwBhAGwAYQByAHMAIABhAG4AZAAgAGEAcgByAGEAeQBzACAAYQByAGUAIABzAHUAcABwAG8AcgB0AGUAZAAuACAAUgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgAG0AdQBzAHQAIABiAGUAIABuAHUAbQBlAHIAaQBjAFwAbgAgACAAIAAgAGEAbgBkACAAZSIgADEALgBcAG4AXABuAFAAYQByAGEAbQBlAHQAZQByAHMAOgBcAG4AIAAgACAAIABhAHIAcgBhAHkAIAAgACAAIAAtACAAMgBEACAAYQByAHIAYQB5ACAAdwBoAG8AcwBlACAAcgBvAHcAcwAgAHcAaQBsAGwAIABiAGUAIAByAGUAcABlAGEAdABlAGQALgBcAG4AIAAgACAAIAByAGUAcABlAGEAdAAgACAAIAAtACAAMQBEACAAYQByAHIAYQB5ACAAbwBmACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAcwAgACgAbgB1AG0AZQByAGkAYwAsACAAZSIgADEAKQAuAFwAbgBcAG4ATgBvAHQAZQBzADoAXABuACAAIAAgACAAIiAgAEkAZgAgAHIAZQBwAGUAYQB0ACAAaABhAHMAIABmAGUAdwBlAHIAIABlAG4AdAByAGkAZQBzACAAdABoAGEAbgAgAHQAaABlACAAbgB1AG0AYgBlAHIAIABvAGYAIAByAG8AdwBzACwAIAB0AGgAZQAgAGwAYQBzAHQAIAByAGUAcABlAGEAdABcAG4AIAAgACAAIAAgACAAdgBhAGwAdQBlACAAaQBzACAAZQB4AHQAZQBuAGQAZQBkACAAdABvACAAbQBhAHQAYwBoACAAdABoAGUAIABhAHIAcgBhAHkAIABoAGUAaQBnAGgAdAAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAHAAcgBlAHMAZQByAHYAZQBzACAAdABoAGUAIABjAG8AbAB1AG0AbgAgAHMAdAByAHUAYwB0AHUAcgBlACAAbwBmACAAdABoAGUAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUgBlAHAAZQBhAHQAUgBvAHcAcwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIAByAGUAcABlAGEAdAAsAFwAbgBcAG4ASQBGACgATwBSACgASQBTAFQARQBYAFQAKAByAGUAcABlAGEAdAApACwAIAByAGUAcABlAGEAdAAgADwAPQAgADAAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAHIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAXABuACAAIAAgACAAcgBlAHAAZQBhAHQALAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAQQBoACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABSAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AGUAbgBkACAAcgBlAHAAZQBhAHQAIAB2AGUAYwB0AG8AcgAgAGkAZgAgAG4AZQBlAGQAZQBkAFwAbgAgACAAIAAgAHIALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQBoACAAPAA+ACAAUgBoACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAcgBlAHAAZQBhAHQALAAgAEEAaAAsACAALAAgAEAAVABBAEsARQAoAHIAZQBwAGUAYQB0ACwAIAAtADEAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBwAGUAYQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBhAHMAZQAgAHIAbwB3ACAAaQBuAGQAaQBjAGUAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAFIATwBXAFMAKAByACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGEAeABpAG0AdQBtACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAXABuACAAIAAgACAAbQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAHIAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAHUAaQBsAGQAIABpAG4AZABlAHgAIAB2AGUAYwB0AG8AcgBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAVABPAEMATwBMACgASQBGACgAUwBJAEcATgAoAHIAIAAtACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAG0ALAAgADAAKQApACAAPQAgADEALABpACwATgBBACgAKQApACwAMgApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQBSAE8AVwBTACgAYQByAHIAYQB5ACwAIABpAGQAeAAoACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABSAGUAcABlAGEAdABDAG8AbABzALsDXABuAEMAYQB0AGUAZwBvAHIAeQA6ACAAIAAgACAAIABUAEIARABcAG4AQQB1AHQAaABvAHIAOgAgACAAIAAgACAAIAAgAFAAYQB0AHIAaQBjAGsAIABIAC4AXABuAFYAZQByAHMAaQBvAG4AOgAgACAAIAAgACAAIAAxAC4AMQBcAG4AXABuAEQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAbgAgACAAIAAgAFIAZQBwAGUAYQB0AHMAIABlAGEAYwBoACAAYwBvAGwAdQBtAG4AIABvAGYAIABhACAAcwB1AHAAcABsAGkAZQBkACAAYQByAHIAYQB5ACAAYQBjAGMAbwByAGQAaQBuAGcAIAB0AG8AIABhACAAdgBlAGMAdABvAHIAIABvAGYAIAByAGUAcABlAGEAdABcAG4AIAAgACAAIABjAG8AdQBuAHQAcwAuACAAUwBjAGEAbABhAHIAcwAgAGEAbgBkACAAYQByAHIAYQB5AHMAIABhAHIAZQAgAHMAdQBwAHAAbwByAHQAZQBkAC4AIABSAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAbQB1AHMAdAAgAGIAZQAgAG4AdQBtAGUAcgBpAGMAXABuACAAIAAgACAAYQBuAGQAIABlIiAAMQAuAFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgAC0AIAAyAEQAIABhAHIAcgBhAHkAIAB3AGgAbwBzAGUAIABjAG8AbAB1AG0AbgBzACAAdwBpAGwAbAAgAGIAZQAgAHIAZQBwAGUAYQB0AGUAZAAuAFwAbgAgACAAIAAgAHIAZQBwAGUAYQB0ACAAIAAgAC0AIAAxAEQAIABhAHIAcgBhAHkAIABvAGYAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzACAAKABuAHUAbQBlAHIAaQBjACwAIABlIiAAMQApAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAASQBmACAAcgBlAHAAZQBhAHQAIABoAGEAcwAgAGYAZQB3AGUAcgAgAGUAbgB0AHIAaQBlAHMAIAB0AGgAYQBuACAAdABoAGUAIABuAHUAbQBiAGUAcgAgAG8AZgAgAGMAbwBsAHUAbQBuAHMALAAgAHQAaABlACAAbABhAHMAdAAgAHIAZQBwAGUAYQB0AFwAbgAgACAAIAAgACAAIAB2AGEAbAB1AGUAIABpAHMAIABlAHgAdABlAG4AZABlAGQAIAB0AG8AIABtAGEAdABjAGgAIAB0AGgAZQAgAGEAcgByAGEAeQAgAHcAaQBkAHQAaAAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAHAAcgBlAHMAZQByAHYAZQBzACAAdABoAGUAIAByAG8AdwAgAHMAdAByAHUAYwB0AHUAcgBlACAAbwBmACAAdABoAGUAIABpAG4AcAB1AHQAIABhAHIAcgBhAHkALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AKgAvAFwAbgBcAG4AUgBlAHAAZQBhAHQAQwBvAGwAcwC7AyAAPQBcAG4ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHIAcgBhAHkALABcAG4AIAAgACAAIAByAGUAcABlAGEAdAAsAFwAbgBcAG4ASQBGACgATwBSACgASQBTAFQARQBYAFQAKAByAGUAcABlAGEAdAApACwAIAByAGUAcABlAGEAdAAgADwAPQAgADAAKQAsAFwAIgAjAFYAQQBMAFUARQAhAFwAIgAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABOAG8AcgBtAGEAbABpAHoAZQAgAHIAZQBwAGUAYQB0ACAAdgBlAGMAdABvAHIAXABuACAAIAAgACAAcgBlAHAAZQBhAHQALAAgACAAIAAgACAAIAAgACAAIABUAE8AQwBPAEwAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAaQBtAGUAbgBzAGkAbwBuAHMAXABuACAAIAAgACAAQQB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABDAE8ATABVAE0ATgBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIABSAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBXAFMAKAByAGUAcABlAGEAdAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEUAeAB0AGUAbgBkACAAcgBlAHAAZQBhAHQAIAB2AGUAYwB0AG8AcgAgAGkAZgAgAG4AZQBlAGQAZQBkAFwAbgAgACAAIAAgAGMALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAASQBGACgAQQB3ACAAPAA+ACAAUgBoACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEUAWABQAEEATgBEACgAcgBlAHAAZQBhAHQALAAgAEEAdwAsACAALAAgAEAAVABBAEsARQAoAHIAZQBwAGUAYQB0ACwAIAAtADEAKQApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHIAZQBwAGUAYQB0ACkALABcAG4AXABuACAAIAAgACAALwAvACAAQgBhAHMAZQAgAGMAbwBsAHUAbQBuACAAaQBuAGQAaQBjAGUAcwBcAG4AIAAgACAAIABpACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMARQBRAFUARQBOAEMARQAoAFIATwBXAFMAKABjACkAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABNAGEAeABpAG0AdQBtACAAcgBlAHAAZQBhAHQAIABjAG8AdQBuAHQAXABuACAAIAAgACAAbQAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAGMAKQAsAFwAbgBcAG4AIAAgACAAIAAvAC8AIABCAHUAaQBsAGQAIABpAG4AZABlAHgAIAB2AGUAYwB0AG8AcgBcAG4AIAAgACAAIABpAGQAeAAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAVABPAEMATwBMACgASQBGACgAUwBJAEcATgAoAGMAIAAtACAAUwBFAFEAVQBFAE4AQwBFACgALAAgAG0ALAAgADAAKQApACAAPQAgADEALABpACwATgBBACgAKQApACwAMgApACkALABcAG4AXABuACAAIAAgACAAZABlAGwAaQB2AGUAcgAsACAAIAAgACAAIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAYQByAHIAYQB5ACwAIABpAGQAeAAoACkAKQAsAFwAbgBcAG4AIAAgACAAIABkAGUAbABpAHYAZQByAFwAbgApACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFsAVABCAEQAXQAgAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEYAdQBuAGMAdABpAG8AbgA6ACAAIAAgACAAIABSAGUAcwBpAHoAZQC7A1wAbgBDAGEAdABlAGcAbwByAHkAOgAgACAAIAAgACAAVABCAEQAXABuAEEAdQB0AGgAbwByADoAIAAgACAAIAAgACAAIABQAGEAdAByAGkAYwBrACAASAAuAFwAbgBWAGUAcgBzAGkAbwBuADoAIAAgACAAIAAgACAAMQAuADEAXABuAFwAbgBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcAG4AIAAgACAAIABSAGUAcABlAGEAdABzACAAYQAgADIARAAgAGEAcgByAGEAeQAgAHYAZQByAHQAaQBjAGEAbABsAHkAIABhAG4AZAAvAG8AcgAgAGgAbwByAGkAegBvAG4AdABhAGwAbAB5ACAAYgB5ACAAaQBuAHQAZQBnAGUAcgAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AHMALgBcAG4AIAAgACAAIABVAHMAZQByAHMAIABtAGEAeQAgAHMAcABlAGMAaQBmAHkAIABoAGUAaQBnAGgAdAAsACAAdwBpAGQAdABoACwAIABvAHIAIABiAG8AdABoAC4AIABJAGYAIABlAGkAdABoAGUAcgAgAHAAYQByAGEAbQBlAHQAZQByACAAaQBzACAAbwBtAGkAdAB0AGUAZAAsAFwAbgAgACAAIAAgAHQAaABlACAAbwBtAGkAdAB0AGUAZAAgAGQAaQBtAGUAbgBzAGkAbwBuACAAZABlAGYAYQB1AGwAdABzACAAdABvACAAMQAuACAARwBlAG8AbQBlAHQAcgB5ACAAaQBzACAAcAByAGUAcwBlAHIAdgBlAGQAOwAgAG4AbwAgAGYAbABhAHQAdABlAG4AaQBuAGcAXABuACAAIAAgACAAbwBjAGMAdQByAHMALgBcAG4AXABuAEUAeABhAG0AcABsAGUAOgBcAG4AIAAgACAAIABJAG4AcAB1AHQAOgBcAG4AIAAgACAAIAAgACAAIAAgAHsAMQAsADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAMwAsADQAfQBcAG4AXABuACAAIAAgACAAPQBSAGUAcwBpAHoAZQC7AygAYQByAHIAYQB5ACwAIAAyACwAIAAzACkAXABuAFwAbgAgACAAIAAgAE8AdQB0AHAAdQB0ADoAXABuACAAIAAgACAAIAAgACAAIAB7ADEALAAyACwAMQAsADIALAAxACwAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAzACwANAAsADMALAA0ACwAMwAsADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAMQAsADIALAAxACwAMgAsADEALAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgADMALAA0ACwAMwAsADQALAAzACwANAB9AFwAbgBcAG4AUABhAHIAYQBtAGUAdABlAHIAcwA6AFwAbgAgACAAIAAgAGEAcgByAGEAeQAgACAAIAAgACAAIAAgACAALQAgAFIAZQBxAHUAaQByAGUAZAAgADIARAAgAGEAcgByAGEAeQAgAHQAbwAgAGIAZQAgAHIAZQBwAGUAYQB0AGUAZAAuAFwAbgAgACAAIAAgAFsAaABlAGkAZwBoAHQAXQAgACAAIAAgACAALQAgAE8AcAB0AGkAbwBuAGEAbAAgAHYAZQByAHQAaQBjAGEAbAAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAxAC4AXABuACAAIAAgACAAWwB3AGkAZAB0AGgAXQAgACAAIAAgACAAIAAtACAATwBwAHQAaQBvAG4AYQBsACAAaABvAHIAaQB6AG8AbgB0AGEAbAAgAHIAZQBwAGUAYQB0ACAAYwBvAHUAbgB0AC4AIABEAGUAZgBhAHUAbAB0AHMAIAB0AG8AIAAxAC4AXABuAFwAbgBOAG8AdABlAHMAOgBcAG4AIAAgACAAIAAiICAAUgBlAHAAZQB0AGkAdABpAG8AbgAgAGkAcwAgAHAAZQByAGYAbwByAG0AZQBkACAAdgBpAGEAIABpAG4AZABlAHgAIAByAGUAbQBhAHAAcABpAG4AZwAuAFwAbgAgACAAIAAgACIgIABPAHUAdABwAHUAdAAgAGcAZQBvAG0AZQB0AHIAeQAgAGkAcwAgACgAaAAgANcAIABoAGUAaQBnAGgAdAApACAAYgB5ACAAKAB3ACAA1wAgAHcAaQBkAHQAaAApAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtACoALwBcAG4AXABuAFIAZQBzAGkAegBlALsDIAA9AFwAbgBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFsAaABlAGkAZwBoAHQAXQAsAFwAbgAgACAAIAAgAFsAdwBpAGQAdABoAF0ALABcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABEAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGgALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwBTACgAYQByAHIAYQB5ACkALABcAG4AIAAgACAAIAB3ACwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AUwAoAGEAcgByAGEAeQApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAE8AbQBpAHMAcwBpAG8AbgAgAGMAaABlAGMAawBzAFwAbgAgACAAIAAgAEgAZQBpAGcAaAB0AE8AbQBpAHQAdABlAGQAPwAsACAAIABJAFMATwBNAEkAVABUAEUARAAoAGgAZQBpAGcAaAB0ACkALABcAG4AIAAgACAAIABXAGkAZAB0AGgATwBtAGkAdAB0AGUAZAA/ACwAIAAgACAASQBTAE8ATQBJAFQAVABFAEQAKAB3AGkAZAB0AGgAKQAsAFwAbgAgACAAIAAgAE4AbwBIAFcASQBuAHAAdQB0AD8ALAAgACAAIAAgACAAIABIAGUAaQBnAGgAdABPAG0AaQB0AHQAZQBkAD8AIAArACAAVwBpAGQAdABoAE8AbQBpAHQAdABlAGQAPwAgAD0AIAAyACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEQAZQBmAGEAdQBsAHQAIAByAGUAcABlAGEAdAAgAGMAbwB1AG4AdABzAFwAbgAgACAAIAAgAGgAZQBpAGcAaAB0ACwAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABOAG8ASABXAEkAbgBwAHUAdAA/ACwAIABIAGUAaQBnAGgAdABPAG0AaQB0AHQAZQBkAD8AKQAsACAAMQAsACAAaABlAGkAZwBoAHQAKQAsAFwAbgAgACAAIAAgAHcAaQBkAHQAaAAsACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABPAFIAKABOAG8ASABXAEkAbgBwAHUAdAA/ACwAIABXAGkAZAB0AGgATwBtAGkAdAB0AGUAZAA/ACkALAAgADEALAAgAHcAaQBkAHQAaAApACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAFMAYwBlAG4AYQByAGkAbwBzAFwAbgAgACAAIAAgAE4AbwBSAGUAcABlAGEAdAA/ACwAIAAgACAAIAAgACAAIABBAE4ARAAoAGgAZQBpAGcAaAB0ACAAPQAgADEALAAgAHcAaQBkAHQAaAAgAD0AIAAxACkALABcAG4AIAAgACAAIABJAHMAUwBjAGEAbABhAHIAPwAsACAAIAAgACAAIAAgACAAQQBOAEQAKABoACAAPQAgADEALAAgAHcAIAA9ACAAMQApACwAXABuACAAIAAgACAARQB4AHAAYQBuAGQAUwBjAGEAbABhAHIALAAgACAAIAAgAEUAWABQAEEATgBEACgAYQByAHIAYQB5ACwAIABoAGUAaQBnAGgAdAAsACAAdwBpAGQAdABoACwAIABhAHIAcgBhAHkAKQAsAFwAbgBcAG4AIAAgACAAIABJAG4AdgBhAGwAaQBkAFIAZQBwAGUAYQB0AD8ALAAgACAATwBSACgASQBTAFQARQBYAFQAKABoAGUAaQBnAGgAdAApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkAUwBUAEUAWABUACgAdwBpAGQAdABoACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAATwBSACgAQQBOAEQAKABJAFMATgBVAE0AQgBFAFIAKABoAGUAaQBnAGgAdAApACwAIABoAGUAaQBnAGgAdAAgADwAPQAgADAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABBAE4ARAAoAEkAUwBOAFUATQBCAEUAUgAoAHcAaQBkAHQAaAApACwAIAAgAHcAaQBkAHQAaAAgADwAPQAgADAAKQApACkALABcAG4AXABuACAAIAAgACAALwAvACAATABvAGcAaQBjACAAZwBhAHQAZQBcAG4AIAAgACAAIABJAEYAKABOAG8AUgBlAHAAZQBhAHQAPwAsACAAYQByAHIAYQB5ACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgASQBzAFMAYwBhAGwAYQByAD8ALAAgAEUAeABwAGEAbgBkAFMAYwBhAGwAYQByACwAXABuAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAG4AdgBhAGwAaQBkAFIAZQBwAGUAYQB0AD8ALAAgAGEAcgByAGEAeQAsAFwAbgBcAG4ATABFAFQAKABcAG4AIAAgACAAIAAvAC8AIABFAHgAcABhAG4AZABlAGQAIABkAGkAbQBlAG4AcwBpAG8AbgBzAFwAbgAgACAAIAAgAGsALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABoACAAKgAgAGgAZQBpAGcAaAB0ACwAXABuACAAIAAgACAAawCCICwAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAHcAIAAqACAAdwBpAGQAdABoACwAXABuAFwAbgAgACAAIAAgAC8ALwAgAEkAbgBkAGkAYwBlAHMAIAAoAGQAZQBmAGUAcgByAGUAZAApAFwAbgAgACAAIAAgAGkALAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoADEAIAArACAATQBPAEQAKABTAEUAUQBVAEUATgBDAEUAKABrACwALAAwACwAKQAsACAAaAApACAAKgAgAFMARQBRAFUARQBOAEMARQAoACwAIABrAIIgLAAgADEALAAgADAAKQApACwAXABuACAAIAAgACAAagAsACAAIAAgACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAMQAgACsAIABNAE8ARAAoAFMARQBRAFUARQBOAEMARQAoACwAIABrAIIgLAAgADAAKQAsACAAdwApACAAKgAgAFMARQBRAFUARQBOAEMARQAoAGsALAAsACAAMQAsACAAMAApACkALABcAG4AXABuACAAIAAgACAALwAvACAAQwBvAG4AcwB0AHIAdQBjAHQAIAByAGUAcABlAGEAdABlAGQAIABhAHIAcgBhAHkAXABuACAAIAAgACAAcgBlAHMAdQBsAHQALAAgACAAIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAGEAcgByAGEAeQAsACAAaQAoACkALAAgAGoAKAApACkALABcAG4AXABuACAAIAAgACAAcgBlAHMAdQBsAHQAXABuACkAKQApACkAKQApADsAXABuAFwAbgBcAG4ALwAvACAARQBuAGQAIABvAGYAIABNAG8AZAB1AGwAZQAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBNAGEAZwBuAGkAZgB5ALsDIgAsACIAQQBsAGkAZwBuAFIAbwB3AHMAuwMiACwAIgBBAGwAaQBnAG4AQwBvAGwAcwC7AyIALAAiAEYAbwBsAGQAuwMiACwAIgBaAGkAcAC7AyIALAAiAFAAYQBpAHIAdwBpAHMAZQC7AyIALAAiAFQAcgBpAHAAbABlAHcAaQBzAGUAuwMiACwAIgBRAHUAYQBkAHcAaQBzAGUAuwMiACwAIgBFAGMAaABvALsDIgAsACIAQgBsAG8AYwBrAHMAuwMiACwAIgBXAGkAbgBkAG8AdwBlAGQAuwMiACwAIgBDAG8AbgB2AG8AbAB2AGUAuwMiACwAIgBHAHIAaQBkAEwAbwBvAGsAdQBwALsDIgAsACIATgBhAHYAaQBnAGEAdABlADIARAC7AyIALAAiAE0AYQB0AGMAaAAyAEQAuwMiACwAIgBWAFMAcABsAGkAdAC7AyIALAAiAEgAUwBwAGwAaQB0ALsDIgAsACIATQBHAHIAaQBkALsDIgAsACIAUgBlAHAAZQBhAHQAUgBvAHcAcwC7AyIALAAiAFIAZQBwAGUAYQB0AEMAbwBsAHMAuwMiACwAIgBSAGUAcwBpAHoAZQC7AyIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIATQBEAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
